--- a/source/assets/workbooks/texas.xlsx
+++ b/source/assets/workbooks/texas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tpcus808.sharepoint.com/sites/DataEntryAutomation/Shared Documents/New Automation Documents/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F04EF44A1142426DCE9F4511414016BFA20E4AD1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68035730-C946-437E-B059-604666A1D1DB}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_F04EF44A1142426DCE9F4511414016BFA20E4AD1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8555807C-BFC7-45DE-B4A1-AF3E07847AD8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="851" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="435" windowWidth="21600" windowHeight="12450" tabRatio="851" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="310">
   <si>
     <t>35% of paid crew must be Texas Residents</t>
   </si>
@@ -709,25 +709,13 @@
     <t>Harris</t>
   </si>
   <si>
-    <t>DAY 1 of 4</t>
-  </si>
-  <si>
     <t>Dallas</t>
   </si>
   <si>
-    <t>DAY 2 of 4</t>
-  </si>
-  <si>
     <t>Tarrant</t>
   </si>
   <si>
-    <t>DAY 3 of 4</t>
-  </si>
-  <si>
     <t>Bexar</t>
-  </si>
-  <si>
-    <t>DAY 4 of 4</t>
   </si>
   <si>
     <t>Travis</t>
@@ -2735,14 +2723,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2750,6 +2730,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4480,62 +4468,62 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O66"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="122" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" style="122" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="122" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" style="122" customWidth="1"/>
     <col min="3" max="3" width="47" style="122" customWidth="1"/>
-    <col min="4" max="6" width="12.5703125" style="122" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="122" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="122" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="122" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" style="122" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="122" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.28515625" style="122" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="122" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="122" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" style="122" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="122" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="122"/>
+    <col min="4" max="6" width="12.5546875" style="122" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="122" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="122" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="122" customWidth="1"/>
+    <col min="10" max="10" width="20.88671875" style="122" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" style="122" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.33203125" style="122" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" style="122" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" style="122" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.109375" style="122" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="122" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="122"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="121" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="408" t="s">
+    <row r="1" spans="1:15" s="121" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="404" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="409"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
-      <c r="M1" s="409"/>
-      <c r="N1" s="409"/>
-    </row>
-    <row r="2" spans="1:15" s="121" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="408" t="s">
+      <c r="B1" s="405"/>
+      <c r="C1" s="405"/>
+      <c r="D1" s="405"/>
+      <c r="E1" s="405"/>
+      <c r="F1" s="405"/>
+      <c r="G1" s="405"/>
+      <c r="H1" s="405"/>
+      <c r="I1" s="405"/>
+      <c r="J1" s="405"/>
+      <c r="K1" s="405"/>
+      <c r="L1" s="405"/>
+      <c r="M1" s="405"/>
+      <c r="N1" s="405"/>
+    </row>
+    <row r="2" spans="1:15" s="121" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="404" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="409"/>
-      <c r="C2" s="409"/>
-      <c r="D2" s="409"/>
-      <c r="E2" s="409"/>
-      <c r="F2" s="409"/>
-      <c r="G2" s="409"/>
-      <c r="H2" s="409"/>
-      <c r="I2" s="409"/>
-      <c r="J2" s="409"/>
-      <c r="K2" s="409"/>
-      <c r="L2" s="409"/>
-      <c r="M2" s="409"/>
-      <c r="N2" s="409"/>
-    </row>
-    <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="405"/>
+      <c r="C2" s="405"/>
+      <c r="D2" s="405"/>
+      <c r="E2" s="405"/>
+      <c r="F2" s="405"/>
+      <c r="G2" s="405"/>
+      <c r="H2" s="405"/>
+      <c r="I2" s="405"/>
+      <c r="J2" s="405"/>
+      <c r="K2" s="405"/>
+      <c r="L2" s="405"/>
+      <c r="M2" s="405"/>
+      <c r="N2" s="405"/>
+    </row>
+    <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="229"/>
       <c r="B4" s="228" t="s">
         <v>65</v>
@@ -4557,7 +4545,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="229"/>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="229"/>
       <c r="B5" s="228" t="s">
         <v>68</v>
@@ -4573,7 +4561,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="229"/>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="229"/>
       <c r="B6" s="228"/>
       <c r="C6" s="387"/>
@@ -4585,7 +4573,7 @@
       <c r="M6" s="229"/>
       <c r="N6" s="229"/>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="229"/>
       <c r="B7" s="228" t="s">
         <v>69</v>
@@ -4599,7 +4587,7 @@
       <c r="M7" s="229"/>
       <c r="N7" s="229"/>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="229"/>
       <c r="B8" s="228" t="s">
         <v>70</v>
@@ -4611,7 +4599,7 @@
       <c r="M8" s="69"/>
       <c r="N8" s="229"/>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="229"/>
       <c r="B9" s="228" t="s">
         <v>71</v>
@@ -4621,7 +4609,7 @@
       </c>
       <c r="D9" s="229"/>
       <c r="E9" s="229"/>
-      <c r="G9" s="410" t="s">
+      <c r="G9" s="406" t="s">
         <v>72</v>
       </c>
       <c r="H9" s="407"/>
@@ -4632,7 +4620,7 @@
       <c r="M9" s="229"/>
       <c r="N9" s="229"/>
     </row>
-    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="229"/>
       <c r="B10" s="228" t="s">
         <v>73</v>
@@ -4656,7 +4644,7 @@
       <c r="N10" s="229"/>
       <c r="O10" s="229"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="229"/>
       <c r="B11" s="228" t="s">
         <v>76</v>
@@ -4678,7 +4666,7 @@
       <c r="N11" s="229"/>
       <c r="O11" s="229"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="229"/>
       <c r="B12" s="228"/>
       <c r="C12" s="229"/>
@@ -4698,7 +4686,7 @@
       <c r="N12" s="229"/>
       <c r="O12" s="229"/>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="229"/>
       <c r="B13" s="228" t="s">
         <v>79</v>
@@ -4724,7 +4712,7 @@
       <c r="N13" s="229"/>
       <c r="O13" s="229"/>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="229"/>
       <c r="B14" s="228" t="s">
         <v>81</v>
@@ -4743,7 +4731,7 @@
       <c r="N14" s="229"/>
       <c r="O14" s="229"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="229"/>
       <c r="B15" s="228" t="s">
         <v>82</v>
@@ -4768,7 +4756,7 @@
       <c r="N15" s="229"/>
       <c r="O15" s="81"/>
     </row>
-    <row r="16" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="229"/>
       <c r="B16" s="228" t="s">
         <v>86</v>
@@ -4802,7 +4790,7 @@
       <c r="N16" s="229"/>
       <c r="O16" s="81"/>
     </row>
-    <row r="17" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="228" t="s">
         <v>89</v>
       </c>
@@ -4835,7 +4823,7 @@
       <c r="N17" s="229"/>
       <c r="O17" s="229"/>
     </row>
-    <row r="18" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="228" t="s">
         <v>92</v>
       </c>
@@ -4866,7 +4854,7 @@
       <c r="N18" s="229"/>
       <c r="O18" s="229"/>
     </row>
-    <row r="19" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="228" t="s">
         <v>94</v>
       </c>
@@ -4897,7 +4885,7 @@
       <c r="N19" s="229"/>
       <c r="O19" s="229"/>
     </row>
-    <row r="20" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="228" t="s">
         <v>96</v>
       </c>
@@ -4928,7 +4916,7 @@
       <c r="N20" s="229"/>
       <c r="O20" s="229"/>
     </row>
-    <row r="21" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="310" t="s">
         <v>98</v>
       </c>
@@ -4959,7 +4947,7 @@
       <c r="N21" s="229"/>
       <c r="O21" s="229"/>
     </row>
-    <row r="22" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="310" t="s">
         <v>100</v>
       </c>
@@ -4990,7 +4978,7 @@
       <c r="N22" s="229"/>
       <c r="O22" s="229"/>
     </row>
-    <row r="23" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="310" t="s">
         <v>102</v>
       </c>
@@ -5020,7 +5008,7 @@
       <c r="N23" s="229"/>
       <c r="O23" s="229"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="310"/>
       <c r="C24" s="307"/>
       <c r="D24" s="229"/>
@@ -5036,7 +5024,7 @@
       <c r="N24" s="229"/>
       <c r="O24" s="229"/>
     </row>
-    <row r="25" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="228" t="s">
         <v>104</v>
       </c>
@@ -5067,7 +5055,7 @@
       <c r="N25" s="229"/>
       <c r="O25" s="229"/>
     </row>
-    <row r="26" spans="2:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B26" s="307"/>
       <c r="C26" s="307"/>
       <c r="D26" s="229"/>
@@ -5082,7 +5070,7 @@
       <c r="M26" s="229"/>
       <c r="N26" s="229"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="228" t="s">
         <v>106</v>
       </c>
@@ -5104,7 +5092,7 @@
       <c r="M27" s="229"/>
       <c r="N27" s="229"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="228" t="s">
         <v>108</v>
       </c>
@@ -5126,7 +5114,7 @@
       <c r="M28" s="229"/>
       <c r="N28" s="229"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="228" t="s">
         <v>110</v>
       </c>
@@ -5147,7 +5135,7 @@
       <c r="L29" s="229"/>
       <c r="M29" s="232"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="229"/>
       <c r="C30" s="229"/>
       <c r="D30" s="268"/>
@@ -5167,7 +5155,7 @@
       <c r="M30" s="236"/>
       <c r="N30" s="229"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="229"/>
       <c r="C31" t="s">
         <v>113</v>
@@ -5184,7 +5172,7 @@
       <c r="M31" s="236"/>
       <c r="N31" s="233"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="229"/>
       <c r="C32" t="s">
         <v>114</v>
@@ -5205,7 +5193,7 @@
       </c>
       <c r="N32" s="229"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B33" s="229"/>
       <c r="C33" t="s">
         <v>117</v>
@@ -5229,7 +5217,7 @@
       </c>
       <c r="N33" s="229"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="229"/>
       <c r="C34" t="s">
         <v>119</v>
@@ -5252,7 +5240,7 @@
       </c>
       <c r="N34" s="229"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="229"/>
       <c r="C35" t="s">
         <v>121</v>
@@ -5276,7 +5264,7 @@
       </c>
       <c r="N35" s="233"/>
     </row>
-    <row r="36" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="229"/>
       <c r="C36" t="s">
         <v>123</v>
@@ -5292,7 +5280,7 @@
       <c r="M36" s="242"/>
       <c r="N36" s="229"/>
     </row>
-    <row r="37" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="229"/>
       <c r="C37" s="229"/>
       <c r="D37" s="229"/>
@@ -5310,7 +5298,7 @@
       </c>
       <c r="N37" s="229"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" s="229"/>
       <c r="C38" t="s">
         <v>126</v>
@@ -5326,7 +5314,7 @@
       <c r="M38" s="229"/>
       <c r="N38" s="237"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B39" s="268"/>
       <c r="C39" t="s">
         <v>127</v>
@@ -5342,7 +5330,7 @@
       <c r="M39" s="229"/>
       <c r="N39" s="242"/>
     </row>
-    <row r="40" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="268"/>
       <c r="C40" t="s">
         <v>128</v>
@@ -5355,7 +5343,7 @@
       <c r="M40" s="229"/>
       <c r="N40" s="244"/>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B41" s="15" t="s">
         <v>129</v>
       </c>
@@ -5367,7 +5355,7 @@
       <c r="M41" s="15"/>
       <c r="N41" s="244"/>
     </row>
-    <row r="42" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="229"/>
       <c r="C42" s="143"/>
       <c r="D42" s="229"/>
@@ -5377,7 +5365,7 @@
       <c r="M42" s="229"/>
       <c r="N42" s="233"/>
     </row>
-    <row r="43" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="229"/>
       <c r="C43" s="374" t="s">
         <v>130</v>
@@ -5389,8 +5377,8 @@
       <c r="M43" s="229"/>
       <c r="N43" s="229"/>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C44" s="406" t="s">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C44" s="408" t="s">
         <v>131</v>
       </c>
       <c r="D44" s="407"/>
@@ -5402,8 +5390,8 @@
       <c r="M44" s="229"/>
       <c r="N44" s="229"/>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C45" s="406" t="s">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C45" s="408" t="s">
         <v>132</v>
       </c>
       <c r="D45" s="407"/>
@@ -5415,8 +5403,8 @@
       <c r="M45" s="229"/>
       <c r="N45" s="229"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C46" s="406" t="s">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C46" s="408" t="s">
         <v>133</v>
       </c>
       <c r="D46" s="407"/>
@@ -5428,8 +5416,8 @@
       <c r="M46" s="229"/>
       <c r="N46" s="229"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C47" s="406" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C47" s="408" t="s">
         <v>134</v>
       </c>
       <c r="D47" s="407"/>
@@ -5441,8 +5429,8 @@
       <c r="M47" s="229"/>
       <c r="N47" s="229"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C48" s="406" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C48" s="408" t="s">
         <v>135</v>
       </c>
       <c r="D48" s="407"/>
@@ -5454,8 +5442,8 @@
       <c r="M48" s="229"/>
       <c r="N48" s="229"/>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C49" s="406" t="s">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C49" s="408" t="s">
         <v>136</v>
       </c>
       <c r="D49" s="407"/>
@@ -5466,11 +5454,11 @@
       <c r="L49" s="229"/>
       <c r="M49" s="229"/>
     </row>
-    <row r="50" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="404" t="s">
+    <row r="50" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C50" s="409" t="s">
         <v>137</v>
       </c>
-      <c r="D50" s="405"/>
+      <c r="D50" s="410"/>
       <c r="E50" s="321" t="b">
         <v>0</v>
       </c>
@@ -5478,12 +5466,12 @@
       <c r="L50" s="229"/>
       <c r="M50" s="229"/>
     </row>
-    <row r="51" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H51" s="229"/>
       <c r="L51" s="229"/>
       <c r="M51" s="229"/>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C52" s="371" t="s">
         <v>138</v>
       </c>
@@ -5493,12 +5481,12 @@
       <c r="L52" s="229"/>
       <c r="M52" s="229"/>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C53" s="322"/>
       <c r="D53" s="229"/>
       <c r="E53" s="323"/>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C54" s="322"/>
       <c r="D54" s="135" t="s">
         <v>139</v>
@@ -5508,7 +5496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C55" s="325"/>
       <c r="D55" s="269" t="s">
         <v>140</v>
@@ -5518,7 +5506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C56" s="322"/>
       <c r="D56" s="135" t="s">
         <v>141</v>
@@ -5528,36 +5516,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C57" s="322"/>
       <c r="D57" s="229"/>
       <c r="E57" s="323"/>
     </row>
-    <row r="58" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C58" s="383" t="s">
         <v>142</v>
       </c>
       <c r="D58" s="384"/>
       <c r="E58" s="385"/>
     </row>
-    <row r="59" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C59" s="229"/>
       <c r="D59" s="229"/>
       <c r="E59" s="229"/>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C60" s="377" t="s">
         <v>143</v>
       </c>
       <c r="D60" s="378"/>
       <c r="E60" s="379"/>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C61" s="322"/>
       <c r="D61" s="229"/>
       <c r="E61" s="323"/>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C62" s="322"/>
       <c r="D62" s="15" t="s">
         <v>144</v>
@@ -5567,7 +5555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C63" s="325"/>
       <c r="D63" s="328" t="s">
         <v>145</v>
@@ -5577,7 +5565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="3:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C64" s="322"/>
       <c r="D64" s="15" t="s">
         <v>146</v>
@@ -5587,12 +5575,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C65" s="322"/>
       <c r="D65" s="229"/>
       <c r="E65" s="323"/>
     </row>
-    <row r="66" spans="3:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C66" s="380" t="s">
         <v>147</v>
       </c>
@@ -5601,16 +5589,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="51" orientation="landscape"/>
@@ -5629,31 +5617,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:X136"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="9" customWidth="1"/>
     <col min="3" max="3" width="9" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="101" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="27" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" customWidth="1"/>
-    <col min="11" max="12" width="17.85546875" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" style="8" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="37.5703125" style="32" customWidth="1"/>
-    <col min="16" max="16" width="31.7109375" style="32" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" style="32" customWidth="1"/>
-    <col min="18" max="18" width="10.140625" style="8" customWidth="1"/>
-    <col min="19" max="19" width="12.28515625" style="32" customWidth="1"/>
-    <col min="20" max="20" width="19.28515625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="101" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" style="27" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" customWidth="1"/>
+    <col min="11" max="12" width="17.88671875" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="37.5546875" style="32" customWidth="1"/>
+    <col min="16" max="16" width="31.6640625" style="32" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" style="32" customWidth="1"/>
+    <col min="18" max="18" width="10.109375" style="8" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" style="32" customWidth="1"/>
+    <col min="20" max="20" width="19.33203125" style="8" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="61.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.5546875" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="397"/>
       <c r="C1" s="398"/>
       <c r="D1" s="398"/>
@@ -5677,7 +5665,7 @@
       <c r="V1" s="417"/>
       <c r="W1" s="401"/>
     </row>
-    <row r="2" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -5701,7 +5689,7 @@
       <c r="V2" s="113"/>
       <c r="W2" s="31"/>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="D3" s="15"/>
       <c r="E3" s="23"/>
       <c r="L3" s="8"/>
@@ -5710,7 +5698,7 @@
       <c r="U3" s="32"/>
       <c r="W3" s="32"/>
     </row>
-    <row r="4" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D4" s="15"/>
       <c r="E4" s="4"/>
       <c r="I4" s="4"/>
@@ -5730,7 +5718,7 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
     </row>
-    <row r="5" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D5" s="15"/>
       <c r="E5" s="4"/>
       <c r="I5" s="4"/>
@@ -5745,58 +5733,58 @@
       <c r="R5" s="112"/>
       <c r="S5" s="112"/>
       <c r="T5" s="112" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
     </row>
-    <row r="6" spans="2:24" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="271" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="271" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D6" s="271" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E6" s="272" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F6" s="273" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G6" s="276" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H6" s="369" t="s">
         <v>61</v>
       </c>
       <c r="I6" s="276" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J6" s="276" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K6" s="274" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L6" s="274" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="274" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N6" s="274" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O6" s="274" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="P6" s="274" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q6" s="274" t="s">
         <v>168</v>
@@ -5808,16 +5796,16 @@
         <v>45</v>
       </c>
       <c r="T6" s="274" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="U6" s="274" t="s">
         <v>41</v>
       </c>
       <c r="V6" s="274" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B7" s="11">
         <v>1</v>
       </c>
@@ -5842,7 +5830,7 @@
       <c r="U7" s="16"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
         <v>2</v>
       </c>
@@ -5867,7 +5855,7 @@
       <c r="U8" s="16"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>3</v>
       </c>
@@ -5892,7 +5880,7 @@
       <c r="U9" s="16"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>4</v>
       </c>
@@ -5917,7 +5905,7 @@
       <c r="U10" s="16"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>5</v>
       </c>
@@ -5942,7 +5930,7 @@
       <c r="U11" s="16"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>6</v>
       </c>
@@ -5967,7 +5955,7 @@
       <c r="U12" s="16"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>7</v>
       </c>
@@ -5992,7 +5980,7 @@
       <c r="U13" s="16"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>8</v>
       </c>
@@ -6017,7 +6005,7 @@
       <c r="U14" s="16"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>9</v>
       </c>
@@ -6042,7 +6030,7 @@
       <c r="U15" s="16"/>
       <c r="V15" s="255"/>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>10</v>
       </c>
@@ -6067,7 +6055,7 @@
       <c r="U16" s="16"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>11</v>
       </c>
@@ -6092,7 +6080,7 @@
       <c r="U17" s="16"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>12</v>
       </c>
@@ -6117,7 +6105,7 @@
       <c r="U18" s="16"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>13</v>
       </c>
@@ -6142,7 +6130,7 @@
       <c r="U19" s="16"/>
       <c r="V19" s="255"/>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>14</v>
       </c>
@@ -6167,7 +6155,7 @@
       <c r="U20" s="16"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <v>15</v>
       </c>
@@ -6192,7 +6180,7 @@
       <c r="U21" s="16"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <v>16</v>
       </c>
@@ -6217,7 +6205,7 @@
       <c r="U22" s="16"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>17</v>
       </c>
@@ -6242,7 +6230,7 @@
       <c r="U23" s="16"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>18</v>
       </c>
@@ -6267,7 +6255,7 @@
       <c r="U24" s="16"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>19</v>
       </c>
@@ -6292,7 +6280,7 @@
       <c r="U25" s="16"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>20</v>
       </c>
@@ -6317,7 +6305,7 @@
       <c r="U26" s="16"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>21</v>
       </c>
@@ -6342,7 +6330,7 @@
       <c r="U27" s="16"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <v>22</v>
       </c>
@@ -6367,7 +6355,7 @@
       <c r="U28" s="16"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <v>23</v>
       </c>
@@ -6392,7 +6380,7 @@
       <c r="U29" s="16"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <v>24</v>
       </c>
@@ -6417,7 +6405,7 @@
       <c r="U30" s="16"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
         <v>25</v>
       </c>
@@ -6442,7 +6430,7 @@
       <c r="U31" s="16"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <v>26</v>
       </c>
@@ -6467,7 +6455,7 @@
       <c r="U32" s="16"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <v>27</v>
       </c>
@@ -6492,7 +6480,7 @@
       <c r="U33" s="16"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <v>28</v>
       </c>
@@ -6517,7 +6505,7 @@
       <c r="U34" s="16"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <v>29</v>
       </c>
@@ -6542,7 +6530,7 @@
       <c r="U35" s="16"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <v>30</v>
       </c>
@@ -6567,7 +6555,7 @@
       <c r="U36" s="16"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <v>31</v>
       </c>
@@ -6592,7 +6580,7 @@
       <c r="U37" s="16"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <v>32</v>
       </c>
@@ -6617,7 +6605,7 @@
       <c r="U38" s="16"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <v>33</v>
       </c>
@@ -6642,7 +6630,7 @@
       <c r="U39" s="16"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <v>34</v>
       </c>
@@ -6667,7 +6655,7 @@
       <c r="U40" s="16"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
         <v>35</v>
       </c>
@@ -6692,7 +6680,7 @@
       <c r="U41" s="16"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
         <v>36</v>
       </c>
@@ -6717,7 +6705,7 @@
       <c r="U42" s="16"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B43" s="11">
         <v>37</v>
       </c>
@@ -6742,7 +6730,7 @@
       <c r="U43" s="16"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B44" s="11">
         <v>38</v>
       </c>
@@ -6767,7 +6755,7 @@
       <c r="U44" s="16"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B45" s="11">
         <v>39</v>
       </c>
@@ -6792,7 +6780,7 @@
       <c r="U45" s="16"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B46" s="11">
         <v>40</v>
       </c>
@@ -6817,7 +6805,7 @@
       <c r="U46" s="16"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B47" s="11">
         <v>41</v>
       </c>
@@ -6842,7 +6830,7 @@
       <c r="U47" s="16"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B48" s="11">
         <v>42</v>
       </c>
@@ -6867,7 +6855,7 @@
       <c r="U48" s="16"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
         <v>43</v>
       </c>
@@ -6892,7 +6880,7 @@
       <c r="U49" s="16"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B50" s="11">
         <v>44</v>
       </c>
@@ -6917,7 +6905,7 @@
       <c r="U50" s="16"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B51" s="11">
         <v>45</v>
       </c>
@@ -6942,7 +6930,7 @@
       <c r="U51" s="16"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <v>46</v>
       </c>
@@ -6967,7 +6955,7 @@
       <c r="U52" s="16"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
         <v>47</v>
       </c>
@@ -6992,7 +6980,7 @@
       <c r="U53" s="16"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B54" s="11">
         <v>48</v>
       </c>
@@ -7017,7 +7005,7 @@
       <c r="U54" s="16"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B55" s="11">
         <v>49</v>
       </c>
@@ -7042,7 +7030,7 @@
       <c r="U55" s="16"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B56" s="11">
         <v>50</v>
       </c>
@@ -7067,7 +7055,7 @@
       <c r="U56" s="16"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
         <v>51</v>
       </c>
@@ -7092,7 +7080,7 @@
       <c r="U57" s="16"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <v>52</v>
       </c>
@@ -7117,7 +7105,7 @@
       <c r="U58" s="16"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <v>53</v>
       </c>
@@ -7142,7 +7130,7 @@
       <c r="U59" s="16"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
         <v>54</v>
       </c>
@@ -7167,7 +7155,7 @@
       <c r="U60" s="16"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <v>55</v>
       </c>
@@ -7192,7 +7180,7 @@
       <c r="U61" s="16"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
         <v>56</v>
       </c>
@@ -7217,7 +7205,7 @@
       <c r="U62" s="16"/>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
         <v>57</v>
       </c>
@@ -7242,7 +7230,7 @@
       <c r="U63" s="16"/>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
         <v>58</v>
       </c>
@@ -7267,7 +7255,7 @@
       <c r="U64" s="16"/>
       <c r="V64" s="1"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
         <v>59</v>
       </c>
@@ -7292,7 +7280,7 @@
       <c r="U65" s="16"/>
       <c r="V65" s="1"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
         <v>60</v>
       </c>
@@ -7317,7 +7305,7 @@
       <c r="U66" s="16"/>
       <c r="V66" s="1"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
         <v>61</v>
       </c>
@@ -7342,7 +7330,7 @@
       <c r="U67" s="16"/>
       <c r="V67" s="255"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
         <v>62</v>
       </c>
@@ -7367,7 +7355,7 @@
       <c r="U68" s="16"/>
       <c r="V68" s="1"/>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
         <v>63</v>
       </c>
@@ -7392,7 +7380,7 @@
       <c r="U69" s="16"/>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B70" s="11">
         <v>64</v>
       </c>
@@ -7417,7 +7405,7 @@
       <c r="U70" s="16"/>
       <c r="V70" s="1"/>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
         <v>65</v>
       </c>
@@ -7442,7 +7430,7 @@
       <c r="U71" s="16"/>
       <c r="V71" s="1"/>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B72" s="11">
         <v>66</v>
       </c>
@@ -7467,7 +7455,7 @@
       <c r="U72" s="16"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B73" s="11">
         <v>67</v>
       </c>
@@ -7492,7 +7480,7 @@
       <c r="U73" s="16"/>
       <c r="V73" s="255"/>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B74" s="11">
         <v>68</v>
       </c>
@@ -7517,7 +7505,7 @@
       <c r="U74" s="16"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B75" s="11">
         <v>69</v>
       </c>
@@ -7542,7 +7530,7 @@
       <c r="U75" s="16"/>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B76" s="11">
         <v>70</v>
       </c>
@@ -7567,7 +7555,7 @@
       <c r="U76" s="16"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
         <v>71</v>
       </c>
@@ -7592,7 +7580,7 @@
       <c r="U77" s="16"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B78" s="11">
         <v>72</v>
       </c>
@@ -7617,7 +7605,7 @@
       <c r="U78" s="16"/>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B79" s="11">
         <v>73</v>
       </c>
@@ -7642,7 +7630,7 @@
       <c r="U79" s="16"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B80" s="11">
         <v>74</v>
       </c>
@@ -7667,7 +7655,7 @@
       <c r="U80" s="16"/>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
         <v>75</v>
       </c>
@@ -7692,7 +7680,7 @@
       <c r="U81" s="16"/>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
         <v>76</v>
       </c>
@@ -7717,7 +7705,7 @@
       <c r="U82" s="16"/>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
         <v>77</v>
       </c>
@@ -7742,7 +7730,7 @@
       <c r="U83" s="16"/>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
         <v>78</v>
       </c>
@@ -7767,7 +7755,7 @@
       <c r="U84" s="16"/>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
         <v>79</v>
       </c>
@@ -7792,7 +7780,7 @@
       <c r="U85" s="16"/>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
         <v>80</v>
       </c>
@@ -7817,7 +7805,7 @@
       <c r="U86" s="16"/>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
         <v>81</v>
       </c>
@@ -7842,7 +7830,7 @@
       <c r="U87" s="16"/>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B88" s="11">
         <v>82</v>
       </c>
@@ -7867,7 +7855,7 @@
       <c r="U88" s="16"/>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B89" s="11">
         <v>83</v>
       </c>
@@ -7892,7 +7880,7 @@
       <c r="U89" s="16"/>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B90" s="11">
         <v>84</v>
       </c>
@@ -7917,7 +7905,7 @@
       <c r="U90" s="16"/>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B91" s="11">
         <v>85</v>
       </c>
@@ -7942,7 +7930,7 @@
       <c r="U91" s="16"/>
       <c r="V91" s="1"/>
     </row>
-    <row r="92" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B92" s="11">
         <v>86</v>
       </c>
@@ -7967,7 +7955,7 @@
       <c r="U92" s="16"/>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B93" s="11">
         <v>87</v>
       </c>
@@ -7992,7 +7980,7 @@
       <c r="U93" s="16"/>
       <c r="V93" s="1"/>
     </row>
-    <row r="94" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B94" s="11">
         <v>88</v>
       </c>
@@ -8017,7 +8005,7 @@
       <c r="U94" s="16"/>
       <c r="V94" s="1"/>
     </row>
-    <row r="95" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
         <v>89</v>
       </c>
@@ -8042,7 +8030,7 @@
       <c r="U95" s="16"/>
       <c r="V95" s="1"/>
     </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
         <v>90</v>
       </c>
@@ -8067,7 +8055,7 @@
       <c r="U96" s="16"/>
       <c r="V96" s="1"/>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
         <v>91</v>
       </c>
@@ -8092,7 +8080,7 @@
       <c r="U97" s="16"/>
       <c r="V97" s="1"/>
     </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B98" s="11">
         <v>92</v>
       </c>
@@ -8117,7 +8105,7 @@
       <c r="U98" s="16"/>
       <c r="V98" s="1"/>
     </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B99" s="11">
         <v>93</v>
       </c>
@@ -8142,7 +8130,7 @@
       <c r="U99" s="16"/>
       <c r="V99" s="1"/>
     </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
         <v>94</v>
       </c>
@@ -8167,7 +8155,7 @@
       <c r="U100" s="16"/>
       <c r="V100" s="1"/>
     </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B101" s="11">
         <v>95</v>
       </c>
@@ -8192,7 +8180,7 @@
       <c r="U101" s="16"/>
       <c r="V101" s="1"/>
     </row>
-    <row r="102" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B102" s="11">
         <v>96</v>
       </c>
@@ -8217,7 +8205,7 @@
       <c r="U102" s="16"/>
       <c r="V102" s="1"/>
     </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B103" s="11">
         <v>97</v>
       </c>
@@ -8242,7 +8230,7 @@
       <c r="U103" s="16"/>
       <c r="V103" s="1"/>
     </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B104" s="11">
         <v>98</v>
       </c>
@@ -8267,7 +8255,7 @@
       <c r="U104" s="16"/>
       <c r="V104" s="1"/>
     </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B105" s="11">
         <v>99</v>
       </c>
@@ -8292,7 +8280,7 @@
       <c r="U105" s="16"/>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
         <v>100</v>
       </c>
@@ -8317,7 +8305,7 @@
       <c r="U106" s="16"/>
       <c r="V106" s="1"/>
     </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B107" s="256"/>
       <c r="C107" s="256"/>
       <c r="D107" s="257"/>
@@ -8340,9 +8328,9 @@
       <c r="U107" s="263"/>
       <c r="V107" s="1"/>
     </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:22" x14ac:dyDescent="0.3">
       <c r="E108" s="108" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F108" s="88"/>
       <c r="G108" s="297">
@@ -8365,14 +8353,14 @@
       <c r="U108" s="56"/>
       <c r="V108" s="63"/>
     </row>
-    <row r="109" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:22" x14ac:dyDescent="0.3">
       <c r="F109" s="47"/>
       <c r="O109" s="64"/>
       <c r="U109" s="38"/>
     </row>
-    <row r="111" spans="2:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E111" s="109" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G111" s="99">
         <f>SUM(G7:G107)</f>
@@ -8386,12 +8374,12 @@
       <c r="M111" s="14"/>
       <c r="N111" s="3"/>
     </row>
-    <row r="112" spans="2:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F112" s="47"/>
       <c r="O112" s="35"/>
       <c r="U112" s="3"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="402" t="s">
         <v>55</v>
       </c>
@@ -8403,7 +8391,7 @@
       <c r="K115" s="128"/>
       <c r="L115" s="129"/>
     </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="65" t="s">
         <v>57</v>
       </c>
@@ -8423,7 +8411,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="110">
         <f>SUMIF($U$7:$U$106,E116,$I$7:$I$106)</f>
         <v>0</v>
@@ -8457,7 +8445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="H118" s="95">
         <f>I111-H117</f>
         <v>0</v>
@@ -8470,14 +8458,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="111"/>
       <c r="F119" s="46"/>
       <c r="G119" s="46"/>
       <c r="J119" s="8"/>
       <c r="L119" s="8"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="G120" s="46"/>
       <c r="H120" s="46" t="s">
         <v>60</v>
@@ -8489,7 +8477,7 @@
       <c r="K120" s="66"/>
       <c r="L120" s="8"/>
     </row>
-    <row r="121" spans="5:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G121" s="46"/>
       <c r="H121" s="97" t="s">
         <v>61</v>
@@ -8501,7 +8489,7 @@
       <c r="K121" s="66"/>
       <c r="L121" s="8"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G122" s="46"/>
       <c r="H122" s="46" t="s">
         <v>62</v>
@@ -8513,7 +8501,7 @@
       <c r="K122" s="66"/>
       <c r="L122" s="8"/>
     </row>
-    <row r="123" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:13" x14ac:dyDescent="0.3">
       <c r="G123" s="46"/>
       <c r="I123" s="46"/>
       <c r="J123" s="95">
@@ -8523,12 +8511,12 @@
       <c r="K123" s="66"/>
       <c r="L123" s="8"/>
     </row>
-    <row r="125" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E125" s="167" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F125" s="161" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G125" s="39" t="s">
         <v>32</v>
@@ -8537,16 +8525,16 @@
         <v>53</v>
       </c>
       <c r="I125" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J125" s="39" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="K125" s="39" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:13" x14ac:dyDescent="0.3">
       <c r="F126" s="8"/>
       <c r="G126" s="50">
         <f t="shared" ref="G126:G134" si="0">SUMIFS($G$7:$G$107, $J$7:$J$107, E126, $D$7:$D$107, F126)</f>
@@ -8563,7 +8551,7 @@
       <c r="J126" s="8"/>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:13" x14ac:dyDescent="0.3">
       <c r="F127" s="8"/>
       <c r="G127" s="50">
         <f t="shared" si="0"/>
@@ -8580,7 +8568,7 @@
       <c r="J127" s="8"/>
       <c r="K127" s="8"/>
     </row>
-    <row r="128" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:13" x14ac:dyDescent="0.3">
       <c r="F128" s="8"/>
       <c r="G128" s="50">
         <f t="shared" si="0"/>
@@ -8597,7 +8585,7 @@
       <c r="J128" s="8"/>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F129" s="8"/>
       <c r="G129" s="50">
         <f t="shared" si="0"/>
@@ -8614,7 +8602,7 @@
       <c r="J129" s="8"/>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F130" s="8"/>
       <c r="G130" s="50">
         <f t="shared" si="0"/>
@@ -8631,7 +8619,7 @@
       <c r="J130" s="8"/>
       <c r="K130" s="8"/>
     </row>
-    <row r="131" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F131" s="8"/>
       <c r="G131" s="50">
         <f t="shared" si="0"/>
@@ -8648,7 +8636,7 @@
       <c r="J131" s="8"/>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F132" s="8"/>
       <c r="G132" s="50">
         <f t="shared" si="0"/>
@@ -8665,7 +8653,7 @@
       <c r="J132" s="8"/>
       <c r="K132" s="8"/>
     </row>
-    <row r="133" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F133" s="8"/>
       <c r="G133" s="50">
         <f t="shared" si="0"/>
@@ -8682,7 +8670,7 @@
       <c r="J133" s="8"/>
       <c r="K133" s="8"/>
     </row>
-    <row r="134" spans="5:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="5:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E134" s="172"/>
       <c r="F134" s="165"/>
       <c r="G134" s="170">
@@ -8700,7 +8688,7 @@
       <c r="J134" s="165"/>
       <c r="K134" s="165"/>
     </row>
-    <row r="135" spans="5:11" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:11" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F135" t="s">
         <v>32</v>
       </c>
@@ -8718,7 +8706,7 @@
       </c>
       <c r="J135" s="8"/>
     </row>
-    <row r="136" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:11" x14ac:dyDescent="0.3">
       <c r="G136" s="95">
         <f>G135-G111</f>
         <v>0</v>
@@ -8811,35 +8799,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AA53"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="107" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="107" customWidth="1"/>
     <col min="4" max="4" width="22" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="46" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="46" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="46" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="46" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" style="46" customWidth="1"/>
     <col min="9" max="9" width="37" style="66" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="8" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="8" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" style="8" customWidth="1"/>
     <col min="16" max="16" width="51" style="32" customWidth="1"/>
-    <col min="17" max="17" width="28.28515625" style="8" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" style="8" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="8" customWidth="1"/>
-    <col min="21" max="21" width="19.28515625" style="8" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" customWidth="1"/>
+    <col min="17" max="17" width="28.33203125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" style="8" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="8" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="8" customWidth="1"/>
+    <col min="21" max="21" width="19.33203125" style="8" customWidth="1"/>
+    <col min="22" max="22" width="15.5546875" customWidth="1"/>
     <col min="23" max="23" width="55" style="32" customWidth="1"/>
-    <col min="24" max="24" width="23.140625" style="32" customWidth="1"/>
+    <col min="24" max="24" width="23.109375" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="397"/>
       <c r="C1" s="413"/>
       <c r="D1" s="396"/>
@@ -8866,7 +8854,7 @@
       <c r="Y1" s="401"/>
       <c r="Z1" s="401"/>
     </row>
-    <row r="2" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -8893,7 +8881,7 @@
       <c r="Y2" s="113"/>
       <c r="Z2" s="31"/>
     </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="15"/>
       <c r="E3" s="23"/>
@@ -8901,7 +8889,7 @@
       <c r="V3" s="32"/>
       <c r="Z3" s="32"/>
     </row>
-    <row r="4" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="D4" s="15"/>
       <c r="E4" s="4"/>
@@ -8921,7 +8909,7 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
     </row>
-    <row r="5" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
       <c r="E5" s="4"/>
@@ -8941,32 +8929,32 @@
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
       <c r="D7" s="208" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H7" s="209" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I7" s="210" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K7" s="208" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L7" s="208" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="2:27" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="79" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>52</v>
@@ -8975,40 +8963,40 @@
         <v>11</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G8" s="51" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="R8" s="12" t="s">
         <v>168</v>
@@ -9020,7 +9008,7 @@
         <v>45</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="V8" s="12" t="s">
         <v>41</v>
@@ -9029,10 +9017,10 @@
         <v>46</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>1</v>
       </c>
@@ -9065,7 +9053,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="29"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>2</v>
       </c>
@@ -9099,7 +9087,7 @@
       <c r="W10" s="36"/>
       <c r="X10" s="29"/>
     </row>
-    <row r="11" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>3</v>
       </c>
@@ -9133,7 +9121,7 @@
       <c r="W11" s="36"/>
       <c r="X11" s="29"/>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>4</v>
       </c>
@@ -9167,7 +9155,7 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>5</v>
       </c>
@@ -9201,7 +9189,7 @@
       <c r="W13" s="36"/>
       <c r="X13" s="36"/>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>6</v>
       </c>
@@ -9235,7 +9223,7 @@
       <c r="W14" s="36"/>
       <c r="X14" s="36"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>7</v>
       </c>
@@ -9269,7 +9257,7 @@
       <c r="W15" s="36"/>
       <c r="X15" s="36"/>
     </row>
-    <row r="16" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>8</v>
       </c>
@@ -9303,7 +9291,7 @@
       <c r="W16" s="36"/>
       <c r="X16" s="36"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>9</v>
       </c>
@@ -9337,7 +9325,7 @@
       <c r="W17" s="36"/>
       <c r="X17" s="36"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>10</v>
       </c>
@@ -9371,7 +9359,7 @@
       <c r="W18" s="36"/>
       <c r="X18" s="36"/>
     </row>
-    <row r="19" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>11</v>
       </c>
@@ -9405,7 +9393,7 @@
       <c r="W19" s="36"/>
       <c r="X19" s="36"/>
     </row>
-    <row r="20" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>12</v>
       </c>
@@ -9439,7 +9427,7 @@
       <c r="W20" s="36"/>
       <c r="X20" s="36"/>
     </row>
-    <row r="21" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <v>13</v>
       </c>
@@ -9473,7 +9461,7 @@
       <c r="W21" s="36"/>
       <c r="X21" s="36"/>
     </row>
-    <row r="22" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <v>14</v>
       </c>
@@ -9507,7 +9495,7 @@
       <c r="W22" s="36"/>
       <c r="X22" s="36"/>
     </row>
-    <row r="23" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>15</v>
       </c>
@@ -9541,7 +9529,7 @@
       <c r="W23" s="36"/>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>16</v>
       </c>
@@ -9575,7 +9563,7 @@
       <c r="W24" s="36"/>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>17</v>
       </c>
@@ -9609,7 +9597,7 @@
       <c r="W25" s="36"/>
       <c r="X25" s="36"/>
     </row>
-    <row r="26" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>18</v>
       </c>
@@ -9643,7 +9631,7 @@
       <c r="W26" s="36"/>
       <c r="X26" s="36"/>
     </row>
-    <row r="27" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>19</v>
       </c>
@@ -9677,7 +9665,7 @@
       <c r="W27" s="36"/>
       <c r="X27" s="36"/>
     </row>
-    <row r="28" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <v>20</v>
       </c>
@@ -9711,7 +9699,7 @@
       <c r="W28" s="36"/>
       <c r="X28" s="36"/>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B29" s="11"/>
       <c r="C29" s="106"/>
       <c r="D29" s="16"/>
@@ -9743,7 +9731,7 @@
       <c r="W29" s="36"/>
       <c r="X29" s="36"/>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C30" s="102"/>
       <c r="D30" s="59"/>
       <c r="E30" s="78"/>
@@ -9779,17 +9767,17 @@
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
       <c r="F31" s="50"/>
       <c r="G31" s="50"/>
       <c r="H31" s="50"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.3">
       <c r="F32" s="50"/>
       <c r="G32" s="50"/>
       <c r="H32" s="50"/>
     </row>
-    <row r="33" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="103"/>
       <c r="D33" s="20"/>
       <c r="E33" s="28"/>
@@ -9819,10 +9807,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="3"/>
     </row>
-    <row r="34" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M34" s="14"/>
     </row>
-    <row r="37" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D37" s="402" t="s">
         <v>55</v>
       </c>
@@ -9835,7 +9823,7 @@
       <c r="K37" s="392"/>
       <c r="L37" s="393"/>
     </row>
-    <row r="38" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D38" s="16" t="s">
         <v>57</v>
       </c>
@@ -9856,7 +9844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D39" s="92">
         <f>SUMIF($V$9:$V$29,D$38,$H$9:$H$29)</f>
         <v>0</v>
@@ -9890,7 +9878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G40" s="95">
         <f>H33-G39</f>
         <v>0</v>
@@ -9902,12 +9890,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D41" s="46"/>
       <c r="E41" s="46"/>
       <c r="G41" s="66"/>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G42" s="119" t="s">
         <v>60</v>
       </c>
@@ -9918,7 +9906,7 @@
       <c r="I42" s="46"/>
       <c r="J42" s="116"/>
     </row>
-    <row r="43" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G43" s="120" t="s">
         <v>61</v>
       </c>
@@ -9929,7 +9917,7 @@
       <c r="I43" s="46"/>
       <c r="J43" s="116"/>
     </row>
-    <row r="44" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G44" s="119" t="s">
         <v>62</v>
       </c>
@@ -9940,20 +9928,20 @@
       <c r="I44" s="46"/>
       <c r="J44" s="116"/>
     </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:22" x14ac:dyDescent="0.3">
       <c r="H45" s="95">
         <f>F33-H44</f>
         <v>0</v>
       </c>
       <c r="I45" s="46"/>
     </row>
-    <row r="46" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:22" x14ac:dyDescent="0.3">
       <c r="H46" s="95"/>
       <c r="I46" s="46"/>
     </row>
-    <row r="48" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G48" s="162" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H48" s="162" t="s">
         <v>32</v>
@@ -9965,9 +9953,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G49" s="46" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H49" s="46">
         <f>SUMIF($J$9:$J$29,G49,$F$9:$F$29)</f>
@@ -9982,9 +9970,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G50" s="46" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H50" s="46">
         <f>SUMIF($J$9:$J$29,G50,$F$9:$F$29)</f>
@@ -9999,9 +9987,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="97" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H51" s="97">
         <f>SUMIF($J$9:$J$29,G51,$F$9:$F$29)</f>
@@ -10016,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="7:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="H52" s="46">
         <f>SUM(H49:H51)</f>
         <v>0</v>
@@ -10030,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
       <c r="H53" s="94">
         <f>H52-H44</f>
         <v>0</v>
@@ -10116,35 +10104,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AA53"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="107" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="107" customWidth="1"/>
     <col min="4" max="4" width="22" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="46" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="46" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="46" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="46" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" style="46" customWidth="1"/>
     <col min="9" max="9" width="37" style="66" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="8" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="8" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" style="8" customWidth="1"/>
     <col min="16" max="16" width="51" style="32" customWidth="1"/>
-    <col min="17" max="17" width="28.28515625" style="8" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" style="8" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="8" customWidth="1"/>
-    <col min="21" max="21" width="19.28515625" style="8" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" customWidth="1"/>
+    <col min="17" max="17" width="28.33203125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" style="8" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="8" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="8" customWidth="1"/>
+    <col min="21" max="21" width="19.33203125" style="8" customWidth="1"/>
+    <col min="22" max="22" width="15.5546875" customWidth="1"/>
     <col min="23" max="23" width="55" style="32" customWidth="1"/>
-    <col min="24" max="24" width="23.140625" style="32" customWidth="1"/>
+    <col min="24" max="24" width="23.109375" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="397"/>
       <c r="C1" s="413"/>
       <c r="D1" s="396"/>
@@ -10171,7 +10159,7 @@
       <c r="Y1" s="401"/>
       <c r="Z1" s="401"/>
     </row>
-    <row r="2" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -10198,7 +10186,7 @@
       <c r="Y2" s="113"/>
       <c r="Z2" s="31"/>
     </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="15"/>
       <c r="E3" s="23"/>
@@ -10206,7 +10194,7 @@
       <c r="V3" s="32"/>
       <c r="Z3" s="32"/>
     </row>
-    <row r="4" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="D4" s="15"/>
       <c r="E4" s="4"/>
@@ -10226,7 +10214,7 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
     </row>
-    <row r="5" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
       <c r="E5" s="4"/>
@@ -10246,32 +10234,32 @@
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
       <c r="D7" s="208" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H7" s="209" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I7" s="210" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K7" s="208" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L7" s="208" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="2:27" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="79" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>52</v>
@@ -10280,40 +10268,40 @@
         <v>11</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G8" s="51" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="R8" s="12" t="s">
         <v>168</v>
@@ -10325,7 +10313,7 @@
         <v>45</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="V8" s="12" t="s">
         <v>41</v>
@@ -10334,10 +10322,10 @@
         <v>46</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>1</v>
       </c>
@@ -10370,7 +10358,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="29"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>2</v>
       </c>
@@ -10404,7 +10392,7 @@
       <c r="W10" s="36"/>
       <c r="X10" s="29"/>
     </row>
-    <row r="11" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>3</v>
       </c>
@@ -10438,7 +10426,7 @@
       <c r="W11" s="36"/>
       <c r="X11" s="29"/>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>4</v>
       </c>
@@ -10472,7 +10460,7 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>5</v>
       </c>
@@ -10506,7 +10494,7 @@
       <c r="W13" s="36"/>
       <c r="X13" s="36"/>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>6</v>
       </c>
@@ -10540,7 +10528,7 @@
       <c r="W14" s="36"/>
       <c r="X14" s="36"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>7</v>
       </c>
@@ -10574,7 +10562,7 @@
       <c r="W15" s="36"/>
       <c r="X15" s="36"/>
     </row>
-    <row r="16" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>8</v>
       </c>
@@ -10608,7 +10596,7 @@
       <c r="W16" s="36"/>
       <c r="X16" s="36"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>9</v>
       </c>
@@ -10642,7 +10630,7 @@
       <c r="W17" s="36"/>
       <c r="X17" s="36"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>10</v>
       </c>
@@ -10676,7 +10664,7 @@
       <c r="W18" s="36"/>
       <c r="X18" s="36"/>
     </row>
-    <row r="19" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>11</v>
       </c>
@@ -10710,7 +10698,7 @@
       <c r="W19" s="36"/>
       <c r="X19" s="36"/>
     </row>
-    <row r="20" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>12</v>
       </c>
@@ -10744,7 +10732,7 @@
       <c r="W20" s="36"/>
       <c r="X20" s="36"/>
     </row>
-    <row r="21" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <v>13</v>
       </c>
@@ -10778,7 +10766,7 @@
       <c r="W21" s="36"/>
       <c r="X21" s="36"/>
     </row>
-    <row r="22" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <v>14</v>
       </c>
@@ -10812,7 +10800,7 @@
       <c r="W22" s="36"/>
       <c r="X22" s="36"/>
     </row>
-    <row r="23" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>15</v>
       </c>
@@ -10846,7 +10834,7 @@
       <c r="W23" s="36"/>
       <c r="X23" s="36"/>
     </row>
-    <row r="24" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>16</v>
       </c>
@@ -10880,7 +10868,7 @@
       <c r="W24" s="36"/>
       <c r="X24" s="36"/>
     </row>
-    <row r="25" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>17</v>
       </c>
@@ -10914,7 +10902,7 @@
       <c r="W25" s="36"/>
       <c r="X25" s="36"/>
     </row>
-    <row r="26" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>18</v>
       </c>
@@ -10948,7 +10936,7 @@
       <c r="W26" s="36"/>
       <c r="X26" s="36"/>
     </row>
-    <row r="27" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>19</v>
       </c>
@@ -10982,7 +10970,7 @@
       <c r="W27" s="36"/>
       <c r="X27" s="36"/>
     </row>
-    <row r="28" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <v>20</v>
       </c>
@@ -11016,7 +11004,7 @@
       <c r="W28" s="36"/>
       <c r="X28" s="36"/>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B29" s="11"/>
       <c r="C29" s="106"/>
       <c r="D29" s="16"/>
@@ -11048,7 +11036,7 @@
       <c r="W29" s="36"/>
       <c r="X29" s="36"/>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C30" s="102"/>
       <c r="D30" s="59"/>
       <c r="E30" s="78"/>
@@ -11084,17 +11072,17 @@
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
       <c r="F31" s="50"/>
       <c r="G31" s="50"/>
       <c r="H31" s="50"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.3">
       <c r="F32" s="50"/>
       <c r="G32" s="50"/>
       <c r="H32" s="50"/>
     </row>
-    <row r="33" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="103"/>
       <c r="D33" s="20"/>
       <c r="E33" s="28"/>
@@ -11124,10 +11112,10 @@
       <c r="U33" s="14"/>
       <c r="V33" s="3"/>
     </row>
-    <row r="34" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M34" s="14"/>
     </row>
-    <row r="37" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D37" s="402" t="s">
         <v>55</v>
       </c>
@@ -11140,7 +11128,7 @@
       <c r="K37" s="392"/>
       <c r="L37" s="393"/>
     </row>
-    <row r="38" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D38" s="16" t="s">
         <v>57</v>
       </c>
@@ -11161,7 +11149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D39" s="92">
         <f>SUMIF($V$9:$V$29,D$38,$H$9:$H$29)</f>
         <v>0</v>
@@ -11195,7 +11183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G40" s="95">
         <f>H33-G39</f>
         <v>0</v>
@@ -11207,12 +11195,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D41" s="46"/>
       <c r="E41" s="46"/>
       <c r="G41" s="66"/>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G42" s="119" t="s">
         <v>60</v>
       </c>
@@ -11223,7 +11211,7 @@
       <c r="I42" s="46"/>
       <c r="J42" s="116"/>
     </row>
-    <row r="43" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G43" s="120" t="s">
         <v>61</v>
       </c>
@@ -11234,7 +11222,7 @@
       <c r="I43" s="46"/>
       <c r="J43" s="116"/>
     </row>
-    <row r="44" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:22" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G44" s="119" t="s">
         <v>62</v>
       </c>
@@ -11245,20 +11233,20 @@
       <c r="I44" s="46"/>
       <c r="J44" s="116"/>
     </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:22" x14ac:dyDescent="0.3">
       <c r="H45" s="95">
         <f>F33-H44</f>
         <v>0</v>
       </c>
       <c r="I45" s="46"/>
     </row>
-    <row r="46" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:22" x14ac:dyDescent="0.3">
       <c r="H46" s="95"/>
       <c r="I46" s="46"/>
     </row>
-    <row r="48" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G48" s="162" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H48" s="162" t="s">
         <v>32</v>
@@ -11270,9 +11258,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G49" s="46" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H49" s="46">
         <f>SUMIF($J$9:$J$29,G49,$F$9:$F$29)</f>
@@ -11287,9 +11275,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G50" s="46" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H50" s="46">
         <f>SUMIF($J$9:$J$29,G50,$F$9:$F$29)</f>
@@ -11304,9 +11292,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="97" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H51" s="97">
         <f>SUMIF($J$9:$J$29,G51,$F$9:$F$29)</f>
@@ -11321,7 +11309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="7:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="H52" s="46">
         <f>SUM(H49:H51)</f>
         <v>0</v>
@@ -11335,7 +11323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
       <c r="H53" s="94">
         <f>H52-H44</f>
         <v>0</v>
@@ -11420,55 +11408,55 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:AB12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" customWidth="1"/>
-    <col min="8" max="8" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" style="8" customWidth="1"/>
-    <col min="22" max="22" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5546875" style="8" customWidth="1"/>
+    <col min="22" max="22" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="F1" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="G1" s="21" t="s">
         <v>276</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>280</v>
       </c>
       <c r="H1" s="21" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AB1" s="39" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
         <v>59</v>
@@ -11480,108 +11468,108 @@
         <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="V2" s="8" t="s">
         <v>59</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H3">
         <f>Overview!C13</f>
         <v>0</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="V3" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB3" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="AB3" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
         <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H4" s="32">
         <f>Overview!C16</f>
         <v>0</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F5" t="s">
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="H5" s="32">
         <f>Overview!C17</f>
@@ -11591,70 +11579,70 @@
         <v>0</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="H6" s="32">
         <f>Overview!C18</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="H7" s="32">
         <f>Overview!C19</f>
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H8" s="32">
         <f>Overview!C20</f>
         <v>0</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H9" s="32">
         <f>Overview!C21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H10" s="32">
         <f>Overview!C22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H11" s="32">
         <f>Overview!C23</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H12" s="32"/>
     </row>
   </sheetData>
@@ -11669,25 +11657,25 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A2:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>150</v>
       </c>
@@ -11695,7 +11683,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>152</v>
       </c>
@@ -11703,7 +11691,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>153</v>
       </c>
@@ -11711,7 +11699,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>155</v>
       </c>
@@ -11719,7 +11707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>156</v>
       </c>
@@ -11727,7 +11715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>157</v>
       </c>
@@ -11735,7 +11723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>158</v>
       </c>
@@ -11743,7 +11731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>159</v>
       </c>
@@ -11751,7 +11739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>160</v>
       </c>
@@ -11759,7 +11747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>161</v>
       </c>
@@ -11778,21 +11766,21 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A2:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
-    <col min="11" max="11" width="3.140625" customWidth="1"/>
-    <col min="12" max="12" width="58.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="11" max="11" width="3.109375" customWidth="1"/>
+    <col min="12" max="12" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
       <c r="C2" s="411" t="s">
         <v>162</v>
       </c>
@@ -11803,7 +11791,7 @@
       <c r="H2" s="401"/>
       <c r="I2" s="217"/>
     </row>
-    <row r="3" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
       <c r="D3" s="217"/>
       <c r="E3" s="217"/>
       <c r="F3" s="217"/>
@@ -11812,7 +11800,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="386" t="s">
         <v>164</v>
       </c>
@@ -11847,10 +11835,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
-        <v>174</v>
-      </c>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29"/>
       <c r="B5" s="36"/>
       <c r="C5" s="218"/>
       <c r="D5" s="36"/>
@@ -11861,13 +11847,11 @@
       <c r="I5" s="220"/>
       <c r="J5" s="219"/>
       <c r="L5" s="319" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>176</v>
-      </c>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29"/>
       <c r="B6" s="36"/>
       <c r="C6" s="218"/>
       <c r="D6" s="36"/>
@@ -11878,13 +11862,11 @@
       <c r="I6" s="220"/>
       <c r="J6" s="219"/>
       <c r="L6" s="319" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>178</v>
-      </c>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29"/>
       <c r="B7" s="36"/>
       <c r="C7" s="218"/>
       <c r="D7" s="36"/>
@@ -11895,13 +11877,11 @@
       <c r="I7" s="220"/>
       <c r="J7" s="219"/>
       <c r="L7" s="319" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>180</v>
-      </c>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
       <c r="B8" s="36"/>
       <c r="C8" s="218"/>
       <c r="D8" s="36"/>
@@ -11912,72 +11892,72 @@
       <c r="I8" s="36"/>
       <c r="J8" s="219"/>
       <c r="L8" s="319" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="319" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="319" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="319" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="319" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L9" s="319" t="s">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="319" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L10" s="319" t="s">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="319" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L11" s="319" t="s">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="319" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L12" s="319" t="s">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="319" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L13" s="319" t="s">
+    <row r="17" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="319" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L14" s="319" t="s">
+    <row r="18" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="319" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L15" s="319" t="s">
+    <row r="19" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="319" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L16" s="319" t="s">
+    <row r="20" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="319" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L17" s="319" t="s">
+    <row r="21" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="319" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="18" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L18" s="319" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L19" s="319" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L20" s="319" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L21" s="319" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -11994,23 +11974,23 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B2:K94"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="5.140625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="30.28515625" customWidth="1"/>
-    <col min="11" max="11" width="21.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="30.33203125" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
       <c r="C2" s="411" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D2" s="401"/>
       <c r="E2" s="401"/>
@@ -12018,77 +11998,77 @@
       <c r="G2" s="401"/>
       <c r="H2" s="401"/>
     </row>
-    <row r="3" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="274" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="274" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="274" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="274" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="274" t="s">
+      <c r="G4" s="274" t="s">
         <v>197</v>
       </c>
-      <c r="D4" s="274" t="s">
+      <c r="H4" s="276" t="s">
         <v>198</v>
       </c>
-      <c r="E4" s="274" t="s">
+      <c r="J4" s="331" t="s">
         <v>199</v>
-      </c>
-      <c r="F4" s="274" t="s">
-        <v>200</v>
-      </c>
-      <c r="G4" s="274" t="s">
-        <v>201</v>
-      </c>
-      <c r="H4" s="276" t="s">
-        <v>202</v>
-      </c>
-      <c r="J4" s="331" t="s">
-        <v>203</v>
       </c>
       <c r="K4" s="332">
         <f>Overview!C9</f>
         <v>46068</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="8">
         <v>1</v>
       </c>
       <c r="C5" s="221" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D5" s="221"/>
       <c r="E5" s="117"/>
       <c r="F5" s="104" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G5" s="104"/>
       <c r="H5" s="36"/>
       <c r="J5" s="333" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K5" s="334">
         <f>K4-120</f>
         <v>45948</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="8">
         <f t="shared" ref="B6:B53" si="0">B5+1</f>
         <v>2</v>
       </c>
       <c r="C6" s="221" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D6" s="221"/>
       <c r="E6" s="117"/>
       <c r="F6" s="104" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G6" s="104"/>
       <c r="H6" s="36"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12100,14 +12080,14 @@
       <c r="G7" s="104"/>
       <c r="H7" s="36"/>
       <c r="J7" s="335" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K7" s="336">
         <f>COUNTIF(F5:F89,"Y")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12119,14 +12099,14 @@
       <c r="G8" s="104"/>
       <c r="H8" s="36"/>
       <c r="J8" s="337" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K8" s="338">
         <f>COUNTA(C5:C90)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -12145,7 +12125,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -12157,7 +12137,7 @@
       <c r="G10" s="104"/>
       <c r="H10" s="36"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -12169,7 +12149,7 @@
       <c r="G11" s="104"/>
       <c r="H11" s="36"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -12181,7 +12161,7 @@
       <c r="G12" s="104"/>
       <c r="H12" s="36"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -12193,7 +12173,7 @@
       <c r="G13" s="104"/>
       <c r="H13" s="36"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -12205,7 +12185,7 @@
       <c r="G14" s="104"/>
       <c r="H14" s="36"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -12217,7 +12197,7 @@
       <c r="G15" s="104"/>
       <c r="H15" s="36"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -12229,7 +12209,7 @@
       <c r="G16" s="104"/>
       <c r="H16" s="36"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -12241,7 +12221,7 @@
       <c r="G17" s="104"/>
       <c r="H17" s="36"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -12253,7 +12233,7 @@
       <c r="G18" s="104"/>
       <c r="H18" s="36"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -12265,7 +12245,7 @@
       <c r="G19" s="104"/>
       <c r="H19" s="36"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -12277,7 +12257,7 @@
       <c r="G20" s="104"/>
       <c r="H20" s="36"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -12289,7 +12269,7 @@
       <c r="G21" s="104"/>
       <c r="H21" s="36"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -12301,7 +12281,7 @@
       <c r="G22" s="104"/>
       <c r="H22" s="36"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -12313,7 +12293,7 @@
       <c r="G23" s="104"/>
       <c r="H23" s="36"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -12325,7 +12305,7 @@
       <c r="G24" s="104"/>
       <c r="H24" s="36"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -12337,7 +12317,7 @@
       <c r="G25" s="104"/>
       <c r="H25" s="36"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -12349,7 +12329,7 @@
       <c r="G26" s="104"/>
       <c r="H26" s="36"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -12361,7 +12341,7 @@
       <c r="G27" s="104"/>
       <c r="H27" s="36"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -12373,7 +12353,7 @@
       <c r="G28" s="104"/>
       <c r="H28" s="36"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -12385,7 +12365,7 @@
       <c r="G29" s="104"/>
       <c r="H29" s="36"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -12397,7 +12377,7 @@
       <c r="G30" s="104"/>
       <c r="H30" s="36"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="8">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -12409,7 +12389,7 @@
       <c r="G31" s="104"/>
       <c r="H31" s="36"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -12421,7 +12401,7 @@
       <c r="G32" s="104"/>
       <c r="H32" s="36"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="8">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -12433,7 +12413,7 @@
       <c r="G33" s="104"/>
       <c r="H33" s="36"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -12445,7 +12425,7 @@
       <c r="G34" s="104"/>
       <c r="H34" s="36"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="8">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -12457,7 +12437,7 @@
       <c r="G35" s="104"/>
       <c r="H35" s="36"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="8">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -12469,7 +12449,7 @@
       <c r="G36" s="104"/>
       <c r="H36" s="36"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="8">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -12481,7 +12461,7 @@
       <c r="G37" s="104"/>
       <c r="H37" s="36"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="8">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -12493,7 +12473,7 @@
       <c r="G38" s="104"/>
       <c r="H38" s="36"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="8">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -12505,7 +12485,7 @@
       <c r="G39" s="104"/>
       <c r="H39" s="36"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="8">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -12517,7 +12497,7 @@
       <c r="G40" s="104"/>
       <c r="H40" s="36"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="8">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -12529,7 +12509,7 @@
       <c r="G41" s="104"/>
       <c r="H41" s="36"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="8">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -12541,7 +12521,7 @@
       <c r="G42" s="104"/>
       <c r="H42" s="36"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="8">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -12553,7 +12533,7 @@
       <c r="G43" s="104"/>
       <c r="H43" s="36"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -12565,7 +12545,7 @@
       <c r="G44" s="104"/>
       <c r="H44" s="36"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="8">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -12577,7 +12557,7 @@
       <c r="G45" s="104"/>
       <c r="H45" s="36"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="8">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -12589,7 +12569,7 @@
       <c r="G46" s="104"/>
       <c r="H46" s="36"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="8">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -12601,7 +12581,7 @@
       <c r="G47" s="104"/>
       <c r="H47" s="36"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="8">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -12613,7 +12593,7 @@
       <c r="G48" s="104"/>
       <c r="H48" s="36"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="8">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -12625,7 +12605,7 @@
       <c r="G49" s="104"/>
       <c r="H49" s="36"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="8">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -12637,7 +12617,7 @@
       <c r="G50" s="104"/>
       <c r="H50" s="36"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="8">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -12649,7 +12629,7 @@
       <c r="G51" s="104"/>
       <c r="H51" s="36"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="8">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -12661,7 +12641,7 @@
       <c r="G52" s="104"/>
       <c r="H52" s="36"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="8">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -12673,54 +12653,54 @@
       <c r="G53" s="104"/>
       <c r="H53" s="36"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="8">
         <v>1</v>
       </c>
       <c r="C54" s="221" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D54" s="221"/>
       <c r="E54" s="117"/>
       <c r="F54" s="104" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G54" s="104"/>
       <c r="H54" s="36"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="8">
         <f t="shared" ref="B55:B79" si="1">B54+1</f>
         <v>2</v>
       </c>
       <c r="C55" s="221" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D55" s="221"/>
       <c r="E55" s="117"/>
       <c r="F55" s="104" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G55" s="104"/>
       <c r="H55" s="36"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="C56" s="159" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D56" s="159"/>
       <c r="E56" s="117"/>
       <c r="F56" s="104" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G56" s="104"/>
       <c r="H56" s="36"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -12732,7 +12712,7 @@
       <c r="G57" s="104"/>
       <c r="H57" s="36"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="8">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -12744,7 +12724,7 @@
       <c r="G58" s="104"/>
       <c r="H58" s="36"/>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -12756,7 +12736,7 @@
       <c r="G59" s="104"/>
       <c r="H59" s="36"/>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -12768,7 +12748,7 @@
       <c r="G60" s="104"/>
       <c r="H60" s="36"/>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="8">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -12780,7 +12760,7 @@
       <c r="G61" s="104"/>
       <c r="H61" s="36"/>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="8">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -12792,7 +12772,7 @@
       <c r="G62" s="104"/>
       <c r="H62" s="36"/>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B63" s="8">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -12804,7 +12784,7 @@
       <c r="G63" s="104"/>
       <c r="H63" s="36"/>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="8">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -12816,7 +12796,7 @@
       <c r="G64" s="104"/>
       <c r="H64" s="36"/>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -12828,7 +12808,7 @@
       <c r="G65" s="104"/>
       <c r="H65" s="36"/>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="8">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -12840,7 +12820,7 @@
       <c r="G66" s="104"/>
       <c r="H66" s="36"/>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="8">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -12852,7 +12832,7 @@
       <c r="G67" s="104"/>
       <c r="H67" s="36"/>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="8">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -12864,7 +12844,7 @@
       <c r="G68" s="104"/>
       <c r="H68" s="36"/>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="8">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -12876,7 +12856,7 @@
       <c r="G69" s="104"/>
       <c r="H69" s="36"/>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="8">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -12888,7 +12868,7 @@
       <c r="G70" s="104"/>
       <c r="H70" s="36"/>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="8">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -12900,7 +12880,7 @@
       <c r="G71" s="104"/>
       <c r="H71" s="36"/>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="8">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -12912,7 +12892,7 @@
       <c r="G72" s="104"/>
       <c r="H72" s="36"/>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="8">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -12924,7 +12904,7 @@
       <c r="G73" s="104"/>
       <c r="H73" s="36"/>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="8">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -12936,7 +12916,7 @@
       <c r="G74" s="104"/>
       <c r="H74" s="36"/>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="8">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -12948,7 +12928,7 @@
       <c r="G75" s="104"/>
       <c r="H75" s="36"/>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="8">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -12960,7 +12940,7 @@
       <c r="G76" s="104"/>
       <c r="H76" s="36"/>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="8">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -12972,7 +12952,7 @@
       <c r="G77" s="104"/>
       <c r="H77" s="36"/>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="8">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -12984,7 +12964,7 @@
       <c r="G78" s="104"/>
       <c r="H78" s="36"/>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="8">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -12996,7 +12976,7 @@
       <c r="G79" s="104"/>
       <c r="H79" s="36"/>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="8">
         <v>27</v>
       </c>
@@ -13007,7 +12987,7 @@
       <c r="G80" s="104"/>
       <c r="H80" s="36"/>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="8">
         <v>28</v>
       </c>
@@ -13018,7 +12998,7 @@
       <c r="G81" s="104"/>
       <c r="H81" s="36"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="8">
         <v>29</v>
       </c>
@@ -13029,7 +13009,7 @@
       <c r="G82" s="104"/>
       <c r="H82" s="36"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="8">
         <v>30</v>
       </c>
@@ -13040,7 +13020,7 @@
       <c r="G83" s="104"/>
       <c r="H83" s="36"/>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="8">
         <v>31</v>
       </c>
@@ -13051,7 +13031,7 @@
       <c r="G84" s="104"/>
       <c r="H84" s="36"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="8">
         <v>32</v>
       </c>
@@ -13062,7 +13042,7 @@
       <c r="G85" s="104"/>
       <c r="H85" s="36"/>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="8">
         <v>33</v>
       </c>
@@ -13073,7 +13053,7 @@
       <c r="G86" s="104"/>
       <c r="H86" s="36"/>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="8">
         <v>34</v>
       </c>
@@ -13084,7 +13064,7 @@
       <c r="G87" s="104"/>
       <c r="H87" s="36"/>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="8">
         <v>35</v>
       </c>
@@ -13095,7 +13075,7 @@
       <c r="G88" s="104"/>
       <c r="H88" s="36"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="8">
         <v>36</v>
       </c>
@@ -13106,7 +13086,7 @@
       <c r="G89" s="104"/>
       <c r="H89" s="36"/>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F94" s="299"/>
       <c r="G94" s="299"/>
     </row>
@@ -13126,60 +13106,60 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BA328"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="101" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="101" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" style="101" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.28515625" style="27" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="27" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" style="27" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" style="42" customWidth="1"/>
-    <col min="15" max="15" width="21.28515625" style="42" customWidth="1"/>
-    <col min="16" max="16" width="20.42578125" style="42" customWidth="1"/>
-    <col min="17" max="17" width="24.7109375" style="42" customWidth="1"/>
-    <col min="18" max="18" width="16.7109375" style="42" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" style="42" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" style="42" customWidth="1"/>
-    <col min="21" max="21" width="9.5703125" style="42" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="42" customWidth="1"/>
-    <col min="23" max="23" width="12.28515625" style="42" customWidth="1"/>
-    <col min="24" max="24" width="21.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="25.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.7109375" style="42" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="42" customWidth="1"/>
-    <col min="29" max="31" width="21.7109375" style="42" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="101" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="101" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.33203125" style="27" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="27" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" style="27" customWidth="1"/>
+    <col min="14" max="14" width="20.6640625" style="42" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" style="42" customWidth="1"/>
+    <col min="16" max="16" width="20.44140625" style="42" customWidth="1"/>
+    <col min="17" max="17" width="24.6640625" style="42" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" style="42" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" style="42" customWidth="1"/>
+    <col min="20" max="20" width="11.109375" style="42" customWidth="1"/>
+    <col min="21" max="21" width="9.5546875" style="42" customWidth="1"/>
+    <col min="22" max="22" width="14.109375" style="42" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" style="42" customWidth="1"/>
+    <col min="24" max="24" width="21.33203125" style="42" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.6640625" style="42" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.33203125" style="42" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.6640625" style="42" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.44140625" style="42" customWidth="1"/>
+    <col min="29" max="31" width="21.6640625" style="42" customWidth="1"/>
     <col min="32" max="32" width="18" style="42" customWidth="1"/>
-    <col min="33" max="33" width="20.42578125" customWidth="1"/>
-    <col min="34" max="34" width="18.42578125" style="8" customWidth="1"/>
-    <col min="35" max="35" width="13.140625" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" customWidth="1"/>
-    <col min="37" max="37" width="21.140625" style="8" customWidth="1"/>
-    <col min="38" max="38" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="9.7109375" customWidth="1"/>
+    <col min="33" max="33" width="20.44140625" customWidth="1"/>
+    <col min="34" max="34" width="18.44140625" style="8" customWidth="1"/>
+    <col min="35" max="35" width="13.109375" customWidth="1"/>
+    <col min="36" max="36" width="12.33203125" customWidth="1"/>
+    <col min="37" max="37" width="21.109375" style="8" customWidth="1"/>
+    <col min="38" max="38" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.6640625" customWidth="1"/>
     <col min="40" max="40" width="8" customWidth="1"/>
-    <col min="41" max="41" width="67.7109375" customWidth="1"/>
-    <col min="42" max="42" width="4.5703125" customWidth="1"/>
-    <col min="43" max="44" width="20.85546875" style="343" customWidth="1"/>
-    <col min="45" max="45" width="9.140625" style="343" customWidth="1"/>
-    <col min="46" max="46" width="12.28515625" style="343" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.140625" style="342" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.42578125" style="342" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.5703125" style="342" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="342" customWidth="1"/>
-    <col min="51" max="51" width="14.28515625" style="342" customWidth="1"/>
-    <col min="52" max="53" width="9.140625" style="342" customWidth="1"/>
+    <col min="41" max="41" width="67.6640625" customWidth="1"/>
+    <col min="42" max="42" width="4.5546875" customWidth="1"/>
+    <col min="43" max="44" width="20.88671875" style="343" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" style="343" customWidth="1"/>
+    <col min="46" max="46" width="12.33203125" style="343" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.109375" style="342" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.44140625" style="342" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.5546875" style="342" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.109375" style="342" customWidth="1"/>
+    <col min="51" max="51" width="14.33203125" style="342" customWidth="1"/>
+    <col min="52" max="53" width="9.109375" style="342" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="397"/>
       <c r="C1" s="398"/>
       <c r="D1" s="398"/>
@@ -13226,7 +13206,7 @@
       <c r="AS1" s="342"/>
       <c r="AT1" s="342"/>
     </row>
-    <row r="2" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -13268,7 +13248,7 @@
       <c r="AS2" s="342"/>
       <c r="AT2" s="342"/>
     </row>
-    <row r="3" spans="1:53" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:53" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -13297,7 +13277,7 @@
       <c r="AS3" s="342"/>
       <c r="AT3" s="342"/>
     </row>
-    <row r="4" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -13333,7 +13313,7 @@
       <c r="AS4" s="342"/>
       <c r="AT4" s="342"/>
     </row>
-    <row r="5" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
@@ -13372,7 +13352,7 @@
       <c r="AS5" s="342"/>
       <c r="AT5" s="342"/>
     </row>
-    <row r="6" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -13405,7 +13385,7 @@
       <c r="AS6" s="342"/>
       <c r="AT6" s="342"/>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="H7" s="27" t="s">
         <v>4</v>
       </c>
@@ -13430,7 +13410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:53" s="7" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" s="7" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="271" t="s">
         <v>7</v>
       </c>
@@ -13573,7 +13553,7 @@
       <c r="AZ8" s="352"/>
       <c r="BA8" s="352"/>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" s="42"/>
       <c r="B9" s="11">
         <v>1</v>
@@ -13658,7 +13638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>2</v>
       </c>
@@ -13741,7 +13721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" s="42"/>
       <c r="B11" s="11">
         <v>3</v>
@@ -13826,7 +13806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" s="42"/>
       <c r="B12" s="11">
         <v>4</v>
@@ -13911,7 +13891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" s="42"/>
       <c r="B13" s="11">
         <v>5</v>
@@ -13996,7 +13976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" s="42"/>
       <c r="B14" s="11">
         <v>6</v>
@@ -14080,7 +14060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>7</v>
       </c>
@@ -14163,7 +14143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" s="42"/>
       <c r="B16" s="11">
         <v>8</v>
@@ -14248,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>9</v>
       </c>
@@ -14331,7 +14311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>10</v>
       </c>
@@ -14414,7 +14394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A19" s="42"/>
       <c r="B19" s="11">
         <v>11</v>
@@ -14499,7 +14479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A20" s="42"/>
       <c r="B20" s="11">
         <v>12</v>
@@ -14584,7 +14564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A21" s="42"/>
       <c r="B21" s="11">
         <v>13</v>
@@ -14669,7 +14649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A22" s="42"/>
       <c r="B22" s="11">
         <v>14</v>
@@ -14753,7 +14733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A23" s="42"/>
       <c r="B23" s="11">
         <v>15</v>
@@ -14838,7 +14818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>16</v>
       </c>
@@ -14921,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>17</v>
       </c>
@@ -15004,7 +14984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="11">
         <v>18</v>
@@ -15089,7 +15069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="11">
         <v>19</v>
@@ -15174,7 +15154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A28" s="42"/>
       <c r="B28" s="11">
         <v>20</v>
@@ -15259,7 +15239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A29" s="42"/>
       <c r="B29" s="11">
         <v>21</v>
@@ -15344,7 +15324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
       <c r="B30" s="11">
         <v>22</v>
@@ -15428,7 +15408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A31" s="42"/>
       <c r="B31" s="11">
         <v>23</v>
@@ -15513,7 +15493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A32" s="42"/>
       <c r="B32" s="11">
         <v>24</v>
@@ -15598,7 +15578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A33" s="42"/>
       <c r="B33" s="11">
         <v>25</v>
@@ -15683,7 +15663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A34" s="42"/>
       <c r="B34" s="11">
         <v>26</v>
@@ -15768,7 +15748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <v>27</v>
       </c>
@@ -15851,7 +15831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <v>28</v>
       </c>
@@ -15934,7 +15914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A37" s="42"/>
       <c r="B37" s="11">
         <v>29</v>
@@ -16019,7 +15999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A38" s="42"/>
       <c r="B38" s="11">
         <v>30</v>
@@ -16104,7 +16084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" s="11">
         <v>31</v>
@@ -16189,7 +16169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A40" s="42"/>
       <c r="B40" s="11">
         <v>32</v>
@@ -16274,7 +16254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A41" s="42"/>
       <c r="B41" s="11">
         <v>33</v>
@@ -16358,7 +16338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A42" s="42"/>
       <c r="B42" s="11">
         <v>34</v>
@@ -16443,7 +16423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A43" s="42"/>
       <c r="B43" s="11">
         <v>35</v>
@@ -16528,7 +16508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A44" s="42"/>
       <c r="B44" s="11">
         <v>36</v>
@@ -16613,7 +16593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A45" s="42"/>
       <c r="B45" s="11">
         <v>37</v>
@@ -16697,7 +16677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B46" s="11">
         <v>38</v>
       </c>
@@ -16780,7 +16760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B47" s="11">
         <v>39</v>
       </c>
@@ -16863,7 +16843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A48" s="42"/>
       <c r="B48" s="11">
         <v>40</v>
@@ -16948,7 +16928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A49" s="42"/>
       <c r="B49" s="11">
         <v>41</v>
@@ -17033,7 +17013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A50" s="42"/>
       <c r="B50" s="11">
         <v>42</v>
@@ -17118,7 +17098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A51" s="42"/>
       <c r="B51" s="11">
         <v>43</v>
@@ -17203,7 +17183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A52" s="42"/>
       <c r="B52" s="11">
         <v>44</v>
@@ -17288,7 +17268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A53" s="42"/>
       <c r="B53" s="11">
         <v>45</v>
@@ -17373,7 +17353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A54" s="42"/>
       <c r="B54" s="11">
         <v>46</v>
@@ -17458,7 +17438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B55" s="43"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43"/>
@@ -17568,7 +17548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.3">
       <c r="H56" s="47"/>
       <c r="I56" s="154"/>
       <c r="J56" s="28"/>
@@ -17605,7 +17585,7 @@
       <c r="AS56" s="342"/>
       <c r="AY56" s="357"/>
     </row>
-    <row r="57" spans="1:52" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:52" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I57" s="154"/>
       <c r="AF57" s="139"/>
       <c r="AN57" s="8"/>
@@ -17626,7 +17606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:52" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:52" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="50"/>
       <c r="I58" s="154"/>
       <c r="N58" s="100">
@@ -17698,7 +17678,7 @@
       <c r="AF58" s="137"/>
       <c r="AY58" s="357"/>
     </row>
-    <row r="59" spans="1:52" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:52" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F59" s="264" t="s">
         <v>52</v>
       </c>
@@ -17713,7 +17693,7 @@
       </c>
       <c r="AY59" s="357"/>
     </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
       <c r="G60" s="223">
         <f>SUMIF($E$9:$E$54,$F60,$AA$9:$AA$54)</f>
         <v>0</v>
@@ -17728,7 +17708,7 @@
       </c>
       <c r="AY60" s="357"/>
     </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:52" x14ac:dyDescent="0.3">
       <c r="G61" s="223">
         <f>SUMIF($E$9:$E$54,$F61,$AA$9:$AA$54)</f>
         <v>0</v>
@@ -17743,7 +17723,7 @@
       </c>
       <c r="AY61" s="357"/>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.3">
       <c r="G62" s="223">
         <f>SUMIF($E$9:$E$54,$F62,$AA$9:$AA$54)</f>
         <v>0</v>
@@ -17785,7 +17765,7 @@
       <c r="AG62" s="8"/>
       <c r="AY62" s="357"/>
     </row>
-    <row r="63" spans="1:52" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:52" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F63" s="197"/>
       <c r="G63" s="267">
         <f>SUMIF($E$9:$E$54,$F63,$AA$9:$AA$54)</f>
@@ -17836,7 +17816,7 @@
       <c r="AG63" s="8"/>
       <c r="AY63" s="357"/>
     </row>
-    <row r="64" spans="1:52" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:52" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F64" s="8" t="s">
         <v>32</v>
       </c>
@@ -17901,7 +17881,7 @@
       </c>
       <c r="AY64" s="357"/>
     </row>
-    <row r="65" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:51" x14ac:dyDescent="0.3">
       <c r="F65" s="8"/>
       <c r="G65" s="224">
         <f>G64-AA58</f>
@@ -17944,7 +17924,7 @@
       </c>
       <c r="AY65" s="357"/>
     </row>
-    <row r="66" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:51" x14ac:dyDescent="0.3">
       <c r="F66" s="8"/>
       <c r="I66" s="154"/>
       <c r="W66" s="46"/>
@@ -17957,7 +17937,7 @@
       <c r="AE66" s="8"/>
       <c r="AY66" s="357"/>
     </row>
-    <row r="67" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I67" s="154"/>
       <c r="W67" s="8"/>
       <c r="X67" s="27"/>
@@ -17976,7 +17956,7 @@
       <c r="AF67" s="46"/>
       <c r="AY67" s="357"/>
     </row>
-    <row r="68" spans="6:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="6:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I68" s="154"/>
       <c r="W68" s="8"/>
       <c r="X68" s="27"/>
@@ -17995,7 +17975,7 @@
       <c r="AF68" s="46"/>
       <c r="AY68" s="357"/>
     </row>
-    <row r="69" spans="6:51" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:51" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="I69" s="154"/>
       <c r="W69" s="8"/>
       <c r="X69" s="27"/>
@@ -18015,7 +17995,7 @@
       <c r="AH69" s="116"/>
       <c r="AY69" s="357"/>
     </row>
-    <row r="70" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I70" s="154"/>
       <c r="W70" s="8"/>
       <c r="X70" s="27"/>
@@ -18033,786 +18013,786 @@
       <c r="AH70" s="116"/>
       <c r="AY70" s="357"/>
     </row>
-    <row r="71" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I71" s="154"/>
       <c r="AY71" s="357"/>
     </row>
-    <row r="72" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I72" s="154"/>
       <c r="AY72" s="357"/>
     </row>
-    <row r="73" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I73" s="28"/>
       <c r="AY73" s="357"/>
     </row>
-    <row r="74" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I74" s="28"/>
       <c r="AY74" s="357"/>
     </row>
-    <row r="75" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:51" x14ac:dyDescent="0.3">
       <c r="AY75" s="357"/>
     </row>
-    <row r="76" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:51" x14ac:dyDescent="0.3">
       <c r="AY76" s="357"/>
     </row>
-    <row r="77" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:51" x14ac:dyDescent="0.3">
       <c r="AY77" s="357"/>
     </row>
-    <row r="78" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:51" x14ac:dyDescent="0.3">
       <c r="AY78" s="357"/>
     </row>
-    <row r="79" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:51" x14ac:dyDescent="0.3">
       <c r="AY79" s="357"/>
     </row>
-    <row r="80" spans="6:51" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:51" x14ac:dyDescent="0.3">
       <c r="I80" s="41"/>
       <c r="AY80" s="357"/>
     </row>
-    <row r="81" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="81" spans="9:51" x14ac:dyDescent="0.3">
       <c r="I81" s="41"/>
       <c r="AY81" s="357"/>
     </row>
-    <row r="82" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="82" spans="9:51" x14ac:dyDescent="0.3">
       <c r="I82" s="41"/>
       <c r="AY82" s="357"/>
     </row>
-    <row r="83" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="83" spans="9:51" x14ac:dyDescent="0.3">
       <c r="I83" s="41"/>
       <c r="AY83" s="357"/>
     </row>
-    <row r="84" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="84" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY84" s="357"/>
     </row>
-    <row r="85" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="85" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY85" s="357"/>
     </row>
-    <row r="86" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="86" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY86" s="357"/>
     </row>
-    <row r="87" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="87" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY87" s="357"/>
     </row>
-    <row r="88" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="88" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY88" s="357"/>
     </row>
-    <row r="89" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="89" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY89" s="357"/>
     </row>
-    <row r="90" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="90" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY90" s="357"/>
     </row>
-    <row r="91" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="91" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY91" s="357"/>
     </row>
-    <row r="92" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="92" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY92" s="357"/>
     </row>
-    <row r="93" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="93" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY93" s="357"/>
     </row>
-    <row r="94" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="94" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY94" s="357"/>
     </row>
-    <row r="95" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="95" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY95" s="357"/>
     </row>
-    <row r="96" spans="9:51" x14ac:dyDescent="0.25">
+    <row r="96" spans="9:51" x14ac:dyDescent="0.3">
       <c r="AY96" s="357"/>
     </row>
-    <row r="97" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="97" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY97" s="357"/>
     </row>
-    <row r="98" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="98" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY98" s="357"/>
     </row>
-    <row r="99" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="99" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY99" s="357"/>
     </row>
-    <row r="100" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="100" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY100" s="357"/>
     </row>
-    <row r="101" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="101" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY101" s="357"/>
     </row>
-    <row r="102" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="102" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY102" s="357"/>
     </row>
-    <row r="103" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="103" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY103" s="357"/>
     </row>
-    <row r="104" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="104" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY104" s="357"/>
     </row>
-    <row r="105" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="105" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY105" s="357"/>
     </row>
-    <row r="106" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="106" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY106" s="357"/>
     </row>
-    <row r="107" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="107" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY107" s="357"/>
     </row>
-    <row r="108" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="108" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY108" s="357"/>
     </row>
-    <row r="109" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="109" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY109" s="357"/>
     </row>
-    <row r="110" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="110" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY110" s="357"/>
     </row>
-    <row r="111" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="111" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY111" s="357"/>
     </row>
-    <row r="112" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="112" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY112" s="357"/>
     </row>
-    <row r="113" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="113" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY113" s="357"/>
     </row>
-    <row r="114" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="114" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY114" s="357"/>
     </row>
-    <row r="115" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="115" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY115" s="357"/>
     </row>
-    <row r="116" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="116" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY116" s="357"/>
     </row>
-    <row r="117" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="117" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY117" s="357"/>
     </row>
-    <row r="118" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="118" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY118" s="357"/>
     </row>
-    <row r="119" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="119" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY119" s="357"/>
     </row>
-    <row r="120" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="120" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY120" s="357"/>
     </row>
-    <row r="121" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="121" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY121" s="357"/>
     </row>
-    <row r="122" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="122" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY122" s="357"/>
     </row>
-    <row r="123" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="123" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY123" s="357"/>
     </row>
-    <row r="124" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="124" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY124" s="357"/>
     </row>
-    <row r="125" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="125" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY125" s="357"/>
     </row>
-    <row r="126" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="126" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY126" s="357"/>
     </row>
-    <row r="127" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="127" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY127" s="357"/>
     </row>
-    <row r="128" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="128" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY128" s="357"/>
     </row>
-    <row r="129" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="129" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY129" s="357"/>
     </row>
-    <row r="130" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="130" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY130" s="357"/>
     </row>
-    <row r="131" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="131" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY131" s="357"/>
     </row>
-    <row r="132" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="132" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY132" s="357"/>
     </row>
-    <row r="133" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="133" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY133" s="357"/>
     </row>
-    <row r="134" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="134" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY134" s="357"/>
     </row>
-    <row r="135" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="135" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY135" s="357"/>
     </row>
-    <row r="136" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="136" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY136" s="357"/>
     </row>
-    <row r="137" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="137" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY137" s="357"/>
     </row>
-    <row r="138" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="138" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY138" s="357"/>
     </row>
-    <row r="139" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="139" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY139" s="357"/>
     </row>
-    <row r="140" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="140" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY140" s="357"/>
     </row>
-    <row r="141" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="141" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY141" s="357"/>
     </row>
-    <row r="142" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="142" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY142" s="357"/>
     </row>
-    <row r="143" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="143" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY143" s="357"/>
     </row>
-    <row r="144" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="144" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY144" s="357"/>
     </row>
-    <row r="145" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="145" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY145" s="357"/>
     </row>
-    <row r="146" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="146" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY146" s="357"/>
     </row>
-    <row r="147" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="147" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY147" s="357"/>
     </row>
-    <row r="148" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="148" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY148" s="357"/>
     </row>
-    <row r="149" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="149" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY149" s="357"/>
     </row>
-    <row r="150" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="150" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY150" s="357"/>
     </row>
-    <row r="151" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="151" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY151" s="357"/>
     </row>
-    <row r="152" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="152" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY152" s="357"/>
     </row>
-    <row r="153" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="153" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY153" s="357"/>
     </row>
-    <row r="154" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="154" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY154" s="357"/>
     </row>
-    <row r="155" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="155" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY155" s="357"/>
     </row>
-    <row r="156" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="156" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY156" s="357"/>
     </row>
-    <row r="157" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="157" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY157" s="357"/>
     </row>
-    <row r="158" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="158" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY158" s="357"/>
     </row>
-    <row r="159" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="159" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY159" s="357"/>
     </row>
-    <row r="160" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="160" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY160" s="357"/>
     </row>
-    <row r="161" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="161" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY161" s="357"/>
     </row>
-    <row r="162" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="162" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY162" s="357"/>
     </row>
-    <row r="163" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="163" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY163" s="357"/>
     </row>
-    <row r="164" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="164" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY164" s="357"/>
     </row>
-    <row r="165" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="165" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY165" s="357"/>
     </row>
-    <row r="166" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="166" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY166" s="357"/>
     </row>
-    <row r="167" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="167" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY167" s="357"/>
     </row>
-    <row r="168" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="168" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY168" s="357"/>
     </row>
-    <row r="169" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="169" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY169" s="357"/>
     </row>
-    <row r="170" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="170" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY170" s="357"/>
     </row>
-    <row r="171" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="171" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY171" s="357"/>
     </row>
-    <row r="172" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="172" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY172" s="357"/>
     </row>
-    <row r="173" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="173" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY173" s="357"/>
     </row>
-    <row r="174" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="174" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY174" s="357"/>
     </row>
-    <row r="175" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="175" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY175" s="357"/>
     </row>
-    <row r="176" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="176" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY176" s="357"/>
     </row>
-    <row r="177" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="177" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY177" s="357"/>
     </row>
-    <row r="178" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="178" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY178" s="357"/>
     </row>
-    <row r="179" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="179" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY179" s="357"/>
     </row>
-    <row r="180" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="180" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY180" s="357"/>
     </row>
-    <row r="181" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="181" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY181" s="357"/>
     </row>
-    <row r="182" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="182" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY182" s="357"/>
     </row>
-    <row r="183" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="183" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY183" s="357"/>
     </row>
-    <row r="184" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="184" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY184" s="357"/>
     </row>
-    <row r="185" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="185" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY185" s="357"/>
     </row>
-    <row r="186" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="186" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY186" s="357"/>
     </row>
-    <row r="187" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="187" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY187" s="357"/>
     </row>
-    <row r="188" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="188" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY188" s="357"/>
     </row>
-    <row r="189" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="189" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY189" s="357"/>
     </row>
-    <row r="190" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="190" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY190" s="357"/>
     </row>
-    <row r="191" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="191" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY191" s="357"/>
     </row>
-    <row r="192" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="192" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY192" s="357"/>
     </row>
-    <row r="193" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="193" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY193" s="357"/>
     </row>
-    <row r="194" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="194" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY194" s="357"/>
     </row>
-    <row r="195" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="195" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY195" s="357"/>
     </row>
-    <row r="196" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="196" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY196" s="357"/>
     </row>
-    <row r="197" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="197" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY197" s="357"/>
     </row>
-    <row r="198" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="198" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY198" s="357"/>
     </row>
-    <row r="199" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="199" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY199" s="357"/>
     </row>
-    <row r="200" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="200" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY200" s="357"/>
     </row>
-    <row r="201" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="201" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY201" s="357"/>
     </row>
-    <row r="202" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="202" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY202" s="357"/>
     </row>
-    <row r="203" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="203" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY203" s="357"/>
     </row>
-    <row r="204" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="204" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY204" s="357"/>
     </row>
-    <row r="205" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="205" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY205" s="357"/>
     </row>
-    <row r="206" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="206" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY206" s="357"/>
     </row>
-    <row r="207" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="207" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY207" s="357"/>
     </row>
-    <row r="208" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="208" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY208" s="357"/>
     </row>
-    <row r="209" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="209" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY209" s="357"/>
     </row>
-    <row r="210" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="210" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY210" s="357"/>
     </row>
-    <row r="211" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="211" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY211" s="357"/>
     </row>
-    <row r="212" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="212" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY212" s="357"/>
     </row>
-    <row r="213" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="213" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY213" s="357"/>
     </row>
-    <row r="214" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="214" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY214" s="357"/>
     </row>
-    <row r="215" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="215" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY215" s="357"/>
     </row>
-    <row r="216" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="216" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY216" s="357"/>
     </row>
-    <row r="217" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="217" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY217" s="357"/>
     </row>
-    <row r="218" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="218" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY218" s="357"/>
     </row>
-    <row r="219" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="219" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY219" s="357"/>
     </row>
-    <row r="220" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="220" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY220" s="357"/>
     </row>
-    <row r="221" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="221" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY221" s="357"/>
     </row>
-    <row r="222" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="222" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY222" s="357"/>
     </row>
-    <row r="223" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="223" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY223" s="357"/>
     </row>
-    <row r="224" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="224" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY224" s="357"/>
     </row>
-    <row r="225" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="225" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY225" s="357"/>
     </row>
-    <row r="226" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="226" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY226" s="357"/>
     </row>
-    <row r="227" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="227" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY227" s="357"/>
     </row>
-    <row r="228" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="228" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY228" s="357"/>
     </row>
-    <row r="229" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="229" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY229" s="357"/>
     </row>
-    <row r="230" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="230" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY230" s="357"/>
     </row>
-    <row r="231" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="231" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY231" s="357"/>
     </row>
-    <row r="232" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="232" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY232" s="357"/>
     </row>
-    <row r="233" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="233" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY233" s="357"/>
     </row>
-    <row r="234" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="234" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY234" s="357"/>
     </row>
-    <row r="235" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="235" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY235" s="357"/>
     </row>
-    <row r="236" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="236" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY236" s="357"/>
     </row>
-    <row r="237" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="237" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY237" s="357"/>
     </row>
-    <row r="238" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="238" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY238" s="357"/>
     </row>
-    <row r="239" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="239" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY239" s="357"/>
     </row>
-    <row r="240" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="240" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY240" s="357"/>
     </row>
-    <row r="241" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="241" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY241" s="357"/>
     </row>
-    <row r="242" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="242" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY242" s="357"/>
     </row>
-    <row r="243" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="243" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY243" s="357"/>
     </row>
-    <row r="244" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="244" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY244" s="357"/>
     </row>
-    <row r="245" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="245" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY245" s="357"/>
     </row>
-    <row r="246" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="246" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY246" s="357"/>
     </row>
-    <row r="247" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="247" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY247" s="357"/>
     </row>
-    <row r="248" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="248" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY248" s="357"/>
     </row>
-    <row r="249" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="249" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY249" s="357"/>
     </row>
-    <row r="250" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="250" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY250" s="357"/>
     </row>
-    <row r="251" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="251" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY251" s="357"/>
     </row>
-    <row r="252" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="252" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY252" s="357"/>
     </row>
-    <row r="253" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="253" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY253" s="357"/>
     </row>
-    <row r="254" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="254" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY254" s="357"/>
     </row>
-    <row r="255" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="255" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY255" s="357"/>
     </row>
-    <row r="256" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="256" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY256" s="357"/>
     </row>
-    <row r="257" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="257" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY257" s="357"/>
     </row>
-    <row r="258" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="258" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY258" s="357"/>
     </row>
-    <row r="259" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="259" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY259" s="357"/>
     </row>
-    <row r="260" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="260" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY260" s="357"/>
     </row>
-    <row r="261" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="261" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY261" s="357"/>
     </row>
-    <row r="262" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="262" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY262" s="357"/>
     </row>
-    <row r="263" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="263" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY263" s="357"/>
     </row>
-    <row r="264" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="264" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY264" s="357"/>
     </row>
-    <row r="265" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="265" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY265" s="357"/>
     </row>
-    <row r="266" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="266" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY266" s="357"/>
     </row>
-    <row r="267" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="267" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY267" s="357"/>
     </row>
-    <row r="268" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="268" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY268" s="357"/>
     </row>
-    <row r="269" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="269" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY269" s="357"/>
     </row>
-    <row r="270" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="270" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY270" s="357"/>
     </row>
-    <row r="271" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="271" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY271" s="357"/>
     </row>
-    <row r="272" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="272" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY272" s="357"/>
     </row>
-    <row r="273" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="273" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY273" s="357"/>
     </row>
-    <row r="274" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="274" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY274" s="357"/>
     </row>
-    <row r="275" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="275" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY275" s="357"/>
     </row>
-    <row r="276" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="276" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY276" s="357"/>
     </row>
-    <row r="277" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="277" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY277" s="357"/>
     </row>
-    <row r="278" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="278" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY278" s="357"/>
     </row>
-    <row r="279" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="279" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY279" s="357"/>
     </row>
-    <row r="280" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="280" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY280" s="357"/>
     </row>
-    <row r="281" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="281" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY281" s="357"/>
     </row>
-    <row r="282" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="282" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY282" s="357"/>
     </row>
-    <row r="283" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="283" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY283" s="357"/>
     </row>
-    <row r="284" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="284" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY284" s="357"/>
     </row>
-    <row r="285" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="285" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY285" s="357"/>
     </row>
-    <row r="286" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="286" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY286" s="357"/>
     </row>
-    <row r="287" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="287" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY287" s="357"/>
     </row>
-    <row r="288" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="288" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY288" s="357"/>
     </row>
-    <row r="289" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="289" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY289" s="357"/>
     </row>
-    <row r="290" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="290" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY290" s="357"/>
     </row>
-    <row r="291" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="291" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY291" s="357"/>
     </row>
-    <row r="292" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="292" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY292" s="357"/>
     </row>
-    <row r="293" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="293" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY293" s="357"/>
     </row>
-    <row r="294" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="294" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY294" s="357"/>
     </row>
-    <row r="295" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="295" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY295" s="357"/>
     </row>
-    <row r="296" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="296" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY296" s="357"/>
     </row>
-    <row r="297" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="297" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY297" s="357"/>
     </row>
-    <row r="298" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="298" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY298" s="357"/>
     </row>
-    <row r="299" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="299" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY299" s="357"/>
     </row>
-    <row r="300" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="300" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY300" s="357"/>
     </row>
-    <row r="301" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="301" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY301" s="357"/>
     </row>
-    <row r="302" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="302" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY302" s="357"/>
     </row>
-    <row r="303" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="303" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY303" s="357"/>
     </row>
-    <row r="304" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="304" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY304" s="357"/>
     </row>
-    <row r="305" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="305" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY305" s="357"/>
     </row>
-    <row r="306" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="306" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY306" s="357"/>
     </row>
-    <row r="307" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="307" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY307" s="357"/>
     </row>
-    <row r="308" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="308" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY308" s="357"/>
     </row>
-    <row r="309" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="309" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY309" s="357"/>
     </row>
-    <row r="310" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="310" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY310" s="357"/>
     </row>
-    <row r="311" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="311" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY311" s="357"/>
     </row>
-    <row r="312" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="312" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY312" s="357"/>
     </row>
-    <row r="313" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="313" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY313" s="357"/>
     </row>
-    <row r="314" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="314" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY314" s="357"/>
     </row>
-    <row r="315" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="315" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY315" s="357"/>
     </row>
-    <row r="316" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="316" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY316" s="357"/>
     </row>
-    <row r="317" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="317" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY317" s="357"/>
     </row>
-    <row r="318" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="318" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY318" s="357"/>
     </row>
-    <row r="319" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="319" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY319" s="357"/>
     </row>
-    <row r="320" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="320" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY320" s="357"/>
     </row>
-    <row r="321" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="321" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY321" s="357"/>
     </row>
-    <row r="322" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="322" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY322" s="357"/>
     </row>
-    <row r="323" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="323" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY323" s="357"/>
     </row>
-    <row r="324" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="324" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY324" s="357"/>
     </row>
-    <row r="325" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="325" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY325" s="357"/>
     </row>
-    <row r="326" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="326" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY326" s="357"/>
     </row>
-    <row r="327" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="327" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY327" s="361"/>
     </row>
-    <row r="328" spans="51:51" x14ac:dyDescent="0.25">
+    <row r="328" spans="51:51" x14ac:dyDescent="0.3">
       <c r="AY328" s="362"/>
     </row>
   </sheetData>
@@ -19048,37 +19028,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="107" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="107" customWidth="1"/>
     <col min="4" max="4" width="22" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="27" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="20.140625" style="46" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="46" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="46" customWidth="1"/>
+    <col min="7" max="10" width="20.109375" style="46" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="46" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" style="46" customWidth="1"/>
     <col min="13" max="14" width="31" style="66" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" style="116" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="8" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="8" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" style="8" customWidth="1"/>
-    <col min="19" max="19" width="19.140625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="13.85546875" style="32" customWidth="1"/>
-    <col min="21" max="21" width="30.7109375" style="32" customWidth="1"/>
-    <col min="22" max="22" width="28.28515625" style="8" customWidth="1"/>
-    <col min="23" max="23" width="18.140625" style="8" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="8" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" style="8" customWidth="1"/>
-    <col min="26" max="26" width="19.28515625" style="32" customWidth="1"/>
-    <col min="27" max="27" width="15.5703125" customWidth="1"/>
+    <col min="15" max="15" width="17.44140625" style="116" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="8" customWidth="1"/>
+    <col min="18" max="18" width="19.5546875" style="8" customWidth="1"/>
+    <col min="19" max="19" width="19.109375" style="8" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" style="32" customWidth="1"/>
+    <col min="21" max="21" width="30.6640625" style="32" customWidth="1"/>
+    <col min="22" max="22" width="28.33203125" style="8" customWidth="1"/>
+    <col min="23" max="23" width="18.109375" style="8" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" style="8" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" style="8" customWidth="1"/>
+    <col min="26" max="26" width="19.33203125" style="32" customWidth="1"/>
+    <col min="27" max="27" width="15.5546875" customWidth="1"/>
     <col min="28" max="28" width="55" style="32" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="24.7109375" style="8" customWidth="1"/>
+    <col min="30" max="30" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="24.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="397"/>
       <c r="C1" s="413"/>
       <c r="D1" s="396"/>
@@ -19110,7 +19090,7 @@
       <c r="AD1" s="113"/>
       <c r="AE1" s="113"/>
     </row>
-    <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -19142,7 +19122,7 @@
       <c r="AD2" s="113"/>
       <c r="AE2" s="113"/>
     </row>
-    <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="113"/>
       <c r="E3" s="25"/>
@@ -19155,7 +19135,7 @@
       <c r="Z3" s="8"/>
       <c r="AA3" s="32"/>
     </row>
-    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="D4" s="113"/>
       <c r="E4" s="25"/>
@@ -19176,7 +19156,7 @@
       <c r="AD4" s="112"/>
       <c r="AE4" s="112"/>
     </row>
-    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
       <c r="E5" s="4"/>
@@ -19197,7 +19177,7 @@
       <c r="AD5" s="112"/>
       <c r="AE5" s="112"/>
     </row>
-    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C6" s="9"/>
       <c r="D6" s="15"/>
       <c r="E6" s="4"/>
@@ -19218,11 +19198,11 @@
       <c r="AD6" s="112"/>
       <c r="AE6" s="112"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="C7" s="101"/>
       <c r="D7" s="101"/>
       <c r="F7" s="27" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K7" s="119"/>
       <c r="P7" s="119"/>
@@ -19241,33 +19221,33 @@
       <c r="AD7" s="119"/>
       <c r="AE7" s="119"/>
     </row>
-    <row r="8" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B8" s="285" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="277" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D8" s="284" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="287" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="279" t="s">
+        <v>214</v>
+      </c>
+      <c r="G8" s="288" t="s">
+        <v>215</v>
+      </c>
+      <c r="H8" s="288" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="288" t="s">
         <v>217</v>
-      </c>
-      <c r="F8" s="279" t="s">
-        <v>218</v>
-      </c>
-      <c r="G8" s="288" t="s">
-        <v>219</v>
-      </c>
-      <c r="H8" s="288" t="s">
-        <v>220</v>
-      </c>
-      <c r="I8" s="288" t="s">
-        <v>221</v>
       </c>
       <c r="J8" s="288" t="s">
         <v>103</v>
@@ -19276,7 +19256,7 @@
         <v>61</v>
       </c>
       <c r="L8" s="288" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M8" s="290" t="s">
         <v>14</v>
@@ -19288,25 +19268,25 @@
         <v>16</v>
       </c>
       <c r="P8" s="315" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q8" s="315" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="R8" s="315" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="S8" s="315" t="s">
         <v>39</v>
       </c>
       <c r="T8" s="315" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="U8" s="315" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="V8" s="315" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="W8" s="315" t="s">
         <v>168</v>
@@ -19318,7 +19298,7 @@
         <v>45</v>
       </c>
       <c r="Z8" s="315" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AA8" s="315" t="s">
         <v>41</v>
@@ -19333,7 +19313,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>1</v>
       </c>
@@ -19379,7 +19359,7 @@
       <c r="AD9" s="146"/>
       <c r="AE9" s="29"/>
     </row>
-    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>2</v>
       </c>
@@ -19425,7 +19405,7 @@
       <c r="AD10" s="146"/>
       <c r="AE10" s="29"/>
     </row>
-    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>3</v>
       </c>
@@ -19471,7 +19451,7 @@
       <c r="AD11" s="146"/>
       <c r="AE11" s="29"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>4</v>
       </c>
@@ -19517,7 +19497,7 @@
       <c r="AD12" s="146"/>
       <c r="AE12" s="29"/>
     </row>
-    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>5</v>
       </c>
@@ -19563,7 +19543,7 @@
       <c r="AD13" s="146"/>
       <c r="AE13" s="29"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>6</v>
       </c>
@@ -19608,7 +19588,7 @@
       <c r="AD14" s="146"/>
       <c r="AE14" s="29"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>7</v>
       </c>
@@ -19654,7 +19634,7 @@
       <c r="AD15" s="146"/>
       <c r="AE15" s="29"/>
     </row>
-    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>8</v>
       </c>
@@ -19700,7 +19680,7 @@
       <c r="AD16" s="146"/>
       <c r="AE16" s="29"/>
     </row>
-    <row r="17" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>9</v>
       </c>
@@ -19746,7 +19726,7 @@
       <c r="AD17" s="146"/>
       <c r="AE17" s="29"/>
     </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>10</v>
       </c>
@@ -19792,7 +19772,7 @@
       <c r="AD18" s="146"/>
       <c r="AE18" s="29"/>
     </row>
-    <row r="19" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>11</v>
       </c>
@@ -19838,7 +19818,7 @@
       <c r="AD19" s="146"/>
       <c r="AE19" s="29"/>
     </row>
-    <row r="20" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>12</v>
       </c>
@@ -19884,7 +19864,7 @@
       <c r="AD20" s="146"/>
       <c r="AE20" s="29"/>
     </row>
-    <row r="21" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <v>13</v>
       </c>
@@ -19930,7 +19910,7 @@
       <c r="AD21" s="146"/>
       <c r="AE21" s="29"/>
     </row>
-    <row r="22" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <v>14</v>
       </c>
@@ -19976,7 +19956,7 @@
       <c r="AD22" s="146"/>
       <c r="AE22" s="29"/>
     </row>
-    <row r="23" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>15</v>
       </c>
@@ -20022,7 +20002,7 @@
       <c r="AD23" s="146"/>
       <c r="AE23" s="29"/>
     </row>
-    <row r="24" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>16</v>
       </c>
@@ -20068,7 +20048,7 @@
       <c r="AD24" s="146"/>
       <c r="AE24" s="29"/>
     </row>
-    <row r="25" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>17</v>
       </c>
@@ -20114,7 +20094,7 @@
       <c r="AD25" s="146"/>
       <c r="AE25" s="29"/>
     </row>
-    <row r="26" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>18</v>
       </c>
@@ -20160,7 +20140,7 @@
       <c r="AD26" s="146"/>
       <c r="AE26" s="29"/>
     </row>
-    <row r="27" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>19</v>
       </c>
@@ -20206,7 +20186,7 @@
       <c r="AD27" s="146"/>
       <c r="AE27" s="29"/>
     </row>
-    <row r="28" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <v>20</v>
       </c>
@@ -20252,7 +20232,7 @@
       <c r="AD28" s="146"/>
       <c r="AE28" s="29"/>
     </row>
-    <row r="29" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <v>21</v>
       </c>
@@ -20298,7 +20278,7 @@
       <c r="AD29" s="146"/>
       <c r="AE29" s="29"/>
     </row>
-    <row r="30" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <v>22</v>
       </c>
@@ -20344,7 +20324,7 @@
       <c r="AD30" s="146"/>
       <c r="AE30" s="29"/>
     </row>
-    <row r="31" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
         <v>23</v>
       </c>
@@ -20390,7 +20370,7 @@
       <c r="AD31" s="146"/>
       <c r="AE31" s="29"/>
     </row>
-    <row r="32" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <v>24</v>
       </c>
@@ -20436,7 +20416,7 @@
       <c r="AD32" s="146"/>
       <c r="AE32" s="29"/>
     </row>
-    <row r="33" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <v>25</v>
       </c>
@@ -20482,7 +20462,7 @@
       <c r="AD33" s="146"/>
       <c r="AE33" s="29"/>
     </row>
-    <row r="34" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <v>26</v>
       </c>
@@ -20528,7 +20508,7 @@
       <c r="AD34" s="146"/>
       <c r="AE34" s="29"/>
     </row>
-    <row r="35" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <v>27</v>
       </c>
@@ -20574,7 +20554,7 @@
       <c r="AD35" s="146"/>
       <c r="AE35" s="29"/>
     </row>
-    <row r="36" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <v>28</v>
       </c>
@@ -20620,7 +20600,7 @@
       <c r="AD36" s="146"/>
       <c r="AE36" s="29"/>
     </row>
-    <row r="37" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <v>29</v>
       </c>
@@ -20666,7 +20646,7 @@
       <c r="AD37" s="146"/>
       <c r="AE37" s="29"/>
     </row>
-    <row r="38" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <v>30</v>
       </c>
@@ -20712,7 +20692,7 @@
       <c r="AD38" s="146"/>
       <c r="AE38" s="29"/>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B39" s="11"/>
       <c r="C39" s="106"/>
       <c r="D39" s="16"/>
@@ -20756,7 +20736,7 @@
       <c r="AD39" s="146"/>
       <c r="AE39" s="29"/>
     </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C40" s="102"/>
       <c r="D40" s="59"/>
       <c r="E40" s="78"/>
@@ -20807,7 +20787,7 @@
       <c r="AD40" s="270"/>
       <c r="AE40" s="270"/>
     </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:31" x14ac:dyDescent="0.3">
       <c r="G41" s="50"/>
       <c r="H41" s="50"/>
       <c r="I41" s="50"/>
@@ -20815,7 +20795,7 @@
       <c r="K41" s="50"/>
       <c r="L41" s="50"/>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.3">
       <c r="G42" s="50"/>
       <c r="H42" s="50"/>
       <c r="I42" s="50"/>
@@ -20823,23 +20803,23 @@
       <c r="K42" s="50"/>
       <c r="L42" s="50"/>
     </row>
-    <row r="43" spans="2:31" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:31" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" s="103"/>
       <c r="D43" s="20"/>
       <c r="E43" s="28"/>
       <c r="F43" s="28"/>
       <c r="G43" s="291"/>
       <c r="H43" s="291" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I43" s="291" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J43" s="291" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K43" s="291" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="L43" s="72">
         <f>SUM(L9:L39)</f>
@@ -20860,10 +20840,10 @@
       <c r="Z43" s="35"/>
       <c r="AA43" s="3"/>
     </row>
-    <row r="44" spans="2:31" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:31" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="R44" s="14"/>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.3">
       <c r="D47" s="127" t="s">
         <v>55</v>
       </c>
@@ -20880,7 +20860,7 @@
       <c r="N47" s="8"/>
       <c r="O47" s="8"/>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.3">
       <c r="D48" s="16" t="s">
         <v>57</v>
       </c>
@@ -20907,7 +20887,7 @@
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
     </row>
-    <row r="49" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D49" s="92">
         <f>SUMIF($AA$9:$AA$38,D48,$L$9:$L$39)</f>
         <v>0</v>
@@ -20947,7 +20927,7 @@
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
     </row>
-    <row r="50" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:15" x14ac:dyDescent="0.3">
       <c r="H50" s="95">
         <f>L43-H49</f>
         <v>0</v>
@@ -20962,7 +20942,7 @@
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
     </row>
-    <row r="51" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D51" s="46"/>
       <c r="E51" s="46"/>
       <c r="F51" s="46"/>
@@ -20971,7 +20951,7 @@
       <c r="M51" s="8"/>
       <c r="O51" s="8"/>
     </row>
-    <row r="52" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:15" x14ac:dyDescent="0.3">
       <c r="H52" s="119" t="s">
         <v>60</v>
       </c>
@@ -20983,7 +20963,7 @@
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
     </row>
-    <row r="53" spans="4:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H53" s="120" t="s">
         <v>61</v>
       </c>
@@ -20995,7 +20975,7 @@
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
     </row>
-    <row r="54" spans="4:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="H54" s="119" t="s">
         <v>62</v>
       </c>
@@ -21007,7 +20987,7 @@
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
     </row>
-    <row r="55" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:15" x14ac:dyDescent="0.3">
       <c r="I55" s="95">
         <f>G43-I54</f>
         <v>0</v>
@@ -21017,7 +20997,7 @@
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
     </row>
-    <row r="56" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:15" x14ac:dyDescent="0.3">
       <c r="J56" s="66"/>
       <c r="K56" s="66"/>
       <c r="L56" s="116"/>
@@ -21025,7 +21005,7 @@
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
     </row>
-    <row r="57" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:15" x14ac:dyDescent="0.3">
       <c r="J57" s="66"/>
       <c r="K57" s="66"/>
       <c r="L57" s="116"/>
@@ -21129,38 +21109,38 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR70"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="4" width="9.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="101" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="34.85546875" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="8" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" style="101" customWidth="1"/>
-    <col min="11" max="12" width="16.140625" style="8" customWidth="1"/>
-    <col min="13" max="23" width="19.28515625" style="42" customWidth="1"/>
-    <col min="24" max="26" width="19.28515625" style="8" customWidth="1"/>
-    <col min="27" max="27" width="26.28515625" style="8" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="8" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="61" customWidth="1"/>
-    <col min="30" max="30" width="20.7109375" customWidth="1"/>
-    <col min="31" max="31" width="44.28515625" customWidth="1"/>
-    <col min="32" max="32" width="14.140625" style="8" customWidth="1"/>
-    <col min="33" max="33" width="10.140625" style="8" customWidth="1"/>
-    <col min="34" max="34" width="8.28515625" style="8" customWidth="1"/>
-    <col min="35" max="35" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.28515625" style="342" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="4" width="9.109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" style="101" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" style="27" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="34.88671875" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" style="101" customWidth="1"/>
+    <col min="11" max="12" width="16.109375" style="8" customWidth="1"/>
+    <col min="13" max="23" width="19.33203125" style="42" customWidth="1"/>
+    <col min="24" max="26" width="19.33203125" style="8" customWidth="1"/>
+    <col min="27" max="27" width="26.33203125" style="8" customWidth="1"/>
+    <col min="28" max="28" width="12.88671875" style="8" customWidth="1"/>
+    <col min="29" max="29" width="13.5546875" style="61" customWidth="1"/>
+    <col min="30" max="30" width="20.6640625" customWidth="1"/>
+    <col min="31" max="31" width="44.33203125" customWidth="1"/>
+    <col min="32" max="32" width="14.109375" style="8" customWidth="1"/>
+    <col min="33" max="33" width="10.109375" style="8" customWidth="1"/>
+    <col min="34" max="34" width="8.33203125" style="8" customWidth="1"/>
+    <col min="35" max="35" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.33203125" style="342" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="12" style="342" customWidth="1"/>
-    <col min="39" max="39" width="13.28515625" style="342" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.28515625" style="342" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.140625" style="342" customWidth="1"/>
-    <col min="42" max="42" width="11.140625" style="344" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="9.140625" style="342" customWidth="1"/>
+    <col min="39" max="39" width="13.33203125" style="342" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.33203125" style="342" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.109375" style="342" customWidth="1"/>
+    <col min="42" max="42" width="11.109375" style="344" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="9.109375" style="342" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="397"/>
       <c r="B1" s="398"/>
       <c r="C1" s="398"/>
@@ -21200,7 +21180,7 @@
       <c r="AK1" s="341"/>
       <c r="AL1" s="341"/>
     </row>
-    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -21239,7 +21219,7 @@
       <c r="AK2" s="341"/>
       <c r="AL2" s="363"/>
     </row>
-    <row r="3" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E3" s="9"/>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -21250,7 +21230,7 @@
       <c r="R3" s="222"/>
       <c r="S3" s="222"/>
       <c r="V3" s="394" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="W3" s="395"/>
       <c r="X3" s="396"/>
@@ -21261,7 +21241,7 @@
       <c r="AJ3" s="32"/>
       <c r="AL3" s="364"/>
     </row>
-    <row r="4" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E4" s="9"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -21271,7 +21251,7 @@
       <c r="K4" s="112"/>
       <c r="L4" s="112"/>
       <c r="V4" s="394" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="W4" s="395"/>
       <c r="X4" s="396"/>
@@ -21290,7 +21270,7 @@
       <c r="AL4" s="365"/>
       <c r="AM4" s="365"/>
     </row>
-    <row r="5" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E5" s="9"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
@@ -21300,7 +21280,7 @@
       <c r="K5" s="112"/>
       <c r="L5" s="112"/>
       <c r="Q5" s="174" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="R5" s="174"/>
       <c r="S5" s="174"/>
@@ -21321,7 +21301,7 @@
       <c r="AL5" s="365"/>
       <c r="AM5" s="365"/>
     </row>
-    <row r="6" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E6" s="9"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -21348,32 +21328,32 @@
       <c r="AL6" s="365"/>
       <c r="AM6" s="365"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="M7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N7" s="176"/>
       <c r="O7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P7" s="176"/>
       <c r="Q7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="S7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="T7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="W7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AB7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AI7" s="176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AK7" s="391" t="s">
         <v>5</v>
@@ -21384,15 +21364,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:44" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E8" s="79" t="s">
         <v>52</v>
@@ -21401,46 +21381,46 @@
         <v>11</v>
       </c>
       <c r="G8" s="254" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="N8" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="O8" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="P8" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q8" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="R8" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="S8" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="N8" s="44" t="s">
+      <c r="T8" s="44" t="s">
         <v>241</v>
-      </c>
-      <c r="O8" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="P8" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>243</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>244</v>
-      </c>
-      <c r="T8" s="44" t="s">
-        <v>245</v>
       </c>
       <c r="U8" s="44" t="s">
         <v>32</v>
@@ -21452,10 +21432,10 @@
         <v>34</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Z8" s="12" t="s">
         <v>38</v>
@@ -21464,16 +21444,16 @@
         <v>39</v>
       </c>
       <c r="AB8" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AC8" s="79" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AD8" s="12" t="s">
         <v>41</v>
       </c>
       <c r="AE8" s="12" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AF8" s="12" t="s">
         <v>43</v>
@@ -21491,7 +21471,7 @@
         <v>49</v>
       </c>
       <c r="AL8" s="350" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AM8" s="350" t="s">
         <v>51</v>
@@ -21502,7 +21482,7 @@
       <c r="AQ8" s="352"/>
       <c r="AR8" s="352"/>
     </row>
-    <row r="9" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="42"/>
       <c r="B9" s="11">
         <v>1</v>
@@ -21574,7 +21554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="11">
         <v>2</v>
@@ -21646,7 +21626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="42"/>
       <c r="B11" s="11">
         <v>3</v>
@@ -21718,7 +21698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>4</v>
       </c>
@@ -21789,7 +21769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="42"/>
       <c r="B13" s="11">
         <v>5</v>
@@ -21861,7 +21841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="42"/>
       <c r="B14" s="11">
         <v>6</v>
@@ -21933,7 +21913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="42"/>
       <c r="B15" s="11">
         <v>7</v>
@@ -22005,7 +21985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>8</v>
       </c>
@@ -22076,7 +22056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:44" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:44" s="32" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="182"/>
       <c r="B17" s="11">
         <v>9</v>
@@ -22150,7 +22130,7 @@
       </c>
       <c r="AR17" s="342"/>
     </row>
-    <row r="18" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="42"/>
       <c r="B18" s="11">
         <v>10</v>
@@ -22222,7 +22202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>11</v>
       </c>
@@ -22293,7 +22273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>12</v>
       </c>
@@ -22364,7 +22344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="42"/>
       <c r="B21" s="11">
         <v>13</v>
@@ -22436,7 +22416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="42"/>
       <c r="B22" s="11">
         <v>14</v>
@@ -22508,7 +22488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="42"/>
       <c r="B23" s="11">
         <v>15</v>
@@ -22580,7 +22560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>16</v>
       </c>
@@ -22651,7 +22631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>17</v>
       </c>
@@ -22722,7 +22702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>18</v>
       </c>
@@ -22793,7 +22773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>19</v>
       </c>
@@ -22864,7 +22844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <v>20</v>
       </c>
@@ -22935,7 +22915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <v>21</v>
       </c>
@@ -23006,7 +22986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <v>22</v>
       </c>
@@ -23077,7 +23057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
         <v>23</v>
       </c>
@@ -23148,7 +23128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <v>24</v>
       </c>
@@ -23219,7 +23199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <v>25</v>
       </c>
@@ -23290,7 +23270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <v>26</v>
       </c>
@@ -23361,7 +23341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="42"/>
       <c r="B35" s="11">
         <v>27</v>
@@ -23433,7 +23413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <v>28</v>
       </c>
@@ -23504,7 +23484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <v>29</v>
       </c>
@@ -23575,7 +23555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <v>30</v>
       </c>
@@ -23646,7 +23626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
@@ -23697,7 +23677,7 @@
       <c r="AP39" s="357"/>
       <c r="AQ39" s="358"/>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B40" s="58"/>
       <c r="C40" s="58"/>
       <c r="D40" s="58"/>
@@ -23765,7 +23745,7 @@
       <c r="AN40" s="356"/>
       <c r="AP40" s="357"/>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A41" s="50"/>
       <c r="F41" s="28"/>
       <c r="G41" s="28"/>
@@ -23785,7 +23765,7 @@
       <c r="AG41" s="155"/>
       <c r="AH41" s="155"/>
     </row>
-    <row r="43" spans="1:43" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:43" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E43" s="103"/>
       <c r="H43" s="42"/>
       <c r="I43" s="14"/>
@@ -23854,7 +23834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
       <c r="AC44" s="185"/>
@@ -23864,28 +23844,28 @@
       <c r="AG44" s="14"/>
       <c r="AH44" s="14"/>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
       <c r="E45" s="167" t="s">
         <v>52</v>
       </c>
       <c r="F45" s="167" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G45" s="167"/>
       <c r="H45" s="167" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I45" s="167" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J45" s="167" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K45" s="167" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
       <c r="F46" s="89">
         <f t="shared" ref="F46:F67" si="11">SUMIF($E$10:$E$39,E46,$M$9:$M$39)+SUMIF($E$10:$E$39,E46,$O$9:$O$39)</f>
         <v>0</v>
@@ -23910,7 +23890,7 @@
       <c r="M46" s="89"/>
       <c r="N46" s="89"/>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
       <c r="F47" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -23953,7 +23933,7 @@
       <c r="AC47" s="8"/>
       <c r="AD47" s="61"/>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
       <c r="F48" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -23987,7 +23967,7 @@
         <v>59</v>
       </c>
       <c r="R48" s="190" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="S48" s="46"/>
       <c r="T48" s="89"/>
@@ -24004,7 +23984,7 @@
       <c r="AC48" s="8"/>
       <c r="AD48" s="61"/>
     </row>
-    <row r="49" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F49" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24069,7 +24049,7 @@
       <c r="AC49" s="8"/>
       <c r="AD49" s="61"/>
     </row>
-    <row r="50" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F50" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24110,7 +24090,7 @@
       <c r="AC50" s="8"/>
       <c r="AD50" s="61"/>
     </row>
-    <row r="51" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F51" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24143,7 +24123,7 @@
       <c r="AC51" s="8"/>
       <c r="AD51" s="61"/>
     </row>
-    <row r="52" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F52" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24187,7 +24167,7 @@
       <c r="AC52" s="8"/>
       <c r="AD52" s="61"/>
     </row>
-    <row r="53" spans="6:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="6:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F53" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24231,7 +24211,7 @@
       <c r="AC53" s="8"/>
       <c r="AD53" s="61"/>
     </row>
-    <row r="54" spans="6:35" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:35" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F54" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24275,7 +24255,7 @@
       <c r="AC54" s="8"/>
       <c r="AD54" s="61"/>
     </row>
-    <row r="55" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F55" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24303,7 +24283,7 @@
       <c r="AC55" s="8"/>
       <c r="AD55" s="61"/>
     </row>
-    <row r="56" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F56" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24335,7 +24315,7 @@
       <c r="AD56" s="61"/>
       <c r="AI56" s="194"/>
     </row>
-    <row r="57" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F57" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24367,7 +24347,7 @@
       <c r="AD57" s="61"/>
       <c r="AI57" s="32"/>
     </row>
-    <row r="58" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F58" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24399,7 +24379,7 @@
       <c r="AD58" s="61"/>
       <c r="AI58" s="194"/>
     </row>
-    <row r="59" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F59" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24428,7 +24408,7 @@
       <c r="AA59" s="139"/>
       <c r="AB59" s="139"/>
     </row>
-    <row r="60" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F60" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24464,7 +24444,7 @@
       <c r="AH60" s="43"/>
       <c r="AI60" s="32"/>
     </row>
-    <row r="61" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F61" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24494,7 +24474,7 @@
       <c r="AB61" s="139"/>
       <c r="AI61" s="32"/>
     </row>
-    <row r="62" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F62" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24524,7 +24504,7 @@
       <c r="AB62" s="139"/>
       <c r="AI62" s="194"/>
     </row>
-    <row r="63" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F63" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24554,7 +24534,7 @@
       <c r="AB63" s="139"/>
       <c r="AI63" s="32"/>
     </row>
-    <row r="64" spans="6:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F64" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24577,7 +24557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F65" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24600,7 +24580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F66" s="89">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -24623,7 +24603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="5:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E67" s="197"/>
       <c r="F67" s="198">
         <f t="shared" si="11"/>
@@ -24647,7 +24627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="5:11" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:11" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="E68" s="8" t="s">
         <v>32</v>
       </c>
@@ -24673,7 +24653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:11" x14ac:dyDescent="0.3">
       <c r="K70" s="139">
         <f>K68-K52-K54-K55-K56-K58</f>
         <v>0</v>
@@ -24945,35 +24925,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AE56"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="107" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="107" customWidth="1"/>
     <col min="4" max="4" width="22" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.42578125" style="27" customWidth="1"/>
-    <col min="7" max="10" width="20.140625" style="46" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="46" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="46" customWidth="1"/>
-    <col min="13" max="13" width="28.42578125" style="66" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" style="116" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="116" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="8" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="8" customWidth="1"/>
+    <col min="5" max="6" width="16.44140625" style="27" customWidth="1"/>
+    <col min="7" max="10" width="20.109375" style="46" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="46" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" style="46" customWidth="1"/>
+    <col min="13" max="13" width="28.44140625" style="66" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" style="116" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5546875" style="116" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="8" customWidth="1"/>
     <col min="18" max="18" width="22" style="8" customWidth="1"/>
-    <col min="19" max="19" width="19.140625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="13.85546875" style="8" customWidth="1"/>
+    <col min="19" max="19" width="19.109375" style="8" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" style="8" customWidth="1"/>
     <col min="21" max="21" width="51" style="8" customWidth="1"/>
-    <col min="22" max="22" width="28.28515625" style="8" customWidth="1"/>
-    <col min="23" max="23" width="18.140625" style="8" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="8" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" style="8" customWidth="1"/>
-    <col min="26" max="26" width="19.28515625" style="32" customWidth="1"/>
-    <col min="27" max="27" width="15.5703125" customWidth="1"/>
+    <col min="22" max="22" width="28.33203125" style="8" customWidth="1"/>
+    <col min="23" max="23" width="18.109375" style="8" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" style="8" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" style="8" customWidth="1"/>
+    <col min="26" max="26" width="19.33203125" style="32" customWidth="1"/>
+    <col min="27" max="27" width="15.5546875" customWidth="1"/>
     <col min="28" max="28" width="55" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="113"/>
       <c r="C1" s="202"/>
       <c r="D1" s="202"/>
@@ -25004,7 +24984,7 @@
       <c r="AC1" s="113"/>
       <c r="AD1" s="113"/>
     </row>
-    <row r="2" spans="2:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -25035,7 +25015,7 @@
       <c r="AC2" s="113"/>
       <c r="AD2" s="31"/>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="15"/>
       <c r="F3" s="23"/>
@@ -25048,7 +25028,7 @@
       <c r="AA3" s="32"/>
       <c r="AD3" s="32"/>
     </row>
-    <row r="4" spans="2:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="D4" s="15"/>
       <c r="E4" s="4"/>
@@ -25069,7 +25049,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" spans="2:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
       <c r="E5" s="4"/>
@@ -25090,12 +25070,12 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
     </row>
-    <row r="7" spans="2:31" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:31" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="79" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>52</v>
@@ -25107,13 +25087,13 @@
         <v>12</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J7" s="48" t="s">
         <v>103</v>
@@ -25122,10 +25102,10 @@
         <v>61</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M7" s="67" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N7" s="204" t="s">
         <v>15</v>
@@ -25134,25 +25114,25 @@
         <v>16</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>39</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>168</v>
@@ -25164,7 +25144,7 @@
         <v>45</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AA7" s="12" t="s">
         <v>41</v>
@@ -25173,7 +25153,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
         <v>1</v>
       </c>
@@ -25217,7 +25197,7 @@
       <c r="AA8" s="16"/>
       <c r="AB8" s="36"/>
     </row>
-    <row r="9" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>2</v>
       </c>
@@ -25261,7 +25241,7 @@
       <c r="AA9" s="16"/>
       <c r="AB9" s="36"/>
     </row>
-    <row r="10" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <f t="shared" ref="B10:B37" si="1">B9+1</f>
         <v>3</v>
@@ -25306,7 +25286,7 @@
       <c r="AA10" s="16"/>
       <c r="AB10" s="36"/>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -25351,7 +25331,7 @@
       <c r="AA11" s="16"/>
       <c r="AB11" s="36"/>
     </row>
-    <row r="12" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -25396,7 +25376,7 @@
       <c r="AA12" s="16"/>
       <c r="AB12" s="36"/>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -25440,7 +25420,7 @@
       <c r="AA13" s="16"/>
       <c r="AB13" s="36"/>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -25485,7 +25465,7 @@
       <c r="AA14" s="16"/>
       <c r="AB14" s="36"/>
     </row>
-    <row r="15" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -25530,7 +25510,7 @@
       <c r="AA15" s="16"/>
       <c r="AB15" s="36"/>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -25575,7 +25555,7 @@
       <c r="AA16" s="16"/>
       <c r="AB16" s="36"/>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -25620,7 +25600,7 @@
       <c r="AA17" s="16"/>
       <c r="AB17" s="36"/>
     </row>
-    <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -25665,7 +25645,7 @@
       <c r="AA18" s="16"/>
       <c r="AB18" s="36"/>
     </row>
-    <row r="19" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -25710,7 +25690,7 @@
       <c r="AA19" s="16"/>
       <c r="AB19" s="36"/>
     </row>
-    <row r="20" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -25755,7 +25735,7 @@
       <c r="AA20" s="16"/>
       <c r="AB20" s="36"/>
     </row>
-    <row r="21" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -25800,7 +25780,7 @@
       <c r="AA21" s="16"/>
       <c r="AB21" s="36"/>
     </row>
-    <row r="22" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -25845,7 +25825,7 @@
       <c r="AA22" s="16"/>
       <c r="AB22" s="36"/>
     </row>
-    <row r="23" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -25890,7 +25870,7 @@
       <c r="AA23" s="16"/>
       <c r="AB23" s="36"/>
     </row>
-    <row r="24" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -25935,7 +25915,7 @@
       <c r="AA24" s="16"/>
       <c r="AB24" s="36"/>
     </row>
-    <row r="25" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -25980,7 +25960,7 @@
       <c r="AA25" s="16"/>
       <c r="AB25" s="36"/>
     </row>
-    <row r="26" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -26025,7 +26005,7 @@
       <c r="AA26" s="16"/>
       <c r="AB26" s="36"/>
     </row>
-    <row r="27" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -26070,7 +26050,7 @@
       <c r="AA27" s="16"/>
       <c r="AB27" s="36"/>
     </row>
-    <row r="28" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -26115,7 +26095,7 @@
       <c r="AA28" s="16"/>
       <c r="AB28" s="36"/>
     </row>
-    <row r="29" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -26160,7 +26140,7 @@
       <c r="AA29" s="16"/>
       <c r="AB29" s="36"/>
     </row>
-    <row r="30" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -26205,7 +26185,7 @@
       <c r="AA30" s="16"/>
       <c r="AB30" s="36"/>
     </row>
-    <row r="31" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -26250,7 +26230,7 @@
       <c r="AA31" s="16"/>
       <c r="AB31" s="36"/>
     </row>
-    <row r="32" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -26295,7 +26275,7 @@
       <c r="AA32" s="16"/>
       <c r="AB32" s="36"/>
     </row>
-    <row r="33" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -26340,7 +26320,7 @@
       <c r="AA33" s="16"/>
       <c r="AB33" s="36"/>
     </row>
-    <row r="34" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -26385,7 +26365,7 @@
       <c r="AA34" s="16"/>
       <c r="AB34" s="36"/>
     </row>
-    <row r="35" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -26430,7 +26410,7 @@
       <c r="AA35" s="16"/>
       <c r="AB35" s="36"/>
     </row>
-    <row r="36" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -26475,7 +26455,7 @@
       <c r="AA36" s="16"/>
       <c r="AB36" s="36"/>
     </row>
-    <row r="37" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -26520,7 +26500,7 @@
       <c r="AA37" s="16"/>
       <c r="AB37" s="36"/>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B38" s="11"/>
       <c r="C38" s="106"/>
       <c r="D38" s="16"/>
@@ -26562,7 +26542,7 @@
       <c r="AA38" s="16"/>
       <c r="AB38" s="36"/>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.3">
       <c r="C39" s="102"/>
       <c r="D39" s="59"/>
       <c r="E39" s="78"/>
@@ -26611,7 +26591,7 @@
       <c r="AA39" s="22"/>
       <c r="AB39" s="37"/>
     </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:28" x14ac:dyDescent="0.3">
       <c r="G40" s="50"/>
       <c r="H40" s="50"/>
       <c r="I40" s="50"/>
@@ -26619,7 +26599,7 @@
       <c r="K40" s="50"/>
       <c r="L40" s="50"/>
     </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:28" x14ac:dyDescent="0.3">
       <c r="G41" s="50"/>
       <c r="H41" s="50"/>
       <c r="I41" s="50"/>
@@ -26627,7 +26607,7 @@
       <c r="K41" s="50"/>
       <c r="L41" s="50"/>
     </row>
-    <row r="42" spans="2:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C42" s="103"/>
       <c r="D42" s="20"/>
       <c r="E42" s="28"/>
@@ -26671,17 +26651,17 @@
       <c r="Z42" s="35"/>
       <c r="AA42" s="3"/>
     </row>
-    <row r="43" spans="2:28" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:28" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="R43" s="14"/>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.3">
       <c r="F45" s="46"/>
       <c r="L45" s="66"/>
       <c r="O45" s="8"/>
       <c r="Y45" s="32"/>
       <c r="AA45" s="32"/>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.3">
       <c r="D46" s="402" t="s">
         <v>55</v>
       </c>
@@ -26700,7 +26680,7 @@
       <c r="Y46" s="32"/>
       <c r="AA46" s="32"/>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.3">
       <c r="D47" s="16" t="s">
         <v>57</v>
       </c>
@@ -26727,7 +26707,7 @@
       <c r="Y47" s="32"/>
       <c r="AA47" s="32"/>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.3">
       <c r="D48" s="92">
         <f>SUMIF($AA$8:$AA$37,D47,$L$8:$L$38)</f>
         <v>0</v>
@@ -26766,7 +26746,7 @@
       <c r="Y48" s="32"/>
       <c r="AA48" s="32"/>
     </row>
-    <row r="49" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:27" x14ac:dyDescent="0.3">
       <c r="G49" s="95">
         <f>L42-G48</f>
         <v>0</v>
@@ -26784,7 +26764,7 @@
       <c r="Y49" s="32"/>
       <c r="AA49" s="32"/>
     </row>
-    <row r="50" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D50" s="46"/>
       <c r="E50" s="46"/>
       <c r="F50" s="46"/>
@@ -26794,7 +26774,7 @@
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
     </row>
-    <row r="51" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:27" x14ac:dyDescent="0.3">
       <c r="H51" s="119" t="s">
         <v>60</v>
       </c>
@@ -26806,7 +26786,7 @@
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
     </row>
-    <row r="52" spans="4:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H52" s="120" t="s">
         <v>61</v>
       </c>
@@ -26818,7 +26798,7 @@
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
     </row>
-    <row r="53" spans="4:27" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:27" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="H53" s="119" t="s">
         <v>62</v>
       </c>
@@ -26830,7 +26810,7 @@
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
     </row>
-    <row r="54" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:27" x14ac:dyDescent="0.3">
       <c r="I54" s="95">
         <f>G42-I53</f>
         <v>0</v>
@@ -26840,7 +26820,7 @@
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
     </row>
-    <row r="55" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:27" x14ac:dyDescent="0.3">
       <c r="J55" s="66"/>
       <c r="K55" s="66"/>
       <c r="L55" s="116"/>
@@ -26848,7 +26828,7 @@
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
     </row>
-    <row r="56" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:27" x14ac:dyDescent="0.3">
       <c r="J56" s="66"/>
       <c r="K56" s="66"/>
       <c r="L56" s="116"/>
@@ -26940,34 +26920,34 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:X123"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="107" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="27" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="46" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="46" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.5703125" style="66" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="8" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="8" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" style="32" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="32" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="107" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="46" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5546875" style="66" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="32" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" style="32" customWidth="1"/>
     <col min="16" max="16" width="42" style="32" customWidth="1"/>
-    <col min="17" max="17" width="28.28515625" style="8" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" style="8" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="8" customWidth="1"/>
-    <col min="21" max="21" width="19.28515625" style="32" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" customWidth="1"/>
-    <col min="23" max="23" width="125.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.33203125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" style="8" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="8" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="8" customWidth="1"/>
+    <col min="21" max="21" width="19.33203125" style="32" customWidth="1"/>
+    <col min="22" max="22" width="15.5546875" customWidth="1"/>
+    <col min="23" max="23" width="125.33203125" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="397"/>
       <c r="C1" s="413"/>
       <c r="D1" s="396"/>
@@ -26992,7 +26972,7 @@
       <c r="W1" s="417"/>
       <c r="X1" s="401"/>
     </row>
-    <row r="2" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
@@ -27017,7 +26997,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="113"/>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C3" s="9"/>
       <c r="D3" s="15"/>
       <c r="E3" s="23"/>
@@ -27028,7 +27008,7 @@
       <c r="U3" s="8"/>
       <c r="V3" s="32"/>
     </row>
-    <row r="4" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="D4" s="15"/>
       <c r="E4" s="4"/>
@@ -27045,7 +27025,7 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
     </row>
-    <row r="5" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
       <c r="E5" s="4"/>
@@ -27063,7 +27043,7 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
     </row>
-    <row r="6" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C6" s="9"/>
       <c r="D6" s="15"/>
       <c r="E6" s="4"/>
@@ -27081,7 +27061,7 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C7" s="101"/>
       <c r="E7" s="101"/>
       <c r="F7" s="101"/>
@@ -27098,12 +27078,12 @@
       <c r="U7" s="101"/>
       <c r="V7" s="101"/>
     </row>
-    <row r="8" spans="2:24" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:24" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="271" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="272" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D8" s="274" t="s">
         <v>52</v>
@@ -27112,40 +27092,40 @@
         <v>11</v>
       </c>
       <c r="F8" s="292" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G8" s="369" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="292" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I8" s="293" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J8" s="274" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K8" s="274" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L8" s="274" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M8" s="274" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N8" s="274" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="274" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P8" s="274" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q8" s="274" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="R8" s="274" t="s">
         <v>168</v>
@@ -27157,7 +27137,7 @@
         <v>45</v>
       </c>
       <c r="U8" s="274" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="V8" s="274" t="s">
         <v>41</v>
@@ -27167,7 +27147,7 @@
       </c>
       <c r="X8" s="370"/>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>1</v>
       </c>
@@ -27193,7 +27173,7 @@
       <c r="V9" s="16"/>
       <c r="W9" s="36"/>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>2</v>
       </c>
@@ -27219,7 +27199,7 @@
       <c r="V10" s="16"/>
       <c r="W10" s="36"/>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>3</v>
       </c>
@@ -27245,7 +27225,7 @@
       <c r="V11" s="16"/>
       <c r="W11" s="36"/>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>4</v>
       </c>
@@ -27271,7 +27251,7 @@
       <c r="V12" s="16"/>
       <c r="W12" s="36"/>
     </row>
-    <row r="13" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>5</v>
       </c>
@@ -27297,7 +27277,7 @@
       <c r="V13" s="16"/>
       <c r="W13" s="36"/>
     </row>
-    <row r="14" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>6</v>
       </c>
@@ -27323,7 +27303,7 @@
       <c r="V14" s="16"/>
       <c r="W14" s="36"/>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>7</v>
       </c>
@@ -27349,7 +27329,7 @@
       <c r="V15" s="16"/>
       <c r="W15" s="36"/>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>8</v>
       </c>
@@ -27375,7 +27355,7 @@
       <c r="V16" s="16"/>
       <c r="W16" s="36"/>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>9</v>
       </c>
@@ -27401,7 +27381,7 @@
       <c r="V17" s="16"/>
       <c r="W17" s="36"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>10</v>
       </c>
@@ -27427,7 +27407,7 @@
       <c r="V18" s="16"/>
       <c r="W18" s="36"/>
     </row>
-    <row r="19" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>11</v>
       </c>
@@ -27453,7 +27433,7 @@
       <c r="V19" s="16"/>
       <c r="W19" s="36"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>12</v>
       </c>
@@ -27478,7 +27458,7 @@
       <c r="V20" s="16"/>
       <c r="W20" s="36"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <v>13</v>
       </c>
@@ -27504,7 +27484,7 @@
       <c r="V21" s="16"/>
       <c r="W21" s="36"/>
     </row>
-    <row r="22" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <v>14</v>
       </c>
@@ -27530,7 +27510,7 @@
       <c r="V22" s="16"/>
       <c r="W22" s="36"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>15</v>
       </c>
@@ -27556,7 +27536,7 @@
       <c r="V23" s="16"/>
       <c r="W23" s="36"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>16</v>
       </c>
@@ -27582,7 +27562,7 @@
       <c r="V24" s="16"/>
       <c r="W24" s="36"/>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>17</v>
       </c>
@@ -27608,7 +27588,7 @@
       <c r="V25" s="16"/>
       <c r="W25" s="36"/>
     </row>
-    <row r="26" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>18</v>
       </c>
@@ -27634,7 +27614,7 @@
       <c r="V26" s="16"/>
       <c r="W26" s="36"/>
     </row>
-    <row r="27" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>19</v>
       </c>
@@ -27660,7 +27640,7 @@
       <c r="V27" s="16"/>
       <c r="W27" s="36"/>
     </row>
-    <row r="28" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <v>20</v>
       </c>
@@ -27686,7 +27666,7 @@
       <c r="V28" s="16"/>
       <c r="W28" s="36"/>
     </row>
-    <row r="29" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <v>21</v>
       </c>
@@ -27712,7 +27692,7 @@
       <c r="V29" s="16"/>
       <c r="W29" s="36"/>
     </row>
-    <row r="30" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <v>22</v>
       </c>
@@ -27738,7 +27718,7 @@
       <c r="V30" s="16"/>
       <c r="W30" s="36"/>
     </row>
-    <row r="31" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
         <v>23</v>
       </c>
@@ -27764,7 +27744,7 @@
       <c r="V31" s="16"/>
       <c r="W31" s="36"/>
     </row>
-    <row r="32" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <v>24</v>
       </c>
@@ -27790,7 +27770,7 @@
       <c r="V32" s="16"/>
       <c r="W32" s="36"/>
     </row>
-    <row r="33" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <v>25</v>
       </c>
@@ -27816,7 +27796,7 @@
       <c r="V33" s="16"/>
       <c r="W33" s="36"/>
     </row>
-    <row r="34" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <v>26</v>
       </c>
@@ -27842,7 +27822,7 @@
       <c r="V34" s="16"/>
       <c r="W34" s="36"/>
     </row>
-    <row r="35" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <v>27</v>
       </c>
@@ -27868,7 +27848,7 @@
       <c r="V35" s="16"/>
       <c r="W35" s="36"/>
     </row>
-    <row r="36" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <v>28</v>
       </c>
@@ -27894,7 +27874,7 @@
       <c r="V36" s="16"/>
       <c r="W36" s="36"/>
     </row>
-    <row r="37" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <v>29</v>
       </c>
@@ -27920,7 +27900,7 @@
       <c r="V37" s="16"/>
       <c r="W37" s="36"/>
     </row>
-    <row r="38" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <v>30</v>
       </c>
@@ -27946,7 +27926,7 @@
       <c r="V38" s="16"/>
       <c r="W38" s="36"/>
     </row>
-    <row r="39" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <v>31</v>
       </c>
@@ -27972,7 +27952,7 @@
       <c r="V39" s="16"/>
       <c r="W39" s="36"/>
     </row>
-    <row r="40" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <v>32</v>
       </c>
@@ -27998,7 +27978,7 @@
       <c r="V40" s="16"/>
       <c r="W40" s="36"/>
     </row>
-    <row r="41" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
         <v>33</v>
       </c>
@@ -28024,7 +28004,7 @@
       <c r="V41" s="16"/>
       <c r="W41" s="36"/>
     </row>
-    <row r="42" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
         <v>34</v>
       </c>
@@ -28050,7 +28030,7 @@
       <c r="V42" s="16"/>
       <c r="W42" s="36"/>
     </row>
-    <row r="43" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="11">
         <v>35</v>
       </c>
@@ -28076,7 +28056,7 @@
       <c r="V43" s="16"/>
       <c r="W43" s="36"/>
     </row>
-    <row r="44" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="11">
         <v>36</v>
       </c>
@@ -28102,7 +28082,7 @@
       <c r="V44" s="16"/>
       <c r="W44" s="36"/>
     </row>
-    <row r="45" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="11">
         <v>37</v>
       </c>
@@ -28128,7 +28108,7 @@
       <c r="V45" s="16"/>
       <c r="W45" s="36"/>
     </row>
-    <row r="46" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="11">
         <v>38</v>
       </c>
@@ -28154,7 +28134,7 @@
       <c r="V46" s="16"/>
       <c r="W46" s="36"/>
     </row>
-    <row r="47" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="11">
         <v>39</v>
       </c>
@@ -28180,7 +28160,7 @@
       <c r="V47" s="16"/>
       <c r="W47" s="36"/>
     </row>
-    <row r="48" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="11">
         <v>40</v>
       </c>
@@ -28206,7 +28186,7 @@
       <c r="V48" s="16"/>
       <c r="W48" s="36"/>
     </row>
-    <row r="49" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
         <v>41</v>
       </c>
@@ -28232,7 +28212,7 @@
       <c r="V49" s="16"/>
       <c r="W49" s="36"/>
     </row>
-    <row r="50" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="11">
         <v>42</v>
       </c>
@@ -28258,7 +28238,7 @@
       <c r="V50" s="16"/>
       <c r="W50" s="36"/>
     </row>
-    <row r="51" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="11">
         <v>43</v>
       </c>
@@ -28284,7 +28264,7 @@
       <c r="V51" s="16"/>
       <c r="W51" s="36"/>
     </row>
-    <row r="52" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <v>44</v>
       </c>
@@ -28310,7 +28290,7 @@
       <c r="V52" s="16"/>
       <c r="W52" s="36"/>
     </row>
-    <row r="53" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
         <v>45</v>
       </c>
@@ -28336,7 +28316,7 @@
       <c r="V53" s="16"/>
       <c r="W53" s="36"/>
     </row>
-    <row r="54" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="11">
         <v>46</v>
       </c>
@@ -28362,7 +28342,7 @@
       <c r="V54" s="16"/>
       <c r="W54" s="36"/>
     </row>
-    <row r="55" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="11">
         <v>47</v>
       </c>
@@ -28388,7 +28368,7 @@
       <c r="V55" s="16"/>
       <c r="W55" s="36"/>
     </row>
-    <row r="56" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="11">
         <v>48</v>
       </c>
@@ -28414,7 +28394,7 @@
       <c r="V56" s="16"/>
       <c r="W56" s="36"/>
     </row>
-    <row r="57" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
         <v>49</v>
       </c>
@@ -28440,7 +28420,7 @@
       <c r="V57" s="16"/>
       <c r="W57" s="36"/>
     </row>
-    <row r="58" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <v>50</v>
       </c>
@@ -28466,7 +28446,7 @@
       <c r="V58" s="16"/>
       <c r="W58" s="36"/>
     </row>
-    <row r="59" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <v>51</v>
       </c>
@@ -28492,7 +28472,7 @@
       <c r="V59" s="16"/>
       <c r="W59" s="36"/>
     </row>
-    <row r="60" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
         <v>52</v>
       </c>
@@ -28518,7 +28498,7 @@
       <c r="V60" s="16"/>
       <c r="W60" s="253"/>
     </row>
-    <row r="61" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <v>53</v>
       </c>
@@ -28544,7 +28524,7 @@
       <c r="V61" s="16"/>
       <c r="W61" s="253"/>
     </row>
-    <row r="62" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
         <v>54</v>
       </c>
@@ -28570,7 +28550,7 @@
       <c r="V62" s="16"/>
       <c r="W62" s="36"/>
     </row>
-    <row r="63" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
         <v>55</v>
       </c>
@@ -28596,7 +28576,7 @@
       <c r="V63" s="16"/>
       <c r="W63" s="36"/>
     </row>
-    <row r="64" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
         <v>56</v>
       </c>
@@ -28622,7 +28602,7 @@
       <c r="V64" s="16"/>
       <c r="W64" s="36"/>
     </row>
-    <row r="65" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
         <v>57</v>
       </c>
@@ -28648,7 +28628,7 @@
       <c r="V65" s="16"/>
       <c r="W65" s="36"/>
     </row>
-    <row r="66" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
         <v>58</v>
       </c>
@@ -28674,7 +28654,7 @@
       <c r="V66" s="16"/>
       <c r="W66" s="36"/>
     </row>
-    <row r="67" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
         <v>59</v>
       </c>
@@ -28700,7 +28680,7 @@
       <c r="V67" s="16"/>
       <c r="W67" s="36"/>
     </row>
-    <row r="68" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
         <v>60</v>
       </c>
@@ -28726,7 +28706,7 @@
       <c r="V68" s="16"/>
       <c r="W68" s="36"/>
     </row>
-    <row r="69" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
         <v>61</v>
       </c>
@@ -28752,7 +28732,7 @@
       <c r="V69" s="16"/>
       <c r="W69" s="36"/>
     </row>
-    <row r="70" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="11">
         <v>62</v>
       </c>
@@ -28778,7 +28758,7 @@
       <c r="V70" s="16"/>
       <c r="W70" s="36"/>
     </row>
-    <row r="71" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
         <v>63</v>
       </c>
@@ -28804,7 +28784,7 @@
       <c r="V71" s="16"/>
       <c r="W71" s="36"/>
     </row>
-    <row r="72" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="11">
         <v>64</v>
       </c>
@@ -28830,7 +28810,7 @@
       <c r="V72" s="16"/>
       <c r="W72" s="36"/>
     </row>
-    <row r="73" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="11">
         <v>65</v>
       </c>
@@ -28856,7 +28836,7 @@
       <c r="V73" s="16"/>
       <c r="W73" s="36"/>
     </row>
-    <row r="74" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="11">
         <v>66</v>
       </c>
@@ -28882,7 +28862,7 @@
       <c r="V74" s="16"/>
       <c r="W74" s="36"/>
     </row>
-    <row r="75" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="11">
         <v>67</v>
       </c>
@@ -28908,7 +28888,7 @@
       <c r="V75" s="16"/>
       <c r="W75" s="36"/>
     </row>
-    <row r="76" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="11">
         <v>68</v>
       </c>
@@ -28934,7 +28914,7 @@
       <c r="V76" s="16"/>
       <c r="W76" s="36"/>
     </row>
-    <row r="77" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
         <v>69</v>
       </c>
@@ -28960,7 +28940,7 @@
       <c r="V77" s="16"/>
       <c r="W77" s="36"/>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B78" s="11">
         <v>70</v>
       </c>
@@ -28986,7 +28966,7 @@
       <c r="V78" s="16"/>
       <c r="W78" s="36"/>
     </row>
-    <row r="79" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="11">
         <v>71</v>
       </c>
@@ -29012,7 +28992,7 @@
       <c r="V79" s="16"/>
       <c r="W79" s="36"/>
     </row>
-    <row r="80" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="11">
         <v>72</v>
       </c>
@@ -29038,7 +29018,7 @@
       <c r="V80" s="16"/>
       <c r="W80" s="36"/>
     </row>
-    <row r="81" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
         <v>73</v>
       </c>
@@ -29064,7 +29044,7 @@
       <c r="V81" s="16"/>
       <c r="W81" s="36"/>
     </row>
-    <row r="82" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
         <v>74</v>
       </c>
@@ -29090,7 +29070,7 @@
       <c r="V82" s="16"/>
       <c r="W82" s="36"/>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
         <v>75</v>
       </c>
@@ -29116,7 +29096,7 @@
       <c r="V83" s="16"/>
       <c r="W83" s="36"/>
     </row>
-    <row r="84" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
         <v>76</v>
       </c>
@@ -29142,7 +29122,7 @@
       <c r="V84" s="16"/>
       <c r="W84" s="36"/>
     </row>
-    <row r="85" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
         <v>77</v>
       </c>
@@ -29168,7 +29148,7 @@
       <c r="V85" s="16"/>
       <c r="W85" s="36"/>
     </row>
-    <row r="86" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
         <v>78</v>
       </c>
@@ -29194,7 +29174,7 @@
       <c r="V86" s="16"/>
       <c r="W86" s="36"/>
     </row>
-    <row r="87" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
         <v>79</v>
       </c>
@@ -29220,7 +29200,7 @@
       <c r="V87" s="16"/>
       <c r="W87" s="36"/>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B88" s="11"/>
       <c r="C88" s="106"/>
       <c r="D88" s="16"/>
@@ -29244,7 +29224,7 @@
       <c r="V88" s="16"/>
       <c r="W88" s="36"/>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C89" s="102"/>
       <c r="D89" s="59"/>
       <c r="E89" s="78"/>
@@ -29279,23 +29259,23 @@
       <c r="V89" s="22"/>
       <c r="W89" s="37"/>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:23" x14ac:dyDescent="0.3">
       <c r="F90" s="50"/>
       <c r="G90" s="50"/>
       <c r="H90" s="50"/>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:23" x14ac:dyDescent="0.3">
       <c r="F91" s="50"/>
       <c r="G91" s="50"/>
       <c r="H91" s="50"/>
     </row>
-    <row r="92" spans="2:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C92" s="103"/>
       <c r="D92" s="20"/>
       <c r="E92" s="28"/>
       <c r="F92" s="291"/>
       <c r="G92" s="295" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H92" s="72">
         <f>SUM(H9:H88)</f>
@@ -29315,10 +29295,10 @@
       <c r="U92" s="35"/>
       <c r="V92" s="3"/>
     </row>
-    <row r="93" spans="2:23" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:23" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M93" s="14"/>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D96" s="402" t="s">
         <v>55</v>
       </c>
@@ -29332,7 +29312,7 @@
       <c r="K96" s="393"/>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D97" s="16" t="s">
         <v>57</v>
       </c>
@@ -29354,7 +29334,7 @@
       </c>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D98" s="92">
         <f>SUMIF($V$9:$V$88,D97,$H$9:$H$88)</f>
         <v>0</v>
@@ -29388,7 +29368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G99" s="95">
         <f>H92-G98</f>
         <v>0</v>
@@ -29401,13 +29381,13 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D100" s="46"/>
       <c r="E100" s="46"/>
       <c r="G100" s="66"/>
       <c r="L100" s="8"/>
     </row>
-    <row r="101" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G101" s="119" t="s">
         <v>60</v>
       </c>
@@ -29419,7 +29399,7 @@
       <c r="J101" s="66"/>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G102" s="120" t="s">
         <v>61</v>
       </c>
@@ -29431,7 +29411,7 @@
       <c r="J102" s="66"/>
       <c r="L102" s="8"/>
     </row>
-    <row r="103" spans="4:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G103" s="119" t="s">
         <v>62</v>
       </c>
@@ -29442,16 +29422,16 @@
       <c r="I103" s="46"/>
       <c r="J103" s="66"/>
     </row>
-    <row r="104" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:12" x14ac:dyDescent="0.3">
       <c r="H104" s="95">
         <f>F92-H103</f>
         <v>0</v>
       </c>
       <c r="I104" s="46"/>
     </row>
-    <row r="106" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G106" s="162" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H106" s="162" t="s">
         <v>32</v>
@@ -29463,9 +29443,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G107" s="46" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H107" s="46">
         <f>SUMIF($J$9:$J$88,G107,$F$9:$F$88)</f>
@@ -29480,9 +29460,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G108" s="46" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H108" s="46">
         <f>SUMIF($J$9:$J$88,G108,$F$9:$F$88)</f>
@@ -29497,9 +29477,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G109" s="97" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H109" s="97">
         <f>SUMIF($J$9:$J$88,G109,$F$9:$F$88)</f>
@@ -29514,7 +29494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="4:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="H110" s="46">
         <f>SUM(H107:H109)</f>
         <v>0</v>
@@ -29528,7 +29508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:12" x14ac:dyDescent="0.3">
       <c r="H111" s="94">
         <f>H110-H103</f>
         <v>0</v>
@@ -29542,46 +29522,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C113" s="156"/>
       <c r="D113" s="32"/>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C114" s="156"/>
       <c r="D114" s="32"/>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C115" s="156"/>
       <c r="D115" s="32"/>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C116" s="156"/>
       <c r="D116" s="32"/>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C117" s="156"/>
       <c r="D117" s="32"/>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C118" s="156"/>
       <c r="D118" s="32"/>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C119" s="157"/>
       <c r="D119" s="4"/>
       <c r="E119" s="155"/>
       <c r="F119" s="93"/>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C120" s="156"/>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C121" s="156"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C122" s="156"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C123" s="156"/>
     </row>
   </sheetData>
@@ -29656,6 +29636,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4e7d37e-1dcc-4436-a729-076bff741eab">
@@ -29664,15 +29653,6 @@
     <TaxCatchAll xmlns="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29871,20 +29851,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7896FE09-375C-4B80-B12E-A86A22AFA945}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B44F4C-5208-463C-B02B-93FE2A2E7C51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f4e7d37e-1dcc-4436-a729-076bff741eab"/>
     <ds:schemaRef ds:uri="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7896FE09-375C-4B80-B12E-A86A22AFA945}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/source/assets/workbooks/texas.xlsx
+++ b/source/assets/workbooks/texas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tpcus808.sharepoint.com/sites/DataEntryAutomation/Shared Documents/New Automation Documents/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_F04EF44A1142426DCE9F4511414016BFA20E4AD1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8555807C-BFC7-45DE-B4A1-AF3E07847AD8}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_F04EF44A1142426DCE9F4511414016BFA20E4AD1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5A90798-1D72-4250-8B23-D7712328D52A}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="435" windowWidth="21600" windowHeight="12450" tabRatio="851" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11856" yWindow="12852" windowWidth="23256" windowHeight="13896" tabRatio="851" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="304">
   <si>
     <t>35% of paid crew must be Texas Residents</t>
   </si>
@@ -787,36 +787,15 @@
     <t>1st Shoot date</t>
   </si>
   <si>
-    <t>CREW #1</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>120 Days Prior to Shoot date</t>
   </si>
   <si>
-    <t>CREW #2</t>
-  </si>
-  <si>
     <t>TOTAL TX ONLY - CREW &amp; CAST</t>
   </si>
   <si>
     <t>TOTAL ALL CREW &amp; CAST</t>
   </si>
   <si>
-    <t>CAST #1</t>
-  </si>
-  <si>
-    <t>CAST #2</t>
-  </si>
-  <si>
-    <t>CAST #3</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>Pay period to Check Number</t>
   </si>
   <si>
@@ -1115,6 +1094,9 @@
   </si>
   <si>
     <t>On PTIP</t>
+  </si>
+  <si>
+    <t>From Documents</t>
   </si>
 </sst>
 </file>
@@ -2692,16 +2674,40 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2713,37 +2719,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2754,6 +2730,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3263,13 +3245,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -3340,28 +3315,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3396,6 +3350,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -3418,6 +3379,27 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3452,6 +3434,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="3" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -3460,6 +3449,48 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3515,41 +3546,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -3592,21 +3588,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3627,14 +3609,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3795,34 +3777,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -3879,6 +3833,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -3893,6 +3854,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -3901,6 +3869,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3991,14 +3973,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4089,21 +4071,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4138,6 +4106,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -4152,14 +4134,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4488,40 +4470,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="121" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="404" t="s">
+      <c r="A1" s="397" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="405"/>
-      <c r="G1" s="405"/>
-      <c r="H1" s="405"/>
-      <c r="I1" s="405"/>
-      <c r="J1" s="405"/>
-      <c r="K1" s="405"/>
-      <c r="L1" s="405"/>
-      <c r="M1" s="405"/>
-      <c r="N1" s="405"/>
+      <c r="B1" s="398"/>
+      <c r="C1" s="398"/>
+      <c r="D1" s="398"/>
+      <c r="E1" s="398"/>
+      <c r="F1" s="398"/>
+      <c r="G1" s="398"/>
+      <c r="H1" s="398"/>
+      <c r="I1" s="398"/>
+      <c r="J1" s="398"/>
+      <c r="K1" s="398"/>
+      <c r="L1" s="398"/>
+      <c r="M1" s="398"/>
+      <c r="N1" s="398"/>
     </row>
     <row r="2" spans="1:15" s="121" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="404" t="s">
+      <c r="A2" s="397" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="405"/>
-      <c r="C2" s="405"/>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
-      <c r="F2" s="405"/>
-      <c r="G2" s="405"/>
-      <c r="H2" s="405"/>
-      <c r="I2" s="405"/>
-      <c r="J2" s="405"/>
-      <c r="K2" s="405"/>
-      <c r="L2" s="405"/>
-      <c r="M2" s="405"/>
-      <c r="N2" s="405"/>
+      <c r="B2" s="398"/>
+      <c r="C2" s="398"/>
+      <c r="D2" s="398"/>
+      <c r="E2" s="398"/>
+      <c r="F2" s="398"/>
+      <c r="G2" s="398"/>
+      <c r="H2" s="398"/>
+      <c r="I2" s="398"/>
+      <c r="J2" s="398"/>
+      <c r="K2" s="398"/>
+      <c r="L2" s="398"/>
+      <c r="M2" s="398"/>
+      <c r="N2" s="398"/>
     </row>
     <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="229"/>
@@ -4609,12 +4591,12 @@
       </c>
       <c r="D9" s="229"/>
       <c r="E9" s="229"/>
-      <c r="G9" s="406" t="s">
+      <c r="G9" s="399" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="407"/>
-      <c r="I9" s="407"/>
-      <c r="J9" s="407"/>
+      <c r="H9" s="396"/>
+      <c r="I9" s="396"/>
+      <c r="J9" s="396"/>
       <c r="K9" s="229"/>
       <c r="L9" s="229"/>
       <c r="M9" s="229"/>
@@ -5378,10 +5360,10 @@
       <c r="N43" s="229"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C44" s="408" t="s">
+      <c r="C44" s="395" t="s">
         <v>131</v>
       </c>
-      <c r="D44" s="407"/>
+      <c r="D44" s="396"/>
       <c r="E44" s="320" t="b">
         <v>0</v>
       </c>
@@ -5391,10 +5373,10 @@
       <c r="N44" s="229"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C45" s="408" t="s">
+      <c r="C45" s="395" t="s">
         <v>132</v>
       </c>
-      <c r="D45" s="407"/>
+      <c r="D45" s="396"/>
       <c r="E45" s="320" t="b">
         <v>0</v>
       </c>
@@ -5404,10 +5386,10 @@
       <c r="N45" s="229"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C46" s="408" t="s">
+      <c r="C46" s="395" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="407"/>
+      <c r="D46" s="396"/>
       <c r="E46" s="320" t="b">
         <v>0</v>
       </c>
@@ -5417,10 +5399,10 @@
       <c r="N46" s="229"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C47" s="408" t="s">
+      <c r="C47" s="395" t="s">
         <v>134</v>
       </c>
-      <c r="D47" s="407"/>
+      <c r="D47" s="396"/>
       <c r="E47" s="320" t="b">
         <v>0</v>
       </c>
@@ -5430,10 +5412,10 @@
       <c r="N47" s="229"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C48" s="408" t="s">
+      <c r="C48" s="395" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="407"/>
+      <c r="D48" s="396"/>
       <c r="E48" s="320" t="b">
         <v>0</v>
       </c>
@@ -5443,10 +5425,10 @@
       <c r="N48" s="229"/>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C49" s="408" t="s">
+      <c r="C49" s="395" t="s">
         <v>136</v>
       </c>
-      <c r="D49" s="407"/>
+      <c r="D49" s="396"/>
       <c r="E49" s="320" t="b">
         <v>0</v>
       </c>
@@ -5455,10 +5437,10 @@
       <c r="M49" s="229"/>
     </row>
     <row r="50" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C50" s="409" t="s">
+      <c r="C50" s="393" t="s">
         <v>137</v>
       </c>
-      <c r="D50" s="410"/>
+      <c r="D50" s="394"/>
       <c r="E50" s="321" t="b">
         <v>0</v>
       </c>
@@ -5551,8 +5533,8 @@
         <v>144</v>
       </c>
       <c r="E62" s="324">
-        <f>'Cast &amp; Crew List'!K8</f>
-        <v>5</v>
+        <f>'Cast &amp; Crew List'!L8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="3:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5561,8 +5543,8 @@
         <v>145</v>
       </c>
       <c r="E63" s="326">
-        <f>'Cast &amp; Crew List'!K7</f>
-        <v>4</v>
+        <f>'Cast &amp; Crew List'!L7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="3:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -5570,9 +5552,9 @@
       <c r="D64" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="E64" s="327">
+      <c r="E64" s="327" t="e">
         <f>E63/E62</f>
-        <v>0.8</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.3">
@@ -5589,16 +5571,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A2:N2"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="51" orientation="landscape"/>
@@ -5642,28 +5624,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="397"/>
-      <c r="C1" s="398"/>
-      <c r="D1" s="398"/>
-      <c r="E1" s="399"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="401"/>
-      <c r="H1" s="401"/>
-      <c r="I1" s="401"/>
-      <c r="J1" s="401"/>
-      <c r="K1" s="401"/>
-      <c r="L1" s="401"/>
-      <c r="M1" s="396"/>
-      <c r="N1" s="401"/>
-      <c r="O1" s="417"/>
-      <c r="P1" s="417"/>
-      <c r="Q1" s="417"/>
-      <c r="R1" s="396"/>
-      <c r="S1" s="417"/>
-      <c r="T1" s="396"/>
-      <c r="U1" s="401"/>
-      <c r="V1" s="417"/>
-      <c r="W1" s="401"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="408"/>
+      <c r="D1" s="408"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="401"/>
+      <c r="G1" s="392"/>
+      <c r="H1" s="392"/>
+      <c r="I1" s="392"/>
+      <c r="J1" s="392"/>
+      <c r="K1" s="392"/>
+      <c r="L1" s="392"/>
+      <c r="M1" s="402"/>
+      <c r="N1" s="392"/>
+      <c r="O1" s="415"/>
+      <c r="P1" s="415"/>
+      <c r="Q1" s="415"/>
+      <c r="R1" s="402"/>
+      <c r="S1" s="415"/>
+      <c r="T1" s="402"/>
+      <c r="U1" s="392"/>
+      <c r="V1" s="415"/>
+      <c r="W1" s="392"/>
     </row>
     <row r="2" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
@@ -5733,7 +5715,7 @@
       <c r="R5" s="112"/>
       <c r="S5" s="112"/>
       <c r="T5" s="112" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -5745,46 +5727,46 @@
         <v>7</v>
       </c>
       <c r="C6" s="271" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D6" s="271" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E6" s="272" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F6" s="273" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G6" s="276" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H6" s="369" t="s">
         <v>61</v>
       </c>
       <c r="I6" s="276" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="J6" s="276" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="K6" s="274" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="L6" s="274" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="274" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="N6" s="274" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="O6" s="274" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="P6" s="274" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="Q6" s="274" t="s">
         <v>168</v>
@@ -5796,7 +5778,7 @@
         <v>45</v>
       </c>
       <c r="T6" s="274" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="U6" s="274" t="s">
         <v>41</v>
@@ -8330,7 +8312,7 @@
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.3">
       <c r="E108" s="108" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F108" s="88"/>
       <c r="G108" s="297">
@@ -8360,7 +8342,7 @@
     </row>
     <row r="111" spans="2:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E111" s="109" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G111" s="99">
         <f>SUM(G7:G107)</f>
@@ -8380,11 +8362,11 @@
       <c r="U112" s="3"/>
     </row>
     <row r="115" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E115" s="402" t="s">
+      <c r="E115" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="F115" s="392"/>
-      <c r="G115" s="393"/>
+      <c r="F115" s="404"/>
+      <c r="G115" s="405"/>
       <c r="J115" s="127" t="s">
         <v>56</v>
       </c>
@@ -8513,10 +8495,10 @@
     </row>
     <row r="125" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E125" s="167" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F125" s="161" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G125" s="39" t="s">
         <v>32</v>
@@ -8525,10 +8507,10 @@
         <v>53</v>
       </c>
       <c r="I125" s="39" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J125" s="39" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="K125" s="39" t="s">
         <v>15</v>
@@ -8828,31 +8810,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="397"/>
-      <c r="C1" s="413"/>
-      <c r="D1" s="396"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="414"/>
-      <c r="G1" s="414"/>
-      <c r="H1" s="414"/>
-      <c r="I1" s="415"/>
-      <c r="J1" s="396"/>
-      <c r="K1" s="396"/>
-      <c r="L1" s="396"/>
-      <c r="M1" s="396"/>
-      <c r="N1" s="396"/>
-      <c r="O1" s="396"/>
-      <c r="P1" s="417"/>
-      <c r="Q1" s="396"/>
-      <c r="R1" s="396"/>
-      <c r="S1" s="396"/>
-      <c r="T1" s="396"/>
-      <c r="U1" s="396"/>
-      <c r="V1" s="401"/>
-      <c r="W1" s="417"/>
-      <c r="X1" s="417"/>
-      <c r="Y1" s="401"/>
-      <c r="Z1" s="401"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="411"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="401"/>
+      <c r="F1" s="412"/>
+      <c r="G1" s="412"/>
+      <c r="H1" s="412"/>
+      <c r="I1" s="413"/>
+      <c r="J1" s="402"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="402"/>
+      <c r="M1" s="402"/>
+      <c r="N1" s="402"/>
+      <c r="O1" s="402"/>
+      <c r="P1" s="415"/>
+      <c r="Q1" s="402"/>
+      <c r="R1" s="402"/>
+      <c r="S1" s="402"/>
+      <c r="T1" s="402"/>
+      <c r="U1" s="402"/>
+      <c r="V1" s="392"/>
+      <c r="W1" s="415"/>
+      <c r="X1" s="415"/>
+      <c r="Y1" s="392"/>
+      <c r="Z1" s="392"/>
     </row>
     <row r="2" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
@@ -8931,22 +8913,22 @@
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
       <c r="D7" s="208" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H7" s="209" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I7" s="210" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="K7" s="208" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="L7" s="208" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:27" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8954,7 +8936,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="79" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>52</v>
@@ -8963,40 +8945,40 @@
         <v>11</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G8" s="51" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="R8" s="12" t="s">
         <v>168</v>
@@ -9008,7 +8990,7 @@
         <v>45</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="V8" s="12" t="s">
         <v>41</v>
@@ -9017,7 +8999,7 @@
         <v>46</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
@@ -9811,17 +9793,17 @@
       <c r="M34" s="14"/>
     </row>
     <row r="37" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="D37" s="402" t="s">
+      <c r="D37" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="392"/>
-      <c r="F37" s="393"/>
+      <c r="E37" s="404"/>
+      <c r="F37" s="405"/>
       <c r="G37" s="8"/>
-      <c r="J37" s="402" t="s">
+      <c r="J37" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="K37" s="392"/>
-      <c r="L37" s="393"/>
+      <c r="K37" s="404"/>
+      <c r="L37" s="405"/>
     </row>
     <row r="38" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D38" s="16" t="s">
@@ -9941,7 +9923,7 @@
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G48" s="162" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H48" s="162" t="s">
         <v>32</v>
@@ -9955,7 +9937,7 @@
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G49" s="46" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H49" s="46">
         <f>SUMIF($J$9:$J$29,G49,$F$9:$F$29)</f>
@@ -9972,7 +9954,7 @@
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G50" s="46" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H50" s="46">
         <f>SUMIF($J$9:$J$29,G50,$F$9:$F$29)</f>
@@ -9989,7 +9971,7 @@
     </row>
     <row r="51" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="97" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H51" s="97">
         <f>SUMIF($J$9:$J$29,G51,$F$9:$F$29)</f>
@@ -10133,31 +10115,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="397"/>
-      <c r="C1" s="413"/>
-      <c r="D1" s="396"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="414"/>
-      <c r="G1" s="414"/>
-      <c r="H1" s="414"/>
-      <c r="I1" s="415"/>
-      <c r="J1" s="396"/>
-      <c r="K1" s="396"/>
-      <c r="L1" s="396"/>
-      <c r="M1" s="396"/>
-      <c r="N1" s="396"/>
-      <c r="O1" s="396"/>
-      <c r="P1" s="417"/>
-      <c r="Q1" s="396"/>
-      <c r="R1" s="396"/>
-      <c r="S1" s="396"/>
-      <c r="T1" s="396"/>
-      <c r="U1" s="396"/>
-      <c r="V1" s="401"/>
-      <c r="W1" s="417"/>
-      <c r="X1" s="417"/>
-      <c r="Y1" s="401"/>
-      <c r="Z1" s="401"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="411"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="401"/>
+      <c r="F1" s="412"/>
+      <c r="G1" s="412"/>
+      <c r="H1" s="412"/>
+      <c r="I1" s="413"/>
+      <c r="J1" s="402"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="402"/>
+      <c r="M1" s="402"/>
+      <c r="N1" s="402"/>
+      <c r="O1" s="402"/>
+      <c r="P1" s="415"/>
+      <c r="Q1" s="402"/>
+      <c r="R1" s="402"/>
+      <c r="S1" s="402"/>
+      <c r="T1" s="402"/>
+      <c r="U1" s="402"/>
+      <c r="V1" s="392"/>
+      <c r="W1" s="415"/>
+      <c r="X1" s="415"/>
+      <c r="Y1" s="392"/>
+      <c r="Z1" s="392"/>
     </row>
     <row r="2" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
@@ -10236,22 +10218,22 @@
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
       <c r="D7" s="208" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H7" s="209" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I7" s="210" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="K7" s="208" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="L7" s="208" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:27" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10259,7 +10241,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="79" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>52</v>
@@ -10268,40 +10250,40 @@
         <v>11</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G8" s="51" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="R8" s="12" t="s">
         <v>168</v>
@@ -10313,7 +10295,7 @@
         <v>45</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="V8" s="12" t="s">
         <v>41</v>
@@ -10322,7 +10304,7 @@
         <v>46</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
@@ -11116,17 +11098,17 @@
       <c r="M34" s="14"/>
     </row>
     <row r="37" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="D37" s="402" t="s">
+      <c r="D37" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="392"/>
-      <c r="F37" s="393"/>
+      <c r="E37" s="404"/>
+      <c r="F37" s="405"/>
       <c r="G37" s="8"/>
-      <c r="J37" s="402" t="s">
+      <c r="J37" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="K37" s="392"/>
-      <c r="L37" s="393"/>
+      <c r="K37" s="404"/>
+      <c r="L37" s="405"/>
     </row>
     <row r="38" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D38" s="16" t="s">
@@ -11246,7 +11228,7 @@
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G48" s="162" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H48" s="162" t="s">
         <v>32</v>
@@ -11260,7 +11242,7 @@
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G49" s="46" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H49" s="46">
         <f>SUMIF($J$9:$J$29,G49,$F$9:$F$29)</f>
@@ -11277,7 +11259,7 @@
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G50" s="46" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H50" s="46">
         <f>SUMIF($J$9:$J$29,G50,$F$9:$F$29)</f>
@@ -11294,7 +11276,7 @@
     </row>
     <row r="51" spans="7:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="97" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H51" s="97">
         <f>SUMIF($J$9:$J$29,G51,$F$9:$F$29)</f>
@@ -11421,42 +11403,42 @@
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="H1" s="21" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AB1" s="39" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
         <v>59</v>
@@ -11468,94 +11450,94 @@
         <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="V2" s="8" t="s">
         <v>59</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="H3">
         <f>Overview!C13</f>
         <v>0</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E4" t="s">
         <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="G4" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="H4" s="32">
         <f>Overview!C16</f>
         <v>0</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -11563,13 +11545,13 @@
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F5" t="s">
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H5" s="32">
         <f>Overview!C17</f>
@@ -11579,51 +11561,51 @@
         <v>0</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="H6" s="32">
         <f>Overview!C18</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H7" s="32">
         <f>Overview!C19</f>
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="H8" s="32">
         <f>Overview!C20</f>
         <v>0</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H9" s="32">
         <f>Overview!C21</f>
@@ -11781,14 +11763,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="C2" s="411" t="s">
+      <c r="C2" s="391" t="s">
         <v>162</v>
       </c>
-      <c r="D2" s="401"/>
-      <c r="E2" s="401"/>
-      <c r="F2" s="401"/>
-      <c r="G2" s="401"/>
-      <c r="H2" s="401"/>
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
       <c r="I2" s="217"/>
     </row>
     <row r="3" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
@@ -11973,7 +11955,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:K94"/>
+  <dimension ref="B2:L94"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5.109375" style="8" customWidth="1"/>
@@ -11982,28 +11964,28 @@
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="30.33203125" customWidth="1"/>
-    <col min="11" max="11" width="21.33203125" customWidth="1"/>
+    <col min="8" max="9" width="41.33203125" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="C2" s="411" t="s">
+    <row r="2" spans="2:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="C2" s="391" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="401"/>
-      <c r="E2" s="401"/>
-      <c r="F2" s="401"/>
-      <c r="G2" s="401"/>
-      <c r="H2" s="401"/>
-    </row>
-    <row r="3" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
+    </row>
+    <row r="3" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C4" s="274" t="s">
         <v>193</v>
       </c>
@@ -12022,55 +12004,50 @@
       <c r="H4" s="276" t="s">
         <v>198</v>
       </c>
-      <c r="J4" s="331" t="s">
+      <c r="I4" s="276" t="s">
+        <v>303</v>
+      </c>
+      <c r="K4" s="331" t="s">
         <v>199</v>
       </c>
-      <c r="K4" s="332">
+      <c r="L4" s="332">
         <f>Overview!C9</f>
         <v>46068</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="221" t="s">
-        <v>200</v>
-      </c>
+      <c r="C5" s="221"/>
       <c r="D5" s="221"/>
       <c r="E5" s="117"/>
-      <c r="F5" s="104" t="s">
-        <v>201</v>
-      </c>
+      <c r="F5" s="104"/>
       <c r="G5" s="104"/>
       <c r="H5" s="36"/>
-      <c r="J5" s="333" t="s">
-        <v>202</v>
-      </c>
-      <c r="K5" s="334">
-        <f>K4-120</f>
+      <c r="I5" s="36"/>
+      <c r="K5" s="333" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" s="334">
+        <f>L4-120</f>
         <v>45948</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="8">
-        <f t="shared" ref="B6:B53" si="0">B5+1</f>
         <v>2</v>
       </c>
-      <c r="C6" s="221" t="s">
-        <v>203</v>
-      </c>
+      <c r="C6" s="221"/>
       <c r="D6" s="221"/>
       <c r="E6" s="117"/>
-      <c r="F6" s="104" t="s">
-        <v>201</v>
-      </c>
+      <c r="F6" s="104"/>
       <c r="G6" s="104"/>
       <c r="H6" s="36"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I6" s="36"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="8">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C7" s="221"/>
@@ -12079,17 +12056,17 @@
       <c r="F7" s="104"/>
       <c r="G7" s="104"/>
       <c r="H7" s="36"/>
-      <c r="J7" s="335" t="s">
-        <v>204</v>
-      </c>
-      <c r="K7" s="336">
+      <c r="I7" s="36"/>
+      <c r="K7" s="335" t="s">
+        <v>201</v>
+      </c>
+      <c r="L7" s="336">
         <f>COUNTIF(F5:F89,"Y")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="8">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C8" s="221"/>
@@ -12098,17 +12075,17 @@
       <c r="F8" s="104"/>
       <c r="G8" s="104"/>
       <c r="H8" s="36"/>
-      <c r="J8" s="337" t="s">
-        <v>205</v>
-      </c>
-      <c r="K8" s="338">
+      <c r="I8" s="36"/>
+      <c r="K8" s="337" t="s">
+        <v>202</v>
+      </c>
+      <c r="L8" s="338">
         <f>COUNTA(C5:C90)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="8">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C9" s="159"/>
@@ -12117,17 +12094,17 @@
       <c r="F9" s="104"/>
       <c r="G9" s="104"/>
       <c r="H9" s="36"/>
-      <c r="J9" s="339" t="s">
+      <c r="I9" s="36"/>
+      <c r="K9" s="339" t="s">
         <v>146</v>
       </c>
-      <c r="K9" s="340">
-        <f>K7/K8</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="340" t="e">
+        <f>L7/L8</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="8">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C10" s="221"/>
@@ -12136,10 +12113,10 @@
       <c r="F10" s="104"/>
       <c r="G10" s="104"/>
       <c r="H10" s="36"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I10" s="36"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C11" s="221"/>
@@ -12148,10 +12125,10 @@
       <c r="F11" s="104"/>
       <c r="G11" s="104"/>
       <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C12" s="221"/>
@@ -12160,10 +12137,10 @@
       <c r="F12" s="104"/>
       <c r="G12" s="104"/>
       <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I12" s="36"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C13" s="159"/>
@@ -12172,10 +12149,10 @@
       <c r="F13" s="104"/>
       <c r="G13" s="104"/>
       <c r="H13" s="36"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I13" s="36"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C14" s="221"/>
@@ -12184,10 +12161,10 @@
       <c r="F14" s="104"/>
       <c r="G14" s="104"/>
       <c r="H14" s="36"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I14" s="36"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="8">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C15" s="221"/>
@@ -12196,10 +12173,10 @@
       <c r="F15" s="104"/>
       <c r="G15" s="104"/>
       <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I15" s="36"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="8">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C16" s="221"/>
@@ -12208,10 +12185,10 @@
       <c r="F16" s="104"/>
       <c r="G16" s="104"/>
       <c r="H16" s="36"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="36"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="8">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C17" s="221"/>
@@ -12220,10 +12197,10 @@
       <c r="F17" s="104"/>
       <c r="G17" s="104"/>
       <c r="H17" s="36"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="36"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="8">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C18" s="159"/>
@@ -12232,10 +12209,10 @@
       <c r="F18" s="104"/>
       <c r="G18" s="104"/>
       <c r="H18" s="36"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="36"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="8">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C19" s="221"/>
@@ -12244,10 +12221,10 @@
       <c r="F19" s="104"/>
       <c r="G19" s="104"/>
       <c r="H19" s="36"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="36"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="8">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C20" s="159"/>
@@ -12256,10 +12233,10 @@
       <c r="F20" s="104"/>
       <c r="G20" s="104"/>
       <c r="H20" s="36"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="36"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="8">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C21" s="159"/>
@@ -12268,10 +12245,10 @@
       <c r="F21" s="104"/>
       <c r="G21" s="104"/>
       <c r="H21" s="36"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="36"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C22" s="221"/>
@@ -12280,10 +12257,10 @@
       <c r="F22" s="104"/>
       <c r="G22" s="104"/>
       <c r="H22" s="36"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="36"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
-        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C23" s="221"/>
@@ -12292,10 +12269,10 @@
       <c r="F23" s="104"/>
       <c r="G23" s="104"/>
       <c r="H23" s="36"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="36"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C24" s="159"/>
@@ -12304,10 +12281,10 @@
       <c r="F24" s="104"/>
       <c r="G24" s="104"/>
       <c r="H24" s="36"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="36"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C25" s="159"/>
@@ -12316,10 +12293,10 @@
       <c r="F25" s="104"/>
       <c r="G25" s="104"/>
       <c r="H25" s="36"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="36"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C26" s="159"/>
@@ -12328,10 +12305,10 @@
       <c r="F26" s="104"/>
       <c r="G26" s="104"/>
       <c r="H26" s="36"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="36"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C27" s="159"/>
@@ -12340,10 +12317,10 @@
       <c r="F27" s="104"/>
       <c r="G27" s="104"/>
       <c r="H27" s="36"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="36"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
-        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C28" s="159"/>
@@ -12352,10 +12329,10 @@
       <c r="F28" s="104"/>
       <c r="G28" s="104"/>
       <c r="H28" s="36"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="36"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C29" s="221"/>
@@ -12364,10 +12341,10 @@
       <c r="F29" s="104"/>
       <c r="G29" s="104"/>
       <c r="H29" s="36"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="36"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
-        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C30" s="221"/>
@@ -12376,10 +12353,10 @@
       <c r="F30" s="104"/>
       <c r="G30" s="104"/>
       <c r="H30" s="36"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="36"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="8">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C31" s="159"/>
@@ -12388,10 +12365,10 @@
       <c r="F31" s="104"/>
       <c r="G31" s="104"/>
       <c r="H31" s="36"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="36"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="8">
-        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C32" s="221"/>
@@ -12400,10 +12377,10 @@
       <c r="F32" s="104"/>
       <c r="G32" s="104"/>
       <c r="H32" s="36"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="36"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="8">
-        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C33" s="221"/>
@@ -12412,10 +12389,10 @@
       <c r="F33" s="104"/>
       <c r="G33" s="104"/>
       <c r="H33" s="36"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I33" s="36"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C34" s="221"/>
@@ -12424,10 +12401,10 @@
       <c r="F34" s="104"/>
       <c r="G34" s="104"/>
       <c r="H34" s="36"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="36"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="8">
-        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C35" s="221"/>
@@ -12436,10 +12413,10 @@
       <c r="F35" s="104"/>
       <c r="G35" s="104"/>
       <c r="H35" s="36"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I35" s="36"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="8">
-        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C36" s="221"/>
@@ -12448,10 +12425,10 @@
       <c r="F36" s="104"/>
       <c r="G36" s="104"/>
       <c r="H36" s="36"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I36" s="36"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="8">
-        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C37" s="221"/>
@@ -12460,10 +12437,10 @@
       <c r="F37" s="104"/>
       <c r="G37" s="104"/>
       <c r="H37" s="36"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I37" s="36"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="8">
-        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C38" s="221"/>
@@ -12472,10 +12449,10 @@
       <c r="F38" s="104"/>
       <c r="G38" s="104"/>
       <c r="H38" s="36"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I38" s="36"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="8">
-        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C39" s="221"/>
@@ -12484,10 +12461,10 @@
       <c r="F39" s="104"/>
       <c r="G39" s="104"/>
       <c r="H39" s="36"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I39" s="36"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="8">
-        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C40" s="221"/>
@@ -12496,10 +12473,10 @@
       <c r="F40" s="104"/>
       <c r="G40" s="104"/>
       <c r="H40" s="36"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I40" s="36"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41" s="8">
-        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C41" s="221"/>
@@ -12508,10 +12485,10 @@
       <c r="F41" s="104"/>
       <c r="G41" s="104"/>
       <c r="H41" s="36"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I41" s="36"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="8">
-        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="C42" s="221"/>
@@ -12520,10 +12497,10 @@
       <c r="F42" s="104"/>
       <c r="G42" s="104"/>
       <c r="H42" s="36"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I42" s="36"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="8">
-        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C43" s="221"/>
@@ -12532,10 +12509,10 @@
       <c r="F43" s="104"/>
       <c r="G43" s="104"/>
       <c r="H43" s="36"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I43" s="36"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="8">
-        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C44" s="159"/>
@@ -12544,10 +12521,10 @@
       <c r="F44" s="104"/>
       <c r="G44" s="104"/>
       <c r="H44" s="36"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I44" s="36"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="8">
-        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C45" s="159"/>
@@ -12556,10 +12533,10 @@
       <c r="F45" s="104"/>
       <c r="G45" s="104"/>
       <c r="H45" s="36"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I45" s="36"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="8">
-        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C46" s="159"/>
@@ -12568,10 +12545,10 @@
       <c r="F46" s="104"/>
       <c r="G46" s="104"/>
       <c r="H46" s="36"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I46" s="36"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="8">
-        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C47" s="221"/>
@@ -12580,10 +12557,10 @@
       <c r="F47" s="104"/>
       <c r="G47" s="104"/>
       <c r="H47" s="36"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I47" s="36"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="8">
-        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C48" s="159"/>
@@ -12592,10 +12569,10 @@
       <c r="F48" s="104"/>
       <c r="G48" s="104"/>
       <c r="H48" s="36"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="36"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49" s="8">
-        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C49" s="221"/>
@@ -12604,10 +12581,10 @@
       <c r="F49" s="104"/>
       <c r="G49" s="104"/>
       <c r="H49" s="36"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="36"/>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50" s="8">
-        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C50" s="221"/>
@@ -12616,10 +12593,10 @@
       <c r="F50" s="104"/>
       <c r="G50" s="104"/>
       <c r="H50" s="36"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="36"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="8">
-        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C51" s="221"/>
@@ -12628,10 +12605,10 @@
       <c r="F51" s="104"/>
       <c r="G51" s="104"/>
       <c r="H51" s="36"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I51" s="36"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="8">
-        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="C52" s="159"/>
@@ -12640,10 +12617,10 @@
       <c r="F52" s="104"/>
       <c r="G52" s="104"/>
       <c r="H52" s="36"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I52" s="36"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="8">
-        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C53" s="221"/>
@@ -12652,58 +12629,47 @@
       <c r="F53" s="104"/>
       <c r="G53" s="104"/>
       <c r="H53" s="36"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I53" s="36"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54" s="8">
-        <v>1</v>
-      </c>
-      <c r="C54" s="221" t="s">
-        <v>206</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C54" s="221"/>
       <c r="D54" s="221"/>
       <c r="E54" s="117"/>
-      <c r="F54" s="104" t="s">
-        <v>201</v>
-      </c>
+      <c r="F54" s="104"/>
       <c r="G54" s="104"/>
       <c r="H54" s="36"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I54" s="36"/>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55" s="8">
-        <f t="shared" ref="B55:B79" si="1">B54+1</f>
-        <v>2</v>
-      </c>
-      <c r="C55" s="221" t="s">
-        <v>207</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C55" s="221"/>
       <c r="D55" s="221"/>
       <c r="E55" s="117"/>
-      <c r="F55" s="104" t="s">
-        <v>201</v>
-      </c>
+      <c r="F55" s="104"/>
       <c r="G55" s="104"/>
       <c r="H55" s="36"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I55" s="36"/>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="8">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C56" s="159" t="s">
-        <v>208</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C56" s="159"/>
       <c r="D56" s="159"/>
       <c r="E56" s="117"/>
-      <c r="F56" s="104" t="s">
-        <v>209</v>
-      </c>
+      <c r="F56" s="104"/>
       <c r="G56" s="104"/>
       <c r="H56" s="36"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I56" s="36"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57" s="8">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C57" s="221"/>
       <c r="D57" s="221"/>
@@ -12711,11 +12677,11 @@
       <c r="F57" s="104"/>
       <c r="G57" s="104"/>
       <c r="H57" s="36"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="36"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="8">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="C58" s="221"/>
       <c r="D58" s="221"/>
@@ -12723,11 +12689,11 @@
       <c r="F58" s="104"/>
       <c r="G58" s="104"/>
       <c r="H58" s="36"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I58" s="36"/>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59" s="8">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C59" s="159"/>
       <c r="D59" s="159"/>
@@ -12735,11 +12701,11 @@
       <c r="F59" s="104"/>
       <c r="G59" s="104"/>
       <c r="H59" s="36"/>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="36"/>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60" s="8">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="C60" s="159"/>
       <c r="D60" s="159"/>
@@ -12747,11 +12713,11 @@
       <c r="F60" s="104"/>
       <c r="G60" s="104"/>
       <c r="H60" s="36"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I60" s="36"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="8">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C61" s="221"/>
       <c r="D61" s="221"/>
@@ -12759,11 +12725,11 @@
       <c r="F61" s="104"/>
       <c r="G61" s="104"/>
       <c r="H61" s="36"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I61" s="36"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="8">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="C62" s="221"/>
       <c r="D62" s="221"/>
@@ -12771,11 +12737,11 @@
       <c r="F62" s="104"/>
       <c r="G62" s="104"/>
       <c r="H62" s="36"/>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I62" s="36"/>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="8">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C63" s="221"/>
       <c r="D63" s="221"/>
@@ -12783,11 +12749,11 @@
       <c r="F63" s="104"/>
       <c r="G63" s="104"/>
       <c r="H63" s="36"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I63" s="36"/>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="8">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C64" s="221"/>
       <c r="D64" s="221"/>
@@ -12795,11 +12761,11 @@
       <c r="F64" s="104"/>
       <c r="G64" s="104"/>
       <c r="H64" s="36"/>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I64" s="36"/>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65" s="8">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C65" s="221"/>
       <c r="D65" s="221"/>
@@ -12807,11 +12773,11 @@
       <c r="F65" s="104"/>
       <c r="G65" s="104"/>
       <c r="H65" s="36"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I65" s="36"/>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66" s="8">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="C66" s="221"/>
       <c r="D66" s="221"/>
@@ -12819,11 +12785,11 @@
       <c r="F66" s="104"/>
       <c r="G66" s="104"/>
       <c r="H66" s="36"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I66" s="36"/>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67" s="8">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C67" s="221"/>
       <c r="D67" s="221"/>
@@ -12831,11 +12797,11 @@
       <c r="F67" s="104"/>
       <c r="G67" s="104"/>
       <c r="H67" s="36"/>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I67" s="36"/>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="8">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C68" s="221"/>
       <c r="D68" s="221"/>
@@ -12843,11 +12809,11 @@
       <c r="F68" s="104"/>
       <c r="G68" s="104"/>
       <c r="H68" s="36"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I68" s="36"/>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="8">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="C69" s="221"/>
       <c r="D69" s="221"/>
@@ -12855,11 +12821,11 @@
       <c r="F69" s="104"/>
       <c r="G69" s="104"/>
       <c r="H69" s="36"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I69" s="36"/>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="8">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="C70" s="221"/>
       <c r="D70" s="221"/>
@@ -12867,11 +12833,11 @@
       <c r="F70" s="104"/>
       <c r="G70" s="104"/>
       <c r="H70" s="36"/>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I70" s="36"/>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71" s="8">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C71" s="221"/>
       <c r="D71" s="221"/>
@@ -12879,11 +12845,11 @@
       <c r="F71" s="104"/>
       <c r="G71" s="104"/>
       <c r="H71" s="36"/>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I71" s="36"/>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72" s="8">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="C72" s="221"/>
       <c r="D72" s="221"/>
@@ -12891,11 +12857,11 @@
       <c r="F72" s="104"/>
       <c r="G72" s="104"/>
       <c r="H72" s="36"/>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I72" s="36"/>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73" s="8">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C73" s="221"/>
       <c r="D73" s="221"/>
@@ -12903,11 +12869,11 @@
       <c r="F73" s="104"/>
       <c r="G73" s="104"/>
       <c r="H73" s="36"/>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I73" s="36"/>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="8">
-        <f t="shared" si="1"/>
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C74" s="221"/>
       <c r="D74" s="221"/>
@@ -12915,11 +12881,11 @@
       <c r="F74" s="104"/>
       <c r="G74" s="104"/>
       <c r="H74" s="36"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I74" s="36"/>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75" s="8">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C75" s="221"/>
       <c r="D75" s="221"/>
@@ -12927,11 +12893,11 @@
       <c r="F75" s="104"/>
       <c r="G75" s="104"/>
       <c r="H75" s="36"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I75" s="36"/>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76" s="8">
-        <f t="shared" si="1"/>
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="C76" s="221"/>
       <c r="D76" s="221"/>
@@ -12939,11 +12905,11 @@
       <c r="F76" s="104"/>
       <c r="G76" s="104"/>
       <c r="H76" s="36"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I76" s="36"/>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="8">
-        <f t="shared" si="1"/>
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C77" s="221"/>
       <c r="D77" s="221"/>
@@ -12951,11 +12917,11 @@
       <c r="F77" s="104"/>
       <c r="G77" s="104"/>
       <c r="H77" s="36"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I77" s="36"/>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="8">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C78" s="221"/>
       <c r="D78" s="221"/>
@@ -12963,11 +12929,11 @@
       <c r="F78" s="104"/>
       <c r="G78" s="104"/>
       <c r="H78" s="36"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I78" s="36"/>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79" s="8">
-        <f t="shared" si="1"/>
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C79" s="221"/>
       <c r="D79" s="221"/>
@@ -12975,10 +12941,11 @@
       <c r="F79" s="104"/>
       <c r="G79" s="104"/>
       <c r="H79" s="36"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I79" s="36"/>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="8">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C80" s="221"/>
       <c r="D80" s="221"/>
@@ -12986,10 +12953,11 @@
       <c r="F80" s="104"/>
       <c r="G80" s="104"/>
       <c r="H80" s="36"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I80" s="36"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="8">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="C81" s="221"/>
       <c r="D81" s="221"/>
@@ -12997,10 +12965,11 @@
       <c r="F81" s="104"/>
       <c r="G81" s="104"/>
       <c r="H81" s="36"/>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I81" s="36"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="8">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C82" s="221"/>
       <c r="D82" s="221"/>
@@ -13008,10 +12977,11 @@
       <c r="F82" s="104"/>
       <c r="G82" s="104"/>
       <c r="H82" s="36"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I82" s="36"/>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="8">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="C83" s="221"/>
       <c r="D83" s="221"/>
@@ -13019,10 +12989,11 @@
       <c r="F83" s="104"/>
       <c r="G83" s="104"/>
       <c r="H83" s="36"/>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I83" s="36"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="8">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C84" s="221"/>
       <c r="D84" s="221"/>
@@ -13030,10 +13001,11 @@
       <c r="F84" s="104"/>
       <c r="G84" s="104"/>
       <c r="H84" s="36"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I84" s="36"/>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="8">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C85" s="221"/>
       <c r="D85" s="221"/>
@@ -13041,10 +13013,11 @@
       <c r="F85" s="104"/>
       <c r="G85" s="104"/>
       <c r="H85" s="36"/>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I85" s="36"/>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="8">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="C86" s="221"/>
       <c r="D86" s="221"/>
@@ -13052,10 +13025,11 @@
       <c r="F86" s="104"/>
       <c r="G86" s="104"/>
       <c r="H86" s="36"/>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I86" s="36"/>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="8">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C87" s="221"/>
       <c r="D87" s="221"/>
@@ -13063,10 +13037,11 @@
       <c r="F87" s="104"/>
       <c r="G87" s="104"/>
       <c r="H87" s="36"/>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I87" s="36"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="8">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="C88" s="221"/>
       <c r="D88" s="221"/>
@@ -13074,10 +13049,11 @@
       <c r="F88" s="104"/>
       <c r="G88" s="104"/>
       <c r="H88" s="36"/>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I88" s="36"/>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89" s="8">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="C89" s="221"/>
       <c r="D89" s="221"/>
@@ -13085,8 +13061,9 @@
       <c r="F89" s="104"/>
       <c r="G89" s="104"/>
       <c r="H89" s="36"/>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I89" s="36"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F94" s="299"/>
       <c r="G94" s="299"/>
     </row>
@@ -13160,46 +13137,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="397"/>
-      <c r="C1" s="398"/>
-      <c r="D1" s="398"/>
-      <c r="E1" s="399"/>
-      <c r="F1" s="399"/>
-      <c r="G1" s="399"/>
-      <c r="H1" s="400"/>
-      <c r="I1" s="400"/>
-      <c r="J1" s="400"/>
-      <c r="K1" s="396"/>
-      <c r="L1" s="400"/>
-      <c r="M1" s="400"/>
-      <c r="N1" s="395"/>
-      <c r="O1" s="395"/>
-      <c r="P1" s="395"/>
-      <c r="Q1" s="395"/>
-      <c r="R1" s="395"/>
-      <c r="S1" s="395"/>
-      <c r="T1" s="395"/>
-      <c r="U1" s="395"/>
-      <c r="V1" s="395"/>
-      <c r="W1" s="395"/>
-      <c r="X1" s="395"/>
-      <c r="Y1" s="395"/>
-      <c r="Z1" s="395"/>
-      <c r="AA1" s="395"/>
-      <c r="AB1" s="395"/>
-      <c r="AC1" s="395"/>
-      <c r="AD1" s="395"/>
-      <c r="AE1" s="395"/>
-      <c r="AF1" s="395"/>
-      <c r="AG1" s="401"/>
-      <c r="AH1" s="396"/>
-      <c r="AI1" s="401"/>
-      <c r="AJ1" s="401"/>
-      <c r="AK1" s="396"/>
-      <c r="AL1" s="401"/>
-      <c r="AM1" s="401"/>
-      <c r="AN1" s="401"/>
-      <c r="AO1" s="401"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="408"/>
+      <c r="D1" s="408"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="401"/>
+      <c r="I1" s="401"/>
+      <c r="J1" s="401"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="401"/>
+      <c r="M1" s="401"/>
+      <c r="N1" s="410"/>
+      <c r="O1" s="410"/>
+      <c r="P1" s="410"/>
+      <c r="Q1" s="410"/>
+      <c r="R1" s="410"/>
+      <c r="S1" s="410"/>
+      <c r="T1" s="410"/>
+      <c r="U1" s="410"/>
+      <c r="V1" s="410"/>
+      <c r="W1" s="410"/>
+      <c r="X1" s="410"/>
+      <c r="Y1" s="410"/>
+      <c r="Z1" s="410"/>
+      <c r="AA1" s="410"/>
+      <c r="AB1" s="410"/>
+      <c r="AC1" s="410"/>
+      <c r="AD1" s="410"/>
+      <c r="AE1" s="410"/>
+      <c r="AF1" s="410"/>
+      <c r="AG1" s="392"/>
+      <c r="AH1" s="402"/>
+      <c r="AI1" s="392"/>
+      <c r="AJ1" s="392"/>
+      <c r="AK1" s="402"/>
+      <c r="AL1" s="392"/>
+      <c r="AM1" s="392"/>
+      <c r="AN1" s="392"/>
+      <c r="AO1" s="392"/>
       <c r="AP1" s="113"/>
       <c r="AQ1" s="341"/>
       <c r="AR1" s="341"/>
@@ -13253,12 +13230,12 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="23"/>
-      <c r="I3" s="412" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="400"/>
-      <c r="K3" s="396"/>
-      <c r="L3" s="400"/>
+      <c r="I3" s="400" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="401"/>
+      <c r="K3" s="402"/>
+      <c r="L3" s="401"/>
       <c r="V3" s="8"/>
       <c r="W3" s="8"/>
       <c r="X3" s="8"/>
@@ -13400,11 +13377,11 @@
       <c r="AM7" s="8"/>
       <c r="AN7" s="8"/>
       <c r="AO7" s="8"/>
-      <c r="AT7" s="391" t="s">
+      <c r="AT7" s="406" t="s">
         <v>5</v>
       </c>
-      <c r="AU7" s="392"/>
-      <c r="AV7" s="393"/>
+      <c r="AU7" s="404"/>
+      <c r="AV7" s="405"/>
       <c r="AW7" s="344"/>
       <c r="AY7" s="345" t="s">
         <v>6</v>
@@ -17748,20 +17725,20 @@
       <c r="T62" s="46"/>
       <c r="U62" s="46"/>
       <c r="V62" s="46"/>
-      <c r="W62" s="402" t="s">
+      <c r="W62" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="X62" s="392"/>
-      <c r="Y62" s="393"/>
+      <c r="X62" s="404"/>
+      <c r="Y62" s="405"/>
       <c r="Z62" s="46"/>
       <c r="AA62" s="8"/>
-      <c r="AB62" s="402" t="s">
+      <c r="AB62" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="AC62" s="392"/>
-      <c r="AD62" s="392"/>
-      <c r="AE62" s="392"/>
-      <c r="AF62" s="393"/>
+      <c r="AC62" s="404"/>
+      <c r="AD62" s="404"/>
+      <c r="AE62" s="404"/>
+      <c r="AF62" s="405"/>
       <c r="AG62" s="8"/>
       <c r="AY62" s="357"/>
     </row>
@@ -18804,11 +18781,11 @@
     <mergeCell ref="B1:AO1"/>
   </mergeCells>
   <conditionalFormatting sqref="K34:K44">
-    <cfRule type="cellIs" dxfId="198" priority="476" operator="equal">
+    <cfRule type="cellIs" dxfId="198" priority="475" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="197" priority="476" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="475" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48:K54">
@@ -18820,31 +18797,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="cellIs" dxfId="194" priority="497" operator="equal">
-      <formula>"YES"</formula>
+    <cfRule type="cellIs" dxfId="194" priority="495" operator="equal">
+      <formula>"NO-OOS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="193" priority="496" operator="equal">
       <formula>"NO-CO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="495" operator="equal">
-      <formula>"NO-OOS"</formula>
+    <cfRule type="cellIs" dxfId="192" priority="497" operator="equal">
+      <formula>"YES"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="191" priority="498" operator="equal">
       <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB63">
-    <cfRule type="cellIs" dxfId="190" priority="493" operator="equal">
-      <formula>"NO"</formula>
+    <cfRule type="cellIs" dxfId="190" priority="490" operator="equal">
+      <formula>"NO-OOS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="492" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="491" operator="equal">
+      <formula>"NO-CO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="492" operator="equal">
       <formula>"YES"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="490" operator="equal">
-      <formula>"NO-OOS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="491" operator="equal">
-      <formula>"NO-CO"</formula>
+    <cfRule type="cellIs" dxfId="187" priority="493" operator="equal">
+      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG9:AG54">
@@ -18893,11 +18870,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK23 AN23">
-    <cfRule type="cellIs" dxfId="175" priority="529" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="528" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="529" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="528" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK25 AN25">
@@ -18949,19 +18926,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK45:AK54 AN45:AN54">
-    <cfRule type="cellIs" dxfId="161" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="124" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="125" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="124" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK9:AN10 AK27:AN27">
-    <cfRule type="cellIs" dxfId="159" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="3" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="158" priority="4" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="3" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL11:AM26 B55:G55">
@@ -18989,11 +18966,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL43:AN43">
-    <cfRule type="cellIs" dxfId="151" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="5" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="6" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="5" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN11:AN14">
@@ -19005,11 +18982,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ9:AQ54">
-    <cfRule type="cellIs" dxfId="147" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="1" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="146" priority="2" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="1" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
@@ -19059,33 +19036,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="397"/>
-      <c r="C1" s="413"/>
-      <c r="D1" s="396"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="414"/>
-      <c r="H1" s="414"/>
-      <c r="I1" s="414"/>
-      <c r="J1" s="414"/>
-      <c r="K1" s="414"/>
-      <c r="L1" s="414"/>
-      <c r="M1" s="415"/>
-      <c r="N1" s="415"/>
-      <c r="O1" s="416"/>
-      <c r="P1" s="396"/>
-      <c r="Q1" s="396"/>
-      <c r="R1" s="396"/>
-      <c r="S1" s="396"/>
-      <c r="T1" s="417"/>
-      <c r="U1" s="417"/>
-      <c r="V1" s="396"/>
-      <c r="W1" s="396"/>
-      <c r="X1" s="396"/>
-      <c r="Y1" s="396"/>
-      <c r="Z1" s="417"/>
-      <c r="AA1" s="401"/>
-      <c r="AB1" s="417"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="411"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="401"/>
+      <c r="F1" s="401"/>
+      <c r="G1" s="412"/>
+      <c r="H1" s="412"/>
+      <c r="I1" s="412"/>
+      <c r="J1" s="412"/>
+      <c r="K1" s="412"/>
+      <c r="L1" s="412"/>
+      <c r="M1" s="413"/>
+      <c r="N1" s="413"/>
+      <c r="O1" s="414"/>
+      <c r="P1" s="402"/>
+      <c r="Q1" s="402"/>
+      <c r="R1" s="402"/>
+      <c r="S1" s="402"/>
+      <c r="T1" s="415"/>
+      <c r="U1" s="415"/>
+      <c r="V1" s="402"/>
+      <c r="W1" s="402"/>
+      <c r="X1" s="402"/>
+      <c r="Y1" s="402"/>
+      <c r="Z1" s="415"/>
+      <c r="AA1" s="392"/>
+      <c r="AB1" s="415"/>
       <c r="AC1" s="113"/>
       <c r="AD1" s="113"/>
       <c r="AE1" s="113"/>
@@ -19202,7 +19179,7 @@
       <c r="C7" s="101"/>
       <c r="D7" s="101"/>
       <c r="F7" s="27" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K7" s="119"/>
       <c r="P7" s="119"/>
@@ -19223,31 +19200,31 @@
     </row>
     <row r="8" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B8" s="285" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="277" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D8" s="284" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="287" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F8" s="279" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G8" s="288" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H8" s="288" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I8" s="288" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J8" s="288" t="s">
         <v>103</v>
@@ -19256,7 +19233,7 @@
         <v>61</v>
       </c>
       <c r="L8" s="288" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M8" s="290" t="s">
         <v>14</v>
@@ -19268,25 +19245,25 @@
         <v>16</v>
       </c>
       <c r="P8" s="315" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Q8" s="315" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="R8" s="315" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="S8" s="315" t="s">
         <v>39</v>
       </c>
       <c r="T8" s="315" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="U8" s="315" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="V8" s="315" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="W8" s="315" t="s">
         <v>168</v>
@@ -19298,7 +19275,7 @@
         <v>45</v>
       </c>
       <c r="Z8" s="315" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AA8" s="315" t="s">
         <v>41</v>
@@ -20810,16 +20787,16 @@
       <c r="F43" s="28"/>
       <c r="G43" s="291"/>
       <c r="H43" s="291" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="I43" s="291" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="J43" s="291" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="K43" s="291" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L43" s="72">
         <f>SUM(L9:L39)</f>
@@ -20851,11 +20828,11 @@
       <c r="F47" s="128"/>
       <c r="G47" s="129"/>
       <c r="H47" s="8"/>
-      <c r="J47" s="402" t="s">
+      <c r="J47" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="K47" s="392"/>
-      <c r="L47" s="393"/>
+      <c r="K47" s="404"/>
+      <c r="L47" s="405"/>
       <c r="M47" s="8"/>
       <c r="N47" s="8"/>
       <c r="O47" s="8"/>
@@ -21141,27 +21118,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="397"/>
-      <c r="B1" s="398"/>
-      <c r="C1" s="398"/>
-      <c r="D1" s="398"/>
-      <c r="E1" s="399"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="400"/>
-      <c r="H1" s="401"/>
-      <c r="I1" s="396"/>
-      <c r="J1" s="399"/>
-      <c r="K1" s="396"/>
-      <c r="L1" s="396"/>
-      <c r="M1" s="395"/>
-      <c r="N1" s="395"/>
-      <c r="O1" s="395"/>
-      <c r="P1" s="395"/>
-      <c r="Q1" s="395"/>
-      <c r="R1" s="395"/>
-      <c r="S1" s="395"/>
-      <c r="T1" s="395"/>
-      <c r="U1" s="395"/>
+      <c r="A1" s="407"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="408"/>
+      <c r="D1" s="408"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="401"/>
+      <c r="G1" s="401"/>
+      <c r="H1" s="392"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="402"/>
+      <c r="M1" s="410"/>
+      <c r="N1" s="410"/>
+      <c r="O1" s="410"/>
+      <c r="P1" s="410"/>
+      <c r="Q1" s="410"/>
+      <c r="R1" s="410"/>
+      <c r="S1" s="410"/>
+      <c r="T1" s="410"/>
+      <c r="U1" s="410"/>
       <c r="V1" s="113"/>
       <c r="W1" s="113"/>
       <c r="X1" s="113"/>
@@ -21229,12 +21206,12 @@
       <c r="Q3" s="222"/>
       <c r="R3" s="222"/>
       <c r="S3" s="222"/>
-      <c r="V3" s="394" t="s">
-        <v>227</v>
-      </c>
-      <c r="W3" s="395"/>
-      <c r="X3" s="396"/>
-      <c r="Y3" s="396"/>
+      <c r="V3" s="416" t="s">
+        <v>220</v>
+      </c>
+      <c r="W3" s="410"/>
+      <c r="X3" s="402"/>
+      <c r="Y3" s="402"/>
       <c r="AD3" s="32"/>
       <c r="AE3" s="32"/>
       <c r="AI3" s="32"/>
@@ -21250,12 +21227,12 @@
       <c r="J4" s="112"/>
       <c r="K4" s="112"/>
       <c r="L4" s="112"/>
-      <c r="V4" s="394" t="s">
-        <v>228</v>
-      </c>
-      <c r="W4" s="395"/>
-      <c r="X4" s="396"/>
-      <c r="Y4" s="396"/>
+      <c r="V4" s="416" t="s">
+        <v>221</v>
+      </c>
+      <c r="W4" s="410"/>
+      <c r="X4" s="402"/>
+      <c r="Y4" s="402"/>
       <c r="Z4" s="5"/>
       <c r="AA4" s="173"/>
       <c r="AC4" s="4"/>
@@ -21280,7 +21257,7 @@
       <c r="K5" s="112"/>
       <c r="L5" s="112"/>
       <c r="Q5" s="174" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="R5" s="174"/>
       <c r="S5" s="174"/>
@@ -21330,36 +21307,36 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="M7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N7" s="176"/>
       <c r="O7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="P7" s="176"/>
       <c r="Q7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="S7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="T7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="W7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="AB7" s="176" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="AI7" s="176" t="s">
-        <v>230</v>
-      </c>
-      <c r="AK7" s="391" t="s">
+        <v>223</v>
+      </c>
+      <c r="AK7" s="406" t="s">
         <v>5</v>
       </c>
-      <c r="AL7" s="392"/>
-      <c r="AM7" s="393"/>
+      <c r="AL7" s="404"/>
+      <c r="AM7" s="405"/>
       <c r="AP7" s="345" t="s">
         <v>6</v>
       </c>
@@ -21369,10 +21346,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E8" s="79" t="s">
         <v>52</v>
@@ -21381,46 +21358,46 @@
         <v>11</v>
       </c>
       <c r="G8" s="254" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="N8" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="O8" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="P8" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="R8" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="S8" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="T8" s="44" t="s">
         <v>234</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="N8" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="O8" s="48" t="s">
-        <v>216</v>
-      </c>
-      <c r="P8" s="48" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>238</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>240</v>
-      </c>
-      <c r="T8" s="44" t="s">
-        <v>241</v>
       </c>
       <c r="U8" s="44" t="s">
         <v>32</v>
@@ -21432,10 +21409,10 @@
         <v>34</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="Z8" s="12" t="s">
         <v>38</v>
@@ -21444,16 +21421,16 @@
         <v>39</v>
       </c>
       <c r="AB8" s="12" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AC8" s="79" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AD8" s="12" t="s">
         <v>41</v>
       </c>
       <c r="AE8" s="12" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AF8" s="12" t="s">
         <v>43</v>
@@ -21471,7 +21448,7 @@
         <v>49</v>
       </c>
       <c r="AL8" s="350" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AM8" s="350" t="s">
         <v>51</v>
@@ -23849,17 +23826,17 @@
         <v>52</v>
       </c>
       <c r="F45" s="167" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G45" s="167"/>
       <c r="H45" s="167" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I45" s="167" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="J45" s="167" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="K45" s="167" t="s">
         <v>32</v>
@@ -23914,19 +23891,19 @@
       </c>
       <c r="M47" s="8"/>
       <c r="N47" s="8"/>
-      <c r="O47" s="402" t="s">
+      <c r="O47" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="P47" s="392"/>
-      <c r="Q47" s="392"/>
-      <c r="R47" s="393"/>
+      <c r="P47" s="404"/>
+      <c r="Q47" s="404"/>
+      <c r="R47" s="405"/>
       <c r="S47" s="8"/>
       <c r="T47" s="46"/>
-      <c r="U47" s="403" t="s">
+      <c r="U47" s="417" t="s">
         <v>56</v>
       </c>
-      <c r="V47" s="392"/>
-      <c r="W47" s="393"/>
+      <c r="V47" s="404"/>
+      <c r="W47" s="405"/>
       <c r="X47" s="187"/>
       <c r="Y47" s="188"/>
       <c r="Z47" s="188"/>
@@ -23967,7 +23944,7 @@
         <v>59</v>
       </c>
       <c r="R48" s="190" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="S48" s="46"/>
       <c r="T48" s="89"/>
@@ -24681,11 +24658,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J40:L40">
-    <cfRule type="cellIs" dxfId="123" priority="475" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="474" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="122" priority="475" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="474" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:L39">
@@ -24697,11 +24674,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O48">
-    <cfRule type="cellIs" dxfId="119" priority="487" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="486" operator="equal">
+      <formula>"NO-OOS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="487" operator="equal">
       <formula>"NO-CO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="486" operator="equal">
-      <formula>"NO-OOS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="117" priority="488" operator="equal">
       <formula>"YES"</formula>
@@ -24711,25 +24688,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U48">
-    <cfRule type="cellIs" dxfId="115" priority="483" operator="equal">
-      <formula>"YES"</formula>
+    <cfRule type="cellIs" dxfId="115" priority="481" operator="equal">
+      <formula>"NO-OOS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="114" priority="482" operator="equal">
       <formula>"NO-CO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="481" operator="equal">
-      <formula>"NO-OOS"</formula>
+    <cfRule type="cellIs" dxfId="113" priority="483" operator="equal">
+      <formula>"YES"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="112" priority="484" operator="equal">
       <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z9:Z39">
-    <cfRule type="cellIs" dxfId="111" priority="295" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="294" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="295" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="294" operator="equal">
-      <formula>"N/A"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="109" priority="296" operator="equal">
       <formula>"NO"</formula>
@@ -24749,11 +24726,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC60">
-    <cfRule type="cellIs" dxfId="105" priority="458" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="456" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="458" operator="equal">
       <formula>"NO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="456" operator="equal">
-      <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC60:AH60">
@@ -24780,11 +24757,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD60">
-    <cfRule type="cellIs" dxfId="98" priority="461" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="459" operator="equal">
+      <formula>"NO-OOS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="461" operator="equal">
       <formula>"NO-TX"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="459" operator="equal">
-      <formula>"NO-OOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE16:AE25">
@@ -24804,19 +24781,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE10:AG10">
-    <cfRule type="cellIs" dxfId="92" priority="269" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="268" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="269" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="268" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE14:AG14">
-    <cfRule type="cellIs" dxfId="90" priority="273" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="272" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="273" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="272" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE26:AG38">
@@ -24836,11 +24813,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE11:AH11 AE12:AG12 AE13:AH13">
-    <cfRule type="cellIs" dxfId="84" priority="285" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="284" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="285" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="284" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE15:AH15">
@@ -24852,11 +24829,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE38:AH40">
-    <cfRule type="cellIs" dxfId="80" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="16" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="16" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE60:AH60">
@@ -24865,35 +24842,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF16:AG16">
-    <cfRule type="cellIs" dxfId="77" priority="271" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="270" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="271" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="270" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF23:AG25">
-    <cfRule type="cellIs" dxfId="75" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="65" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="66" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="65" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF17:AH22">
-    <cfRule type="cellIs" dxfId="73" priority="279" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="278" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="279" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="278" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH9:AH38">
-    <cfRule type="cellIs" dxfId="71" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="20" operator="equal">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="21" operator="equal">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="20" operator="equal">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -25075,7 +25052,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="79" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>52</v>
@@ -25087,13 +25064,13 @@
         <v>12</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J7" s="48" t="s">
         <v>103</v>
@@ -25102,10 +25079,10 @@
         <v>61</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M7" s="67" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N7" s="204" t="s">
         <v>15</v>
@@ -25114,25 +25091,25 @@
         <v>16</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>39</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>168</v>
@@ -25144,7 +25121,7 @@
         <v>45</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AA7" s="12" t="s">
         <v>41</v>
@@ -26662,17 +26639,17 @@
       <c r="AA45" s="32"/>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="D46" s="402" t="s">
+      <c r="D46" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="392"/>
-      <c r="F46" s="393"/>
+      <c r="E46" s="404"/>
+      <c r="F46" s="405"/>
       <c r="G46" s="8"/>
-      <c r="I46" s="402" t="s">
+      <c r="I46" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="J46" s="392"/>
-      <c r="K46" s="393"/>
+      <c r="J46" s="404"/>
+      <c r="K46" s="405"/>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
       <c r="N46" s="8"/>
@@ -26948,29 +26925,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="397"/>
-      <c r="C1" s="413"/>
-      <c r="D1" s="396"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="414"/>
-      <c r="G1" s="414"/>
-      <c r="H1" s="414"/>
-      <c r="I1" s="415"/>
-      <c r="J1" s="396"/>
-      <c r="K1" s="396"/>
-      <c r="L1" s="417"/>
-      <c r="M1" s="396"/>
-      <c r="N1" s="396"/>
-      <c r="O1" s="417"/>
-      <c r="P1" s="417"/>
-      <c r="Q1" s="396"/>
-      <c r="R1" s="396"/>
-      <c r="S1" s="396"/>
-      <c r="T1" s="396"/>
-      <c r="U1" s="417"/>
-      <c r="V1" s="401"/>
-      <c r="W1" s="417"/>
-      <c r="X1" s="401"/>
+      <c r="B1" s="407"/>
+      <c r="C1" s="411"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="401"/>
+      <c r="F1" s="412"/>
+      <c r="G1" s="412"/>
+      <c r="H1" s="412"/>
+      <c r="I1" s="413"/>
+      <c r="J1" s="402"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="415"/>
+      <c r="M1" s="402"/>
+      <c r="N1" s="402"/>
+      <c r="O1" s="415"/>
+      <c r="P1" s="415"/>
+      <c r="Q1" s="402"/>
+      <c r="R1" s="402"/>
+      <c r="S1" s="402"/>
+      <c r="T1" s="402"/>
+      <c r="U1" s="415"/>
+      <c r="V1" s="392"/>
+      <c r="W1" s="415"/>
+      <c r="X1" s="392"/>
     </row>
     <row r="2" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="113"/>
@@ -27083,7 +27060,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="272" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D8" s="274" t="s">
         <v>52</v>
@@ -27092,40 +27069,40 @@
         <v>11</v>
       </c>
       <c r="F8" s="292" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G8" s="369" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="292" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I8" s="293" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J8" s="274" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K8" s="274" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="L8" s="274" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M8" s="274" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N8" s="274" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="274" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="P8" s="274" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="Q8" s="274" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="R8" s="274" t="s">
         <v>168</v>
@@ -27137,7 +27114,7 @@
         <v>45</v>
       </c>
       <c r="U8" s="274" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="V8" s="274" t="s">
         <v>41</v>
@@ -29275,7 +29252,7 @@
       <c r="E92" s="28"/>
       <c r="F92" s="291"/>
       <c r="G92" s="295" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H92" s="72">
         <f>SUM(H9:H88)</f>
@@ -29299,17 +29276,17 @@
       <c r="M93" s="14"/>
     </row>
     <row r="96" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="D96" s="402" t="s">
+      <c r="D96" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="392"/>
-      <c r="F96" s="393"/>
+      <c r="E96" s="404"/>
+      <c r="F96" s="405"/>
       <c r="G96" s="8"/>
-      <c r="I96" s="402" t="s">
+      <c r="I96" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="J96" s="392"/>
-      <c r="K96" s="393"/>
+      <c r="J96" s="404"/>
+      <c r="K96" s="405"/>
       <c r="L96" s="8"/>
     </row>
     <row r="97" spans="4:12" x14ac:dyDescent="0.3">
@@ -29431,7 +29408,7 @@
     </row>
     <row r="106" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G106" s="162" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H106" s="162" t="s">
         <v>32</v>
@@ -29445,7 +29422,7 @@
     </row>
     <row r="107" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G107" s="46" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H107" s="46">
         <f>SUMIF($J$9:$J$88,G107,$F$9:$F$88)</f>
@@ -29462,7 +29439,7 @@
     </row>
     <row r="108" spans="4:12" x14ac:dyDescent="0.3">
       <c r="G108" s="46" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H108" s="46">
         <f>SUMIF($J$9:$J$88,G108,$F$9:$F$88)</f>
@@ -29479,7 +29456,7 @@
     </row>
     <row r="109" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G109" s="97" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H109" s="97">
         <f>SUMIF($J$9:$J$88,G109,$F$9:$F$88)</f>
@@ -29645,17 +29622,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4e7d37e-1dcc-4436-a729-076bff741eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100504A511723502843AC0584E68EC60535" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fbd80a4f17478eeb58df59f7f6ca8f1e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4e7d37e-1dcc-4436-a729-076bff741eab" xmlns:ns3="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="88c3fc8cee6a1370bae988e1d6c9e850" ns2:_="" ns3:_="">
     <xsd:import namespace="f4e7d37e-1dcc-4436-a729-076bff741eab"/>
@@ -29850,6 +29816,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4e7d37e-1dcc-4436-a729-076bff741eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7896FE09-375C-4B80-B12E-A86A22AFA945}">
   <ds:schemaRefs>
@@ -29859,17 +29836,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B44F4C-5208-463C-B02B-93FE2A2E7C51}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f4e7d37e-1dcc-4436-a729-076bff741eab"/>
-    <ds:schemaRef ds:uri="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B400FA9-B915-4F5E-9F2F-389D7B15AAF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29886,4 +29852,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B44F4C-5208-463C-B02B-93FE2A2E7C51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f4e7d37e-1dcc-4436-a729-076bff741eab"/>
+    <ds:schemaRef ds:uri="7ff3518b-2e3d-4dfb-a834-48e552d5b5bf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>